--- a/static/Жилые_Комплексы/ЖК_Бахор/contract_registry.xlsx
+++ b/static/Жилые_Комплексы/ЖК_Бахор/contract_registry.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R2"/>
+  <dimension ref="A1:R4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -525,10 +525,10 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E2" t="n">
-        <v>25</v>
+        <v>33</v>
       </c>
       <c r="F2" t="n">
         <v>1</v>
@@ -538,57 +538,225 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>166 368 000</t>
+          <t>145 572 000</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>4 800 000</t>
+          <t>4 200 000</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>100</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>49 910 400</t>
+          <t>145 572 000</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>Пробник</t>
+          <t>s</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>213</t>
+          <t>s</t>
         </is>
       </c>
       <c r="N2" t="inlineStr">
         <is>
-          <t>21312</t>
+          <t>s</t>
         </is>
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t>2312</t>
+          <t>s</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>21313</t>
+          <t>ss</t>
         </is>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>21313</t>
+          <t>s</t>
         </is>
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>s</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>2025-04-01</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Блок-1</t>
+        </is>
+      </c>
+      <c r="D3" t="n">
+        <v>5</v>
+      </c>
+      <c r="E3" t="n">
+        <v>33</v>
+      </c>
+      <c r="F3" t="n">
+        <v>1</v>
+      </c>
+      <c r="G3" t="n">
+        <v>34.66</v>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>145 572 000</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>4 200 000</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>145 572 000</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>a</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>s</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>a</t>
+        </is>
+      </c>
+      <c r="O3" t="inlineStr">
+        <is>
+          <t>a</t>
+        </is>
+      </c>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>a</t>
+        </is>
+      </c>
+      <c r="Q3" t="inlineStr">
+        <is>
+          <t>a</t>
+        </is>
+      </c>
+      <c r="R3" t="inlineStr">
+        <is>
+          <t>a</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>2025-04-01</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Блок-1</t>
+        </is>
+      </c>
+      <c r="D4" t="n">
+        <v>5</v>
+      </c>
+      <c r="E4" t="n">
+        <v>33</v>
+      </c>
+      <c r="F4" t="n">
+        <v>1</v>
+      </c>
+      <c r="G4" t="n">
+        <v>34.66</v>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>145 572 000</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>4 200 000</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>145 572 000</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>s</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>s</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>s</t>
+        </is>
+      </c>
+      <c r="O4" t="inlineStr">
+        <is>
+          <t>s</t>
+        </is>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>s</t>
+        </is>
+      </c>
+      <c r="Q4" t="inlineStr">
+        <is>
+          <t>s</t>
+        </is>
+      </c>
+      <c r="R4" t="inlineStr">
+        <is>
+          <t>s</t>
         </is>
       </c>
     </row>

--- a/static/Жилые_Комплексы/ЖК_Бахор/contract_registry.xlsx
+++ b/static/Жилые_Комплексы/ЖК_Бахор/contract_registry.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R4"/>
+  <dimension ref="A1:R1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -505,258 +505,6 @@
       <c r="R1" t="inlineStr">
         <is>
           <t>Отдел Продаж</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>2025-04-01</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Блок-1</t>
-        </is>
-      </c>
-      <c r="D2" t="n">
-        <v>5</v>
-      </c>
-      <c r="E2" t="n">
-        <v>33</v>
-      </c>
-      <c r="F2" t="n">
-        <v>1</v>
-      </c>
-      <c r="G2" t="n">
-        <v>34.66</v>
-      </c>
-      <c r="H2" t="inlineStr">
-        <is>
-          <t>145 572 000</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>4 200 000</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
-      <c r="K2" t="inlineStr">
-        <is>
-          <t>145 572 000</t>
-        </is>
-      </c>
-      <c r="L2" t="inlineStr">
-        <is>
-          <t>s</t>
-        </is>
-      </c>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>s</t>
-        </is>
-      </c>
-      <c r="N2" t="inlineStr">
-        <is>
-          <t>s</t>
-        </is>
-      </c>
-      <c r="O2" t="inlineStr">
-        <is>
-          <t>s</t>
-        </is>
-      </c>
-      <c r="P2" t="inlineStr">
-        <is>
-          <t>ss</t>
-        </is>
-      </c>
-      <c r="Q2" t="inlineStr">
-        <is>
-          <t>s</t>
-        </is>
-      </c>
-      <c r="R2" t="inlineStr">
-        <is>
-          <t>s</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>2025-04-01</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Блок-1</t>
-        </is>
-      </c>
-      <c r="D3" t="n">
-        <v>5</v>
-      </c>
-      <c r="E3" t="n">
-        <v>33</v>
-      </c>
-      <c r="F3" t="n">
-        <v>1</v>
-      </c>
-      <c r="G3" t="n">
-        <v>34.66</v>
-      </c>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>145 572 000</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>4 200 000</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
-      <c r="K3" t="inlineStr">
-        <is>
-          <t>145 572 000</t>
-        </is>
-      </c>
-      <c r="L3" t="inlineStr">
-        <is>
-          <t>a</t>
-        </is>
-      </c>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>s</t>
-        </is>
-      </c>
-      <c r="N3" t="inlineStr">
-        <is>
-          <t>a</t>
-        </is>
-      </c>
-      <c r="O3" t="inlineStr">
-        <is>
-          <t>a</t>
-        </is>
-      </c>
-      <c r="P3" t="inlineStr">
-        <is>
-          <t>a</t>
-        </is>
-      </c>
-      <c r="Q3" t="inlineStr">
-        <is>
-          <t>a</t>
-        </is>
-      </c>
-      <c r="R3" t="inlineStr">
-        <is>
-          <t>a</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>2025-04-01</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Блок-1</t>
-        </is>
-      </c>
-      <c r="D4" t="n">
-        <v>5</v>
-      </c>
-      <c r="E4" t="n">
-        <v>33</v>
-      </c>
-      <c r="F4" t="n">
-        <v>1</v>
-      </c>
-      <c r="G4" t="n">
-        <v>34.66</v>
-      </c>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>145 572 000</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>4 200 000</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
-      <c r="K4" t="inlineStr">
-        <is>
-          <t>145 572 000</t>
-        </is>
-      </c>
-      <c r="L4" t="inlineStr">
-        <is>
-          <t>s</t>
-        </is>
-      </c>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>s</t>
-        </is>
-      </c>
-      <c r="N4" t="inlineStr">
-        <is>
-          <t>s</t>
-        </is>
-      </c>
-      <c r="O4" t="inlineStr">
-        <is>
-          <t>s</t>
-        </is>
-      </c>
-      <c r="P4" t="inlineStr">
-        <is>
-          <t>s</t>
-        </is>
-      </c>
-      <c r="Q4" t="inlineStr">
-        <is>
-          <t>s</t>
-        </is>
-      </c>
-      <c r="R4" t="inlineStr">
-        <is>
-          <t>s</t>
         </is>
       </c>
     </row>

--- a/static/Жилые_Комплексы/ЖК_Бахор/contract_registry.xlsx
+++ b/static/Жилые_Комплексы/ЖК_Бахор/contract_registry.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>

--- a/static/Жилые_Комплексы/ЖК_Бахор/contract_registry.xlsx
+++ b/static/Жилые_Комплексы/ЖК_Бахор/contract_registry.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R1"/>
+  <dimension ref="A1:R3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -505,6 +505,174 @@
       <c r="R1" t="inlineStr">
         <is>
           <t>Отдел Продаж</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>2025-04-02</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>Блок-1</t>
+        </is>
+      </c>
+      <c r="D2" t="n">
+        <v>4</v>
+      </c>
+      <c r="E2" t="n">
+        <v>25</v>
+      </c>
+      <c r="F2" t="n">
+        <v>1</v>
+      </c>
+      <c r="G2" t="n">
+        <v>34.66</v>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>166368000</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>4800000</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>49910400</t>
+        </is>
+      </c>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>BEGIMOVA DILBAR TALIPBAEVNA</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>AC2328553</t>
+        </is>
+      </c>
+      <c r="N2" t="inlineStr">
+        <is>
+          <t>42306750520013</t>
+        </is>
+      </c>
+      <c r="O2" t="inlineStr">
+        <is>
+          <t>TOSHKENT VILOYATI CHIRCHIQ SHAHAR IIB</t>
+        </is>
+      </c>
+      <c r="P2" t="inlineStr">
+        <is>
+          <t>TOSHKENT VILOYATI CHIRCHIQ SHAHAR AMIR TEMUR KOCHSSI  11 UY 99 XONADON</t>
+        </is>
+      </c>
+      <c r="Q2" t="inlineStr">
+        <is>
+          <t>+998978721262</t>
+        </is>
+      </c>
+      <c r="R2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>2025-04-02</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Блок-1</t>
+        </is>
+      </c>
+      <c r="D3" t="n">
+        <v>5</v>
+      </c>
+      <c r="E3" t="n">
+        <v>33</v>
+      </c>
+      <c r="F3" t="n">
+        <v>1</v>
+      </c>
+      <c r="G3" t="n">
+        <v>34.66</v>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>166368000</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>4800000</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>49910400</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>YULDASHEV DAVLAT QO`ZIYEVICH</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>AB2845141</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>32405720560035</t>
+        </is>
+      </c>
+      <c r="O3" t="inlineStr">
+        <is>
+          <t>TOSHKENT VILOYATI QIBRAY TUMANI IIB</t>
+        </is>
+      </c>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>TOSHKENT VILOYATI QIBRAY TUMANI QIPCHOQ Q.F.Y BUNYOD KO`CHASI 7-UY 1-XONADON</t>
+        </is>
+      </c>
+      <c r="Q3" t="inlineStr">
+        <is>
+          <t>+998881701525</t>
+        </is>
+      </c>
+      <c r="R3" t="inlineStr">
+        <is>
+          <t>DILFUZA</t>
         </is>
       </c>
     </row>

--- a/static/Жилые_Комплексы/ЖК_Бахор/contract_registry.xlsx
+++ b/static/Жилые_Комплексы/ЖК_Бахор/contract_registry.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R3"/>
+  <dimension ref="A1:R4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -673,6 +673,84 @@
       <c r="R3" t="inlineStr">
         <is>
           <t>DILFUZA</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>2025-04-02</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Блок-1</t>
+        </is>
+      </c>
+      <c r="D4" t="n">
+        <v>5</v>
+      </c>
+      <c r="E4" t="n">
+        <v>34</v>
+      </c>
+      <c r="F4" t="n">
+        <v>1</v>
+      </c>
+      <c r="G4" t="n">
+        <v>47.91</v>
+      </c>
+      <c r="H4" t="n">
+        <v>229968000</v>
+      </c>
+      <c r="I4" t="n">
+        <v>4800000</v>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="K4" t="n">
+        <v>68990400</v>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>as</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>as</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>sa</t>
+        </is>
+      </c>
+      <c r="O4" t="inlineStr">
+        <is>
+          <t>as</t>
+        </is>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>as</t>
+        </is>
+      </c>
+      <c r="Q4" t="inlineStr">
+        <is>
+          <t>as</t>
+        </is>
+      </c>
+      <c r="R4" t="inlineStr">
+        <is>
+          <t>as</t>
         </is>
       </c>
     </row>

--- a/static/Жилые_Комплексы/ЖК_Бахор/contract_registry.xlsx
+++ b/static/Жилые_Комплексы/ЖК_Бахор/contract_registry.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R4"/>
+  <dimension ref="A1:R5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -620,25 +620,19 @@
       <c r="G3" t="n">
         <v>34.66</v>
       </c>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>166368000</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>4800000</t>
-        </is>
+      <c r="H3" t="n">
+        <v>166368000</v>
+      </c>
+      <c r="I3" t="n">
+        <v>4800000</v>
       </c>
       <c r="J3" t="inlineStr">
         <is>
           <t>30</t>
         </is>
       </c>
-      <c r="K3" t="inlineStr">
-        <is>
-          <t>49910400</t>
-        </is>
+      <c r="K3" t="n">
+        <v>49910400</v>
       </c>
       <c r="L3" t="inlineStr">
         <is>
@@ -672,7 +666,7 @@
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>DILFUZA</t>
+          <t>Dilfuza</t>
         </is>
       </c>
     </row>
@@ -684,73 +678,151 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2025-04-02</t>
+          <t>2025-04-03</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Блок-1</t>
+          <t>Блок 2</t>
         </is>
       </c>
       <c r="D4" t="n">
         <v>5</v>
       </c>
       <c r="E4" t="n">
-        <v>34</v>
+        <v>108</v>
       </c>
       <c r="F4" t="n">
         <v>1</v>
       </c>
       <c r="G4" t="n">
-        <v>47.91</v>
+        <v>32.46</v>
       </c>
       <c r="H4" t="n">
-        <v>229968000</v>
+        <v>149316000</v>
       </c>
       <c r="I4" t="n">
+        <v>4600000</v>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="K4" t="n">
+        <v>44794800</v>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">SAGDIYEV GIYOSBEK MIXRIDDIN O`G`LI </t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">AD8007552 </t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>31605986720016</t>
+        </is>
+      </c>
+      <c r="O4" t="inlineStr">
+        <is>
+          <t>IIV 27224</t>
+        </is>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>TOSHKENT VILOYATI BO`STONLIQ TUMANI XONDOYLIQ QISHLOG`I XO`JA KO`CHASI 42-UY</t>
+        </is>
+      </c>
+      <c r="Q4" t="inlineStr">
+        <is>
+          <t>+998 94 427-32-64</t>
+        </is>
+      </c>
+      <c r="R4" t="inlineStr">
+        <is>
+          <t>Dilfuza</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>2025-04-03</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Блок 3</t>
+        </is>
+      </c>
+      <c r="D5" t="n">
+        <v>3</v>
+      </c>
+      <c r="E5" t="n">
+        <v>205</v>
+      </c>
+      <c r="F5" t="n">
+        <v>3</v>
+      </c>
+      <c r="G5" t="n">
+        <v>57.77</v>
+      </c>
+      <c r="H5" t="n">
+        <v>277296000</v>
+      </c>
+      <c r="I5" t="n">
         <v>4800000</v>
       </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="K4" t="n">
-        <v>68990400</v>
-      </c>
-      <c r="L4" t="inlineStr">
-        <is>
-          <t>as</t>
-        </is>
-      </c>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>as</t>
-        </is>
-      </c>
-      <c r="N4" t="inlineStr">
-        <is>
-          <t>sa</t>
-        </is>
-      </c>
-      <c r="O4" t="inlineStr">
-        <is>
-          <t>as</t>
-        </is>
-      </c>
-      <c r="P4" t="inlineStr">
-        <is>
-          <t>as</t>
-        </is>
-      </c>
-      <c r="Q4" t="inlineStr">
-        <is>
-          <t>as</t>
-        </is>
-      </c>
-      <c r="R4" t="inlineStr">
-        <is>
-          <t>as</t>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="K5" t="n">
+        <v>138648000</v>
+      </c>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>TEMIROVA SHOXISTA UMID QIZI</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>AD0221149</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>60811036340017</t>
+        </is>
+      </c>
+      <c r="O5" t="inlineStr">
+        <is>
+          <t>IIV 22234</t>
+        </is>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>TOSHKENT VILOYATI CHIRCHIQ SHAHAR 50 YILLIK SHOX KO'CHASI 2 UY 122 XONADON</t>
+        </is>
+      </c>
+      <c r="Q5" t="inlineStr">
+        <is>
+          <t>+998934034858</t>
+        </is>
+      </c>
+      <c r="R5" t="inlineStr">
+        <is>
+          <t>DILFUZA</t>
         </is>
       </c>
     </row>

--- a/static/Жилые_Комплексы/ЖК_Бахор/contract_registry.xlsx
+++ b/static/Жилые_Комплексы/ЖК_Бахор/contract_registry.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R5"/>
+  <dimension ref="A1:R16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -823,6 +823,864 @@
       <c r="R5" t="inlineStr">
         <is>
           <t>DILFUZA</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>2025-04-04</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Блок 2</t>
+        </is>
+      </c>
+      <c r="D6" t="n">
+        <v>4</v>
+      </c>
+      <c r="E6" t="n">
+        <v>102</v>
+      </c>
+      <c r="F6" t="n">
+        <v>1</v>
+      </c>
+      <c r="G6" t="n">
+        <v>32.46</v>
+      </c>
+      <c r="H6" t="n">
+        <v>155808000</v>
+      </c>
+      <c r="I6" t="n">
+        <v>4800000</v>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="K6" t="n">
+        <v>46742400</v>
+      </c>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>ABDUXODJAYEVA SARVINOZ GAFUROVNA</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>AD2469585</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>41403880640057</t>
+        </is>
+      </c>
+      <c r="O6" t="inlineStr">
+        <is>
+          <t>IIV 26277 02.02.2033</t>
+        </is>
+      </c>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>TOSHKENT SHAHAR SHAYHONTOHUR TUMANI BEKZOD KUCHASI 71 UY</t>
+        </is>
+      </c>
+      <c r="Q6" t="inlineStr">
+        <is>
+          <t>+998998322266</t>
+        </is>
+      </c>
+      <c r="R6" t="inlineStr">
+        <is>
+          <t>AZIZ</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>2025-04-04</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Блок 2</t>
+        </is>
+      </c>
+      <c r="D7" t="n">
+        <v>3</v>
+      </c>
+      <c r="E7" t="n">
+        <v>96</v>
+      </c>
+      <c r="F7" t="n">
+        <v>1</v>
+      </c>
+      <c r="G7" t="n">
+        <v>32.46</v>
+      </c>
+      <c r="H7" t="n">
+        <v>142824000</v>
+      </c>
+      <c r="I7" t="n">
+        <v>4400000</v>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="K7" t="n">
+        <v>142824000</v>
+      </c>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>XUDAYAROV FARRUX MAKSUDOVICH</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>AD2740629</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>32504880050041</t>
+        </is>
+      </c>
+      <c r="O7" t="inlineStr">
+        <is>
+          <t>IIV 26266</t>
+        </is>
+      </c>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>TOSHKENT SHAHAR, YUNUSOBOD TUMANI, UVAYSIY M.F.Y, 19-MAVZE, 5-UY, 64-XONADON</t>
+        </is>
+      </c>
+      <c r="Q7" t="inlineStr">
+        <is>
+          <t>+998 90 014 00 40</t>
+        </is>
+      </c>
+      <c r="R7" t="inlineStr">
+        <is>
+          <t>NILUFAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>2025-04-06</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Блок-1,1</t>
+        </is>
+      </c>
+      <c r="D8" t="n">
+        <v>4</v>
+      </c>
+      <c r="E8" t="n">
+        <v>69</v>
+      </c>
+      <c r="F8" t="n">
+        <v>1</v>
+      </c>
+      <c r="G8" t="n">
+        <v>34.66</v>
+      </c>
+      <c r="H8" t="n">
+        <v>166368000</v>
+      </c>
+      <c r="I8" t="n">
+        <v>4800000</v>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="K8" t="n">
+        <v>49910400</v>
+      </c>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>DAVIROVA GULANDOM NAJBUDDIN QIZI</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>AD5952187</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr">
+        <is>
+          <t>42112956420015</t>
+        </is>
+      </c>
+      <c r="O8" t="inlineStr">
+        <is>
+          <t>IIV 26296</t>
+        </is>
+      </c>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>TOSHKENT SHAHRI MIRZO ULUG`BEK TUMANI TTZ-1 42 36</t>
+        </is>
+      </c>
+      <c r="Q8" t="inlineStr">
+        <is>
+          <t>+998 98 128-55-22</t>
+        </is>
+      </c>
+      <c r="R8" t="inlineStr">
+        <is>
+          <t>DILFUZA</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>2025-04-06</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Блок 3</t>
+        </is>
+      </c>
+      <c r="D9" t="n">
+        <v>2</v>
+      </c>
+      <c r="E9" t="n">
+        <v>196</v>
+      </c>
+      <c r="F9" t="n">
+        <v>2</v>
+      </c>
+      <c r="G9" t="n">
+        <v>44.28</v>
+      </c>
+      <c r="H9" t="n">
+        <v>230256000</v>
+      </c>
+      <c r="I9" t="n">
+        <v>5200000</v>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="K9" t="n">
+        <v>69076800</v>
+      </c>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>MIRVAKULOVA MADINA MURADILAYEVNA</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>AD6508444</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr">
+        <is>
+          <t>41401790470025</t>
+        </is>
+      </c>
+      <c r="O9" t="inlineStr">
+        <is>
+          <t>IIV 27419</t>
+        </is>
+      </c>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>TOSHKENT VILOYATI CHIRCHIQ SHAHAR TEMIR YO`LCHILAR KO`CHASI 160-UY</t>
+        </is>
+      </c>
+      <c r="Q9" t="inlineStr">
+        <is>
+          <t>+998 90 914-17-00</t>
+        </is>
+      </c>
+      <c r="R9" t="inlineStr">
+        <is>
+          <t>DILFUZA</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>2025-04-09</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Блок 3,2</t>
+        </is>
+      </c>
+      <c r="D10" t="n">
+        <v>3</v>
+      </c>
+      <c r="E10" t="n">
+        <v>262</v>
+      </c>
+      <c r="F10" t="n">
+        <v>2</v>
+      </c>
+      <c r="G10" t="n">
+        <v>44.28</v>
+      </c>
+      <c r="H10" t="n">
+        <v>212544000</v>
+      </c>
+      <c r="I10" t="n">
+        <v>4800000</v>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="K10" t="n">
+        <v>106272000</v>
+      </c>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>RAJABOVA SHAHLO GULAMOVNA</t>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>AB3035920</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr">
+        <is>
+          <t>0405712730043</t>
+        </is>
+      </c>
+      <c r="O10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">QASHQADARYO VILOYATI SHAHRISABZ TUMANI </t>
+        </is>
+      </c>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">QASHQADARYO VILOYATI SHAHRISABZ TUMANI UYMOVIT KOCHASI 166-UY </t>
+        </is>
+      </c>
+      <c r="Q10" t="inlineStr">
+        <is>
+          <t>996722067</t>
+        </is>
+      </c>
+      <c r="R10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Фатима </t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>2025-04-11</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Блок 2</t>
+        </is>
+      </c>
+      <c r="D11" t="n">
+        <v>4</v>
+      </c>
+      <c r="E11" t="n">
+        <v>99</v>
+      </c>
+      <c r="F11" t="n">
+        <v>2</v>
+      </c>
+      <c r="G11" t="n">
+        <v>48.13</v>
+      </c>
+      <c r="H11" t="n">
+        <v>231024000</v>
+      </c>
+      <c r="I11" t="n">
+        <v>4800000</v>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="K11" t="n">
+        <v>69307200</v>
+      </c>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ASANOVA LILYA REMZIYEVNA </t>
+        </is>
+      </c>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>AD6245447</t>
+        </is>
+      </c>
+      <c r="N11" t="inlineStr">
+        <is>
+          <t>40501760270044</t>
+        </is>
+      </c>
+      <c r="O11" t="inlineStr">
+        <is>
+          <t>IIV27419</t>
+        </is>
+      </c>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>8-МКР ДОМ-57А КВ-32</t>
+        </is>
+      </c>
+      <c r="Q11" t="inlineStr">
+        <is>
+          <t>933126685</t>
+        </is>
+      </c>
+      <c r="R11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Фатима </t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>2025-04-11</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Блок 1,2</t>
+        </is>
+      </c>
+      <c r="D12" t="n">
+        <v>4</v>
+      </c>
+      <c r="E12" t="n">
+        <v>136</v>
+      </c>
+      <c r="F12" t="n">
+        <v>2</v>
+      </c>
+      <c r="G12" t="n">
+        <v>50.34</v>
+      </c>
+      <c r="H12" t="n">
+        <v>221496000</v>
+      </c>
+      <c r="I12" t="n">
+        <v>4400000</v>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>70</t>
+        </is>
+      </c>
+      <c r="K12" t="n">
+        <v>155047200</v>
+      </c>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">YULDASHOV RUSTAM JUMABAYEVICH </t>
+        </is>
+      </c>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>AE1422008</t>
+        </is>
+      </c>
+      <c r="N12" t="inlineStr">
+        <is>
+          <t>31509827110021</t>
+        </is>
+      </c>
+      <c r="O12" t="inlineStr">
+        <is>
+          <t>IIV27419</t>
+        </is>
+      </c>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>8-МКР 25-ДОМ КВ-6</t>
+        </is>
+      </c>
+      <c r="Q12" t="inlineStr">
+        <is>
+          <t>930041782</t>
+        </is>
+      </c>
+      <c r="R12" t="inlineStr">
+        <is>
+          <t>Фатима</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>2025-04-15</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Блок-1</t>
+        </is>
+      </c>
+      <c r="D13" t="n">
+        <v>3</v>
+      </c>
+      <c r="E13" t="n">
+        <v>17</v>
+      </c>
+      <c r="F13" t="n">
+        <v>1</v>
+      </c>
+      <c r="G13" t="n">
+        <v>34.66</v>
+      </c>
+      <c r="H13" t="n">
+        <v>173300000</v>
+      </c>
+      <c r="I13" t="n">
+        <v>5000000</v>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="K13" t="n">
+        <v>51990000</v>
+      </c>
+      <c r="L13" t="inlineStr">
+        <is>
+          <t>MIRALIYEVA NURKUL ANVAROVNA</t>
+        </is>
+      </c>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>AC0374727</t>
+        </is>
+      </c>
+      <c r="N13" t="inlineStr">
+        <is>
+          <t>42401710560026</t>
+        </is>
+      </c>
+      <c r="O13" t="inlineStr">
+        <is>
+          <t>TOSHKENT VILOYATI QIBRAY TUMANI IIB</t>
+        </is>
+      </c>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>TOSHKENT SHAHAR, MIRZO ULUG'BEK TUMANI, FERUZA ko'chasi, KATTA YALANG'OCH OTA MFY, 7a uy, 40-xonadon.</t>
+        </is>
+      </c>
+      <c r="Q13" t="inlineStr">
+        <is>
+          <t>+998 99 088 39 10</t>
+        </is>
+      </c>
+      <c r="R13" t="inlineStr">
+        <is>
+          <t>DILFUZA</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>2025-04-16</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Блок 3,1</t>
+        </is>
+      </c>
+      <c r="D14" t="n">
+        <v>4</v>
+      </c>
+      <c r="E14" t="n">
+        <v>241</v>
+      </c>
+      <c r="F14" t="n">
+        <v>3</v>
+      </c>
+      <c r="G14" t="n">
+        <v>57.77</v>
+      </c>
+      <c r="H14" t="n">
+        <v>265742000</v>
+      </c>
+      <c r="I14" t="n">
+        <v>4600000</v>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="K14" t="n">
+        <v>132871000</v>
+      </c>
+      <c r="L14" t="inlineStr">
+        <is>
+          <t>DJUMABAYOV SHAXZOD RASHID O`G`LI</t>
+        </is>
+      </c>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>AD0916309</t>
+        </is>
+      </c>
+      <c r="N14" t="inlineStr">
+        <is>
+          <t>31901950470010</t>
+        </is>
+      </c>
+      <c r="O14" t="inlineStr">
+        <is>
+          <t>TOSHKENT VILOYATI CHIRCHIQ SHAHRI IIV 27419</t>
+        </is>
+      </c>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>CHIRCHIQ SHAHAR  BOBUR M.F.Y G`OFUR G`ULOM KO`CHASI 11-UY</t>
+        </is>
+      </c>
+      <c r="Q14" t="inlineStr">
+        <is>
+          <t>+998 91 777-98-18</t>
+        </is>
+      </c>
+      <c r="R14" t="inlineStr">
+        <is>
+          <t>DILFUZA</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>2025-04-19</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Блок 3</t>
+        </is>
+      </c>
+      <c r="D15" t="n">
+        <v>3</v>
+      </c>
+      <c r="E15" t="n">
+        <v>204</v>
+      </c>
+      <c r="F15" t="n">
+        <v>2</v>
+      </c>
+      <c r="G15" t="n">
+        <v>46.67</v>
+      </c>
+      <c r="H15" t="n">
+        <v>233350000</v>
+      </c>
+      <c r="I15" t="n">
+        <v>5000000</v>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="K15" t="n">
+        <v>70005000</v>
+      </c>
+      <c r="L15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">GANIYEVA NIGORA RUSTAMOVNA </t>
+        </is>
+      </c>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>AB1877409</t>
+        </is>
+      </c>
+      <c r="N15" t="inlineStr">
+        <is>
+          <t>407028105600346</t>
+        </is>
+      </c>
+      <c r="O15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TOSHKENT VILOYATI CHIRCHIQ SHAHAR IIB </t>
+        </is>
+      </c>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>10-МКР 17/8</t>
+        </is>
+      </c>
+      <c r="Q15" t="inlineStr">
+        <is>
+          <t>901340781</t>
+        </is>
+      </c>
+      <c r="R15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">АЗИЗ </t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>2025-04-21</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Блок-1</t>
+        </is>
+      </c>
+      <c r="D16" t="n">
+        <v>5</v>
+      </c>
+      <c r="E16" t="n">
+        <v>34</v>
+      </c>
+      <c r="F16" t="n">
+        <v>1</v>
+      </c>
+      <c r="G16" t="n">
+        <v>47.91</v>
+      </c>
+      <c r="H16" t="n">
+        <v>220386000</v>
+      </c>
+      <c r="I16" t="n">
+        <v>4600000</v>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="K16" t="n">
+        <v>66115800</v>
+      </c>
+      <c r="L16" t="inlineStr">
+        <is>
+          <t>sdf</t>
+        </is>
+      </c>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>sdf</t>
+        </is>
+      </c>
+      <c r="N16" t="inlineStr">
+        <is>
+          <t>sdf</t>
+        </is>
+      </c>
+      <c r="O16" t="inlineStr">
+        <is>
+          <t>sdf</t>
+        </is>
+      </c>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>sdf</t>
+        </is>
+      </c>
+      <c r="Q16" t="inlineStr">
+        <is>
+          <t>df</t>
+        </is>
+      </c>
+      <c r="R16" t="inlineStr">
+        <is>
+          <t>df</t>
         </is>
       </c>
     </row>

--- a/static/Жилые_Комплексы/ЖК_Бахор/contract_registry.xlsx
+++ b/static/Жилые_Комплексы/ЖК_Бахор/contract_registry.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R16"/>
+  <dimension ref="A1:R15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1603,84 +1603,6 @@
       <c r="R15" t="inlineStr">
         <is>
           <t xml:space="preserve">АЗИЗ </t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>2025-04-21</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Блок-1</t>
-        </is>
-      </c>
-      <c r="D16" t="n">
-        <v>5</v>
-      </c>
-      <c r="E16" t="n">
-        <v>34</v>
-      </c>
-      <c r="F16" t="n">
-        <v>1</v>
-      </c>
-      <c r="G16" t="n">
-        <v>47.91</v>
-      </c>
-      <c r="H16" t="n">
-        <v>220386000</v>
-      </c>
-      <c r="I16" t="n">
-        <v>4600000</v>
-      </c>
-      <c r="J16" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="K16" t="n">
-        <v>66115800</v>
-      </c>
-      <c r="L16" t="inlineStr">
-        <is>
-          <t>sdf</t>
-        </is>
-      </c>
-      <c r="M16" t="inlineStr">
-        <is>
-          <t>sdf</t>
-        </is>
-      </c>
-      <c r="N16" t="inlineStr">
-        <is>
-          <t>sdf</t>
-        </is>
-      </c>
-      <c r="O16" t="inlineStr">
-        <is>
-          <t>sdf</t>
-        </is>
-      </c>
-      <c r="P16" t="inlineStr">
-        <is>
-          <t>sdf</t>
-        </is>
-      </c>
-      <c r="Q16" t="inlineStr">
-        <is>
-          <t>df</t>
-        </is>
-      </c>
-      <c r="R16" t="inlineStr">
-        <is>
-          <t>df</t>
         </is>
       </c>
     </row>

--- a/static/Жилые_Комплексы/ЖК_Бахор/contract_registry.xlsx
+++ b/static/Жилые_Комплексы/ЖК_Бахор/contract_registry.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R33"/>
+  <dimension ref="A1:R34"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3010,6 +3010,84 @@
         </is>
       </c>
     </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>34</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>2025-05-03</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>Блок 1,2</t>
+        </is>
+      </c>
+      <c r="D34" t="n">
+        <v>5</v>
+      </c>
+      <c r="E34" t="n">
+        <v>145</v>
+      </c>
+      <c r="F34" t="n">
+        <v>1</v>
+      </c>
+      <c r="G34" t="n">
+        <v>34.66</v>
+      </c>
+      <c r="H34" t="n">
+        <v>166368000</v>
+      </c>
+      <c r="I34" t="n">
+        <v>4800000</v>
+      </c>
+      <c r="J34" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="K34" t="n">
+        <v>49910400</v>
+      </c>
+      <c r="L34" t="inlineStr">
+        <is>
+          <t>MIRALIMOV ERKIN ERGASHVOIVICH</t>
+        </is>
+      </c>
+      <c r="M34" t="inlineStr">
+        <is>
+          <t>AD2988250</t>
+        </is>
+      </c>
+      <c r="N34" t="inlineStr">
+        <is>
+          <t>31710810470037</t>
+        </is>
+      </c>
+      <c r="O34" t="inlineStr">
+        <is>
+          <t>TOSHKENT VILOYATI CHIRCHIQ SHAHAR IIV 27419</t>
+        </is>
+      </c>
+      <c r="P34" t="inlineStr">
+        <is>
+          <t>TOSHKENT VILOYATI CHIRCHIQ SHAHAR G`OFUR G`ULOM KO`CHASI 17-UY</t>
+        </is>
+      </c>
+      <c r="Q34" t="inlineStr">
+        <is>
+          <t xml:space="preserve">+998 77 072 63 69 </t>
+        </is>
+      </c>
+      <c r="R34" t="inlineStr">
+        <is>
+          <t>DILFUZA</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/static/Жилые_Комплексы/ЖК_Бахор/contract_registry.xlsx
+++ b/static/Жилые_Комплексы/ЖК_Бахор/contract_registry.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R34"/>
+  <dimension ref="A1:R36"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3088,6 +3088,162 @@
         </is>
       </c>
     </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>35</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>2025-05-05</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>Блок 3,1</t>
+        </is>
+      </c>
+      <c r="D35" t="n">
+        <v>1</v>
+      </c>
+      <c r="E35" t="n">
+        <v>220</v>
+      </c>
+      <c r="F35" t="n">
+        <v>2</v>
+      </c>
+      <c r="G35" t="n">
+        <v>41.88</v>
+      </c>
+      <c r="H35" t="n">
+        <v>234528000</v>
+      </c>
+      <c r="I35" t="n">
+        <v>5600000</v>
+      </c>
+      <c r="J35" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="K35" t="n">
+        <v>70358400</v>
+      </c>
+      <c r="L35" t="inlineStr">
+        <is>
+          <t>TOSHMATOVA GULGINA MIDXATOVNA</t>
+        </is>
+      </c>
+      <c r="M35" t="inlineStr">
+        <is>
+          <t>AD3519875</t>
+        </is>
+      </c>
+      <c r="N35" t="inlineStr">
+        <is>
+          <t>41408686860016</t>
+        </is>
+      </c>
+      <c r="O35" t="inlineStr">
+        <is>
+          <t>IIV 27419</t>
+        </is>
+      </c>
+      <c r="P35" t="inlineStr">
+        <is>
+          <t>TOSHKENT VILOYATI CHIRCHIQ SHAHAR XAYOTGULI KO'CHASI 39-UY</t>
+        </is>
+      </c>
+      <c r="Q35" t="inlineStr">
+        <is>
+          <t>+998 88 178 98 48</t>
+        </is>
+      </c>
+      <c r="R35" t="inlineStr">
+        <is>
+          <t>DILFUZA</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>36</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>2025-05-05</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>Блок-1</t>
+        </is>
+      </c>
+      <c r="D36" t="n">
+        <v>3</v>
+      </c>
+      <c r="E36" t="n">
+        <v>20</v>
+      </c>
+      <c r="F36" t="n">
+        <v>2</v>
+      </c>
+      <c r="G36" t="n">
+        <v>50.34</v>
+      </c>
+      <c r="H36" t="n">
+        <v>251700000</v>
+      </c>
+      <c r="I36" t="n">
+        <v>5000000</v>
+      </c>
+      <c r="J36" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="K36" t="n">
+        <v>125850000</v>
+      </c>
+      <c r="L36" t="inlineStr">
+        <is>
+          <t>OXUNOV MUXTOR TULQINOVICH</t>
+        </is>
+      </c>
+      <c r="M36" t="inlineStr">
+        <is>
+          <t>AD3843344</t>
+        </is>
+      </c>
+      <c r="N36" t="inlineStr">
+        <is>
+          <t>33005686860012</t>
+        </is>
+      </c>
+      <c r="O36" t="inlineStr">
+        <is>
+          <t>IIV 27419 06.07.2023</t>
+        </is>
+      </c>
+      <c r="P36" t="inlineStr">
+        <is>
+          <t>TOSHKENT VILOYATI CHIRCHIK SHAHAR 10 KICHIK NOXIYA 31 UY 53 XONADON</t>
+        </is>
+      </c>
+      <c r="Q36" t="inlineStr">
+        <is>
+          <t>+998942125661</t>
+        </is>
+      </c>
+      <c r="R36" t="inlineStr">
+        <is>
+          <t>AZIZ</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/static/Жилые_Комплексы/ЖК_Бахор/contract_registry.xlsx
+++ b/static/Жилые_Комплексы/ЖК_Бахор/contract_registry.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R36"/>
+  <dimension ref="A1:R40"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3244,6 +3244,318 @@
         </is>
       </c>
     </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>37</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>2025-05-08</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>Блок 3</t>
+        </is>
+      </c>
+      <c r="D37" t="n">
+        <v>1</v>
+      </c>
+      <c r="E37" t="n">
+        <v>190</v>
+      </c>
+      <c r="F37" t="n">
+        <v>2</v>
+      </c>
+      <c r="G37" t="n">
+        <v>41.88</v>
+      </c>
+      <c r="H37" t="n">
+        <v>234528000</v>
+      </c>
+      <c r="I37" t="n">
+        <v>5600000</v>
+      </c>
+      <c r="J37" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="K37" t="n">
+        <v>70358400</v>
+      </c>
+      <c r="L37" t="inlineStr">
+        <is>
+          <t>NAZIROVA MAFTUNA BAXTIYOROVNA</t>
+        </is>
+      </c>
+      <c r="M37" t="inlineStr">
+        <is>
+          <t>AB4820841</t>
+        </is>
+      </c>
+      <c r="N37" t="inlineStr">
+        <is>
+          <t>41508930500043</t>
+        </is>
+      </c>
+      <c r="O37" t="inlineStr">
+        <is>
+          <t>TOSHKENT VILOYATI BO`STONLIQ TUMANI IIB</t>
+        </is>
+      </c>
+      <c r="P37" t="inlineStr">
+        <is>
+          <t>TOSHKENT VILOYATI CHIRCHIQ SHAHAR MUQUMIY KO`CHASI 38-UY 28-XONADON</t>
+        </is>
+      </c>
+      <c r="Q37" t="inlineStr">
+        <is>
+          <t>+998 99 993-69-47</t>
+        </is>
+      </c>
+      <c r="R37" t="inlineStr">
+        <is>
+          <t>DILFUZA</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>38</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>2025-05-12</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>Блок 3,2</t>
+        </is>
+      </c>
+      <c r="D38" t="n">
+        <v>3</v>
+      </c>
+      <c r="E38" t="n">
+        <v>266</v>
+      </c>
+      <c r="F38" t="n">
+        <v>1</v>
+      </c>
+      <c r="G38" t="n">
+        <v>25.04</v>
+      </c>
+      <c r="H38" t="n">
+        <v>115184000</v>
+      </c>
+      <c r="I38" t="n">
+        <v>4600000</v>
+      </c>
+      <c r="J38" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="K38" t="n">
+        <v>115184000</v>
+      </c>
+      <c r="L38" t="inlineStr">
+        <is>
+          <t>XAMIDULLAYEV ASADBEK SHERXON O'G'LI</t>
+        </is>
+      </c>
+      <c r="M38" t="inlineStr">
+        <is>
+          <t>AC2489461</t>
+        </is>
+      </c>
+      <c r="N38" t="inlineStr">
+        <is>
+          <t>51711036060037</t>
+        </is>
+      </c>
+      <c r="O38" t="inlineStr">
+        <is>
+          <t>SAMARQAND VILOYATI KATTAQO'RG'ON TUMANI IIB</t>
+        </is>
+      </c>
+      <c r="P38" t="inlineStr">
+        <is>
+          <t>SAMARQAND VILOYATI KATTAQO'RG'ON TUMANI KATTA KO'RPA KO'CHASI 2-UY</t>
+        </is>
+      </c>
+      <c r="Q38" t="inlineStr">
+        <is>
+          <t>+998 97 727 36 42</t>
+        </is>
+      </c>
+      <c r="R38" t="inlineStr">
+        <is>
+          <t>NILUFAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>39</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>2025-05-12</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>Блок 3,2</t>
+        </is>
+      </c>
+      <c r="D39" t="n">
+        <v>3</v>
+      </c>
+      <c r="E39" t="n">
+        <v>265</v>
+      </c>
+      <c r="F39" t="n">
+        <v>3</v>
+      </c>
+      <c r="G39" t="n">
+        <v>57.77</v>
+      </c>
+      <c r="H39" t="n">
+        <v>288850000</v>
+      </c>
+      <c r="I39" t="n">
+        <v>5000000</v>
+      </c>
+      <c r="J39" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="K39" t="n">
+        <v>144425000</v>
+      </c>
+      <c r="L39" t="inlineStr">
+        <is>
+          <t>XAMIDULLAYEV ASADBEK SHERXON O'G'LI</t>
+        </is>
+      </c>
+      <c r="M39" t="inlineStr">
+        <is>
+          <t>AC2489461</t>
+        </is>
+      </c>
+      <c r="N39" t="inlineStr">
+        <is>
+          <t>51711036060037</t>
+        </is>
+      </c>
+      <c r="O39" t="inlineStr">
+        <is>
+          <t>SAMARQAND VILOYATI KATTAQO'RG'ON TUMANI IIB</t>
+        </is>
+      </c>
+      <c r="P39" t="inlineStr">
+        <is>
+          <t>SAMARQAND VILOYATI KATTAQO'RG'ON TUMANI KATTA KO'RPA KO'CHASI 2-UY</t>
+        </is>
+      </c>
+      <c r="Q39" t="inlineStr">
+        <is>
+          <t>+998 97 727 36 42</t>
+        </is>
+      </c>
+      <c r="R39" t="inlineStr">
+        <is>
+          <t>NILUFAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>2025-05-13</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>Блок-1,1</t>
+        </is>
+      </c>
+      <c r="D40" t="n">
+        <v>3</v>
+      </c>
+      <c r="E40" t="n">
+        <v>57</v>
+      </c>
+      <c r="F40" t="n">
+        <v>1</v>
+      </c>
+      <c r="G40" t="n">
+        <v>34.66</v>
+      </c>
+      <c r="H40" t="n">
+        <v>173300000</v>
+      </c>
+      <c r="I40" t="n">
+        <v>5000000</v>
+      </c>
+      <c r="J40" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="K40" t="n">
+        <v>86650000</v>
+      </c>
+      <c r="L40" t="inlineStr">
+        <is>
+          <t>REJEPOVA  AYNUR KAZAKBAYEVNA</t>
+        </is>
+      </c>
+      <c r="M40" t="inlineStr">
+        <is>
+          <t>AD4423278</t>
+        </is>
+      </c>
+      <c r="N40" t="inlineStr">
+        <is>
+          <t>42306823470092</t>
+        </is>
+      </c>
+      <c r="O40" t="inlineStr">
+        <is>
+          <t>TOSHKENT VILOYATI CHIRCHIQ SHAHAR IIB</t>
+        </is>
+      </c>
+      <c r="P40" t="inlineStr">
+        <is>
+          <t>TOSHKENT VILOYATI CHIRCHIQ SHAHAR AMIR TEMUR KOCHSSI  9 UY 28 XONADON</t>
+        </is>
+      </c>
+      <c r="Q40" t="inlineStr">
+        <is>
+          <t>+998994034361</t>
+        </is>
+      </c>
+      <c r="R40" t="inlineStr">
+        <is>
+          <t>AZIZ</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/static/Жилые_Комплексы/ЖК_Бахор/contract_registry.xlsx
+++ b/static/Жилые_Комплексы/ЖК_Бахор/contract_registry.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R40"/>
+  <dimension ref="A1:R54"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3481,24 +3481,24 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>41</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>2025-05-13</t>
+          <t>2025-05-14</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Блок-1,1</t>
+          <t>Блок 1,2</t>
         </is>
       </c>
       <c r="D40" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E40" t="n">
-        <v>57</v>
+        <v>137</v>
       </c>
       <c r="F40" t="n">
         <v>1</v>
@@ -3514,43 +3514,1135 @@
       </c>
       <c r="J40" t="inlineStr">
         <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="K40" t="n">
+        <v>51990000</v>
+      </c>
+      <c r="L40" t="inlineStr">
+        <is>
+          <t>XODJAYEVA FERUZA SAYDULLAYEVNA</t>
+        </is>
+      </c>
+      <c r="M40" t="inlineStr">
+        <is>
+          <t>AD7157367</t>
+        </is>
+      </c>
+      <c r="N40" t="inlineStr">
+        <is>
+          <t>41211703930016</t>
+        </is>
+      </c>
+      <c r="O40" t="inlineStr">
+        <is>
+          <t>IIV 27419</t>
+        </is>
+      </c>
+      <c r="P40" t="inlineStr">
+        <is>
+          <t>TOSHKENT VILOYATI CHIRCHIQ SHAHAR 9-KICHIK NOHIYA 25A-UY 16-XONADON</t>
+        </is>
+      </c>
+      <c r="Q40" t="inlineStr">
+        <is>
+          <t>+998 90 011 18 54</t>
+        </is>
+      </c>
+      <c r="R40" t="inlineStr">
+        <is>
+          <t>DILFUZA</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>42</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>2025-05-14</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>Блок 3,1</t>
+        </is>
+      </c>
+      <c r="D41" t="n">
+        <v>5</v>
+      </c>
+      <c r="E41" t="n">
+        <v>244</v>
+      </c>
+      <c r="F41" t="n">
+        <v>2</v>
+      </c>
+      <c r="G41" t="n">
+        <v>44.28</v>
+      </c>
+      <c r="H41" t="n">
+        <v>212544000</v>
+      </c>
+      <c r="I41" t="n">
+        <v>4800000</v>
+      </c>
+      <c r="J41" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="K41" t="n">
+        <v>63763200</v>
+      </c>
+      <c r="L41" t="inlineStr">
+        <is>
+          <t>MANAPOV MURODJON DILSHOD O`G`LI</t>
+        </is>
+      </c>
+      <c r="M41" t="inlineStr">
+        <is>
+          <t>AB0744993</t>
+        </is>
+      </c>
+      <c r="N41" t="inlineStr">
+        <is>
+          <t>32005930470081</t>
+        </is>
+      </c>
+      <c r="O41" t="inlineStr">
+        <is>
+          <t>TOSHKENT VILOYATI CHIRCHIQ SHAHAR IIB</t>
+        </is>
+      </c>
+      <c r="P41" t="inlineStr">
+        <is>
+          <t>CHIRCHIQ SHAHAR G`ALABA M.F.Y G`ALABA KO`CHASI 17-UY 33-XONADON</t>
+        </is>
+      </c>
+      <c r="Q41" t="inlineStr">
+        <is>
+          <t xml:space="preserve">+998 95 647-70-07 </t>
+        </is>
+      </c>
+      <c r="R41" t="inlineStr">
+        <is>
+          <t>DILFUZA</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>43</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>2025-05-15</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>Блок-1</t>
+        </is>
+      </c>
+      <c r="D42" t="n">
+        <v>5</v>
+      </c>
+      <c r="E42" t="n">
+        <v>39</v>
+      </c>
+      <c r="F42" t="n">
+        <v>1</v>
+      </c>
+      <c r="G42" t="n">
+        <v>47.91</v>
+      </c>
+      <c r="H42" t="n">
+        <v>229968000</v>
+      </c>
+      <c r="I42" t="n">
+        <v>4800000</v>
+      </c>
+      <c r="J42" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="K42" t="n">
+        <v>68990400</v>
+      </c>
+      <c r="L42" t="inlineStr">
+        <is>
+          <t>RUSTAMKULOV DILSHOD MANAPOVICH</t>
+        </is>
+      </c>
+      <c r="M42" t="inlineStr">
+        <is>
+          <t>AD6024587</t>
+        </is>
+      </c>
+      <c r="N42" t="inlineStr">
+        <is>
+          <t>33001696860048</t>
+        </is>
+      </c>
+      <c r="O42" t="inlineStr">
+        <is>
+          <t>IIV 27419</t>
+        </is>
+      </c>
+      <c r="P42" t="inlineStr">
+        <is>
+          <t>TOSHKENT VILOYATI CHIRCHIQ SHAHAR G'ALABA MFY G'ALABA KO'CHASI 14-UY 33-XONADON</t>
+        </is>
+      </c>
+      <c r="Q42" t="inlineStr">
+        <is>
+          <t>+998 99 000 25 60</t>
+        </is>
+      </c>
+      <c r="R42" t="inlineStr">
+        <is>
+          <t>NILUFAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>44</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>2025-05-15</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>Блок-1</t>
+        </is>
+      </c>
+      <c r="D43" t="n">
+        <v>5</v>
+      </c>
+      <c r="E43" t="n">
+        <v>38</v>
+      </c>
+      <c r="F43" t="n">
+        <v>1</v>
+      </c>
+      <c r="G43" t="n">
+        <v>47.91</v>
+      </c>
+      <c r="H43" t="n">
+        <v>229968000</v>
+      </c>
+      <c r="I43" t="n">
+        <v>4800000</v>
+      </c>
+      <c r="J43" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="K43" t="n">
+        <v>68990400</v>
+      </c>
+      <c r="L43" t="inlineStr">
+        <is>
+          <t>RUSTAMKULOV DILSHOD MANAPOVICH</t>
+        </is>
+      </c>
+      <c r="M43" t="inlineStr">
+        <is>
+          <t>AD6024587</t>
+        </is>
+      </c>
+      <c r="N43" t="inlineStr">
+        <is>
+          <t>33001696860048</t>
+        </is>
+      </c>
+      <c r="O43" t="inlineStr">
+        <is>
+          <t>IIV 27419</t>
+        </is>
+      </c>
+      <c r="P43" t="inlineStr">
+        <is>
+          <t>TOSHKENT VILOYATI CHIRCHIQ SHAHAR G'ALABA MFY G'ALABA KO'CHASI 14-UY 33-XONADON</t>
+        </is>
+      </c>
+      <c r="Q43" t="inlineStr">
+        <is>
+          <t>+998 99 000 25 60</t>
+        </is>
+      </c>
+      <c r="R43" t="inlineStr">
+        <is>
+          <t>NILUFAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>45</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>2025-05-16</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>Блок 3,2</t>
+        </is>
+      </c>
+      <c r="D44" t="n">
+        <v>5</v>
+      </c>
+      <c r="E44" t="n">
+        <v>274</v>
+      </c>
+      <c r="F44" t="n">
+        <v>2</v>
+      </c>
+      <c r="G44" t="n">
+        <v>44.28</v>
+      </c>
+      <c r="H44" t="n">
+        <v>212544000</v>
+      </c>
+      <c r="I44" t="n">
+        <v>4800000</v>
+      </c>
+      <c r="J44" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="K44" t="n">
+        <v>63763200</v>
+      </c>
+      <c r="L44" t="inlineStr">
+        <is>
+          <t>ATEMKULOV MURAT ORINBASAROVICH</t>
+        </is>
+      </c>
+      <c r="M44" t="inlineStr">
+        <is>
+          <t>AC2593883</t>
+        </is>
+      </c>
+      <c r="N44" t="inlineStr">
+        <is>
+          <t>32903920500010</t>
+        </is>
+      </c>
+      <c r="O44" t="inlineStr">
+        <is>
+          <t>TOSHKENT VILOYATI BO`STONLIQ TUMANI</t>
+        </is>
+      </c>
+      <c r="P44" t="inlineStr">
+        <is>
+          <t>TOSHKENT VILOYATI BO`STONLIQ TUMANI OZODBOSH BERUNIY KO`CHASI 56</t>
+        </is>
+      </c>
+      <c r="Q44" t="inlineStr">
+        <is>
+          <t>+998 99 400 20 01</t>
+        </is>
+      </c>
+      <c r="R44" t="inlineStr">
+        <is>
+          <t>DILFUZA</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>46</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>2025-05-18</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>Блок-1,1</t>
+        </is>
+      </c>
+      <c r="D45" t="n">
+        <v>4</v>
+      </c>
+      <c r="E45" t="n">
+        <v>68</v>
+      </c>
+      <c r="F45" t="n">
+        <v>2</v>
+      </c>
+      <c r="G45" t="n">
+        <v>50.34</v>
+      </c>
+      <c r="H45" t="n">
+        <v>221496000</v>
+      </c>
+      <c r="I45" t="n">
+        <v>4400000</v>
+      </c>
+      <c r="J45" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="K45" t="n">
+        <v>221496000</v>
+      </c>
+      <c r="L45" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ABDUVALIYEV SANJAR SODIQOVICH </t>
+        </is>
+      </c>
+      <c r="M45" t="inlineStr">
+        <is>
+          <t>AD9447749</t>
+        </is>
+      </c>
+      <c r="N45" t="inlineStr">
+        <is>
+          <t>32110840510041</t>
+        </is>
+      </c>
+      <c r="O45" t="inlineStr">
+        <is>
+          <t>IIV 27419 18.11.2024</t>
+        </is>
+      </c>
+      <c r="P45" t="inlineStr">
+        <is>
+          <t>TOSHKENT VILOYATI CHIRCHIQ SHAHAR SEMURG MFY 8 KICHIK NOXYA 8 UY 73 XONADON</t>
+        </is>
+      </c>
+      <c r="Q45" t="inlineStr">
+        <is>
+          <t>+998900044109</t>
+        </is>
+      </c>
+      <c r="R45" t="inlineStr">
+        <is>
+          <t>Фатима</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>47</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>2025-05-18</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>Блок 1,2</t>
+        </is>
+      </c>
+      <c r="D46" t="n">
+        <v>4</v>
+      </c>
+      <c r="E46" t="n">
+        <v>133</v>
+      </c>
+      <c r="F46" t="n">
+        <v>1</v>
+      </c>
+      <c r="G46" t="n">
+        <v>34.66</v>
+      </c>
+      <c r="H46" t="n">
+        <v>173300000</v>
+      </c>
+      <c r="I46" t="n">
+        <v>5000000</v>
+      </c>
+      <c r="J46" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="K46" t="n">
+        <v>51990000</v>
+      </c>
+      <c r="L46" t="inlineStr">
+        <is>
+          <t>NAVROZOV SARVAR ALISHEROVICH</t>
+        </is>
+      </c>
+      <c r="M46" t="inlineStr">
+        <is>
+          <t>AD3743500</t>
+        </is>
+      </c>
+      <c r="N46" t="inlineStr">
+        <is>
+          <t>31607890191388</t>
+        </is>
+      </c>
+      <c r="O46" t="inlineStr">
+        <is>
+          <t>23.06.2023</t>
+        </is>
+      </c>
+      <c r="P46" t="inlineStr">
+        <is>
+          <t>TOSHKENT SHAHAR YUNUSOBOD TUMANI CHINOBOD KOCHASI 8 UY 51 XONADON</t>
+        </is>
+      </c>
+      <c r="Q46" t="inlineStr">
+        <is>
+          <t>+998909003004 +998339005009</t>
+        </is>
+      </c>
+      <c r="R46" t="inlineStr">
+        <is>
+          <t>AZIZ</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>49</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>2025-05-20</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>Блок-1,1</t>
+        </is>
+      </c>
+      <c r="D47" t="n">
+        <v>2</v>
+      </c>
+      <c r="E47" t="n">
+        <v>56</v>
+      </c>
+      <c r="F47" t="n">
+        <v>1</v>
+      </c>
+      <c r="G47" t="n">
+        <v>34.66</v>
+      </c>
+      <c r="H47" t="n">
+        <v>187164000</v>
+      </c>
+      <c r="I47" t="n">
+        <v>5400000</v>
+      </c>
+      <c r="J47" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="K47" t="n">
+        <v>56149200</v>
+      </c>
+      <c r="L47" t="inlineStr">
+        <is>
+          <t>XURRAMOV NURBEK SHOMURODOVICH</t>
+        </is>
+      </c>
+      <c r="M47" t="inlineStr">
+        <is>
+          <t>AD1546754</t>
+        </is>
+      </c>
+      <c r="N47" t="inlineStr">
+        <is>
+          <t>30404842600050</t>
+        </is>
+      </c>
+      <c r="O47" t="inlineStr">
+        <is>
+          <t>IIV  14.07.2022</t>
+        </is>
+      </c>
+      <c r="P47" t="inlineStr">
+        <is>
+          <t>TOSHKENT SHAHAR MIRZO ULUGBEK TUMANI ZAKOVAT MFY FAROVON HAYOT2 KUCHASI 1A UY</t>
+        </is>
+      </c>
+      <c r="Q47" t="inlineStr">
+        <is>
+          <t>+998882021984</t>
+        </is>
+      </c>
+      <c r="R47" t="inlineStr">
+        <is>
+          <t>AZIZ</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
           <t>50</t>
         </is>
       </c>
-      <c r="K40" t="n">
-        <v>86650000</v>
-      </c>
-      <c r="L40" t="inlineStr">
-        <is>
-          <t>REJEPOVA  AYNUR KAZAKBAYEVNA</t>
-        </is>
-      </c>
-      <c r="M40" t="inlineStr">
-        <is>
-          <t>AD4423278</t>
-        </is>
-      </c>
-      <c r="N40" t="inlineStr">
-        <is>
-          <t>42306823470092</t>
-        </is>
-      </c>
-      <c r="O40" t="inlineStr">
-        <is>
-          <t>TOSHKENT VILOYATI CHIRCHIQ SHAHAR IIB</t>
-        </is>
-      </c>
-      <c r="P40" t="inlineStr">
-        <is>
-          <t>TOSHKENT VILOYATI CHIRCHIQ SHAHAR AMIR TEMUR KOCHSSI  9 UY 28 XONADON</t>
-        </is>
-      </c>
-      <c r="Q40" t="inlineStr">
-        <is>
-          <t>+998994034361</t>
-        </is>
-      </c>
-      <c r="R40" t="inlineStr">
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>2025-05-21</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>Блок 3,1</t>
+        </is>
+      </c>
+      <c r="D48" t="n">
+        <v>4</v>
+      </c>
+      <c r="E48" t="n">
+        <v>240</v>
+      </c>
+      <c r="F48" t="n">
+        <v>2</v>
+      </c>
+      <c r="G48" t="n">
+        <v>46.67</v>
+      </c>
+      <c r="H48" t="n">
+        <v>233350000</v>
+      </c>
+      <c r="I48" t="n">
+        <v>5000000</v>
+      </c>
+      <c r="J48" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="K48" t="n">
+        <v>70005000</v>
+      </c>
+      <c r="L48" t="inlineStr">
+        <is>
+          <t>TURGUNOV SHOXOBIDDIN XALDAROVICH</t>
+        </is>
+      </c>
+      <c r="M48" t="inlineStr">
+        <is>
+          <t>AD5175994</t>
+        </is>
+      </c>
+      <c r="N48" t="inlineStr">
+        <is>
+          <t>31506900231893</t>
+        </is>
+      </c>
+      <c r="O48" t="inlineStr">
+        <is>
+          <t>IIV26284 20.11.2023</t>
+        </is>
+      </c>
+      <c r="P48" t="inlineStr">
+        <is>
+          <t>TOSHKENT SHAHAR SERGELI TUMANI XONOBOD MFY YAKUBOV KUCHASI 65 UY</t>
+        </is>
+      </c>
+      <c r="Q48" t="inlineStr">
+        <is>
+          <t>+998998128448</t>
+        </is>
+      </c>
+      <c r="R48" t="inlineStr">
+        <is>
+          <t>Aziz</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>51</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>2025-05-21</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>Блок 3,1</t>
+        </is>
+      </c>
+      <c r="D49" t="n">
+        <v>3</v>
+      </c>
+      <c r="E49" t="n">
+        <v>234</v>
+      </c>
+      <c r="F49" t="n">
+        <v>2</v>
+      </c>
+      <c r="G49" t="n">
+        <v>46.67</v>
+      </c>
+      <c r="H49" t="n">
+        <v>242684000</v>
+      </c>
+      <c r="I49" t="n">
+        <v>5200000</v>
+      </c>
+      <c r="J49" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="K49" t="n">
+        <v>72805200</v>
+      </c>
+      <c r="L49" t="inlineStr">
+        <is>
+          <t>TURAEV JASURXON RAVSHANXONOVI</t>
+        </is>
+      </c>
+      <c r="M49" t="inlineStr">
+        <is>
+          <t>AD2697466</t>
+        </is>
+      </c>
+      <c r="N49" t="inlineStr">
+        <is>
+          <t>31903840230025</t>
+        </is>
+      </c>
+      <c r="O49" t="inlineStr">
+        <is>
+          <t xml:space="preserve">IIV 60006 28.02.2023 </t>
+        </is>
+      </c>
+      <c r="P49" t="inlineStr">
+        <is>
+          <t>TOSHKENT SHAHAR YANGI HAYOT TUMANI XUMO MFY SHOKIR ARIQ G 64 KUCHASI 113 UY</t>
+        </is>
+      </c>
+      <c r="Q49" t="inlineStr">
+        <is>
+          <t>+998909080503</t>
+        </is>
+      </c>
+      <c r="R49" t="inlineStr">
+        <is>
+          <t>Aziz</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>2025-05-22</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>Блок-1,1</t>
+        </is>
+      </c>
+      <c r="D50" t="n">
+        <v>3</v>
+      </c>
+      <c r="E50" t="n">
+        <v>60</v>
+      </c>
+      <c r="F50" t="n">
+        <v>2</v>
+      </c>
+      <c r="G50" t="n">
+        <v>50.34</v>
+      </c>
+      <c r="H50" t="n">
+        <v>231564000</v>
+      </c>
+      <c r="I50" t="n">
+        <v>4600000</v>
+      </c>
+      <c r="J50" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="K50" t="n">
+        <v>231564000</v>
+      </c>
+      <c r="L50" t="inlineStr">
+        <is>
+          <t>YUSUPOVA NAFISA  AXMADJANOVNA</t>
+        </is>
+      </c>
+      <c r="M50" t="inlineStr">
+        <is>
+          <t>AB3354407</t>
+        </is>
+      </c>
+      <c r="N50" t="inlineStr">
+        <is>
+          <t>309242003836860031</t>
+        </is>
+      </c>
+      <c r="O50" t="inlineStr">
+        <is>
+          <t>TOSHKENT  VILOYATI CHIRCHIQ SHAHAR IIB 10.03.2016</t>
+        </is>
+      </c>
+      <c r="P50" t="inlineStr">
+        <is>
+          <t>TOSHKENT  VILOYATI CHIRCHIQ SHAHAR 8 KICHIK NOXYA 10 UY 38 XONADON</t>
+        </is>
+      </c>
+      <c r="Q50" t="inlineStr">
+        <is>
+          <t>+998880133833</t>
+        </is>
+      </c>
+      <c r="R50" t="inlineStr">
+        <is>
+          <t>Aziz</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>53</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>2025-05-22</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>Блок 1,2</t>
+        </is>
+      </c>
+      <c r="D51" t="n">
+        <v>4</v>
+      </c>
+      <c r="E51" t="n">
+        <v>140</v>
+      </c>
+      <c r="F51" t="n">
+        <v>1</v>
+      </c>
+      <c r="G51" t="n">
+        <v>34.66</v>
+      </c>
+      <c r="H51" t="n">
+        <v>152504000</v>
+      </c>
+      <c r="I51" t="n">
+        <v>4400000</v>
+      </c>
+      <c r="J51" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="K51" t="n">
+        <v>152504000</v>
+      </c>
+      <c r="L51" t="inlineStr">
+        <is>
+          <t>SOBIROV ABDULLA FATXILLA OGLI</t>
+        </is>
+      </c>
+      <c r="M51" t="inlineStr">
+        <is>
+          <t>AC0807821</t>
+        </is>
+      </c>
+      <c r="N51" t="inlineStr">
+        <is>
+          <t>33011940560028</t>
+        </is>
+      </c>
+      <c r="O51" t="inlineStr">
+        <is>
+          <t>TOSHKENT VILOYATI CHIRCHIQ SHAHAR IIB 21.08.2018</t>
+        </is>
+      </c>
+      <c r="P51" t="inlineStr">
+        <is>
+          <t>TOSHKENT VILOYATI CHIRCHIQ 8 KICHIK NOXIYA 36 UY 14 XONADON</t>
+        </is>
+      </c>
+      <c r="Q51" t="inlineStr">
+        <is>
+          <t>+998909099101</t>
+        </is>
+      </c>
+      <c r="R51" t="inlineStr">
+        <is>
+          <t>AZIZ</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>54</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>2025-05-23</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>Блок 3</t>
+        </is>
+      </c>
+      <c r="D52" t="n">
+        <v>5</v>
+      </c>
+      <c r="E52" t="n">
+        <v>214</v>
+      </c>
+      <c r="F52" t="n">
+        <v>2</v>
+      </c>
+      <c r="G52" t="n">
+        <v>44.28</v>
+      </c>
+      <c r="H52" t="n">
+        <v>194832000</v>
+      </c>
+      <c r="I52" t="n">
+        <v>4400000</v>
+      </c>
+      <c r="J52" t="inlineStr">
+        <is>
+          <t>70</t>
+        </is>
+      </c>
+      <c r="K52" t="n">
+        <v>136382400</v>
+      </c>
+      <c r="L52" t="inlineStr">
+        <is>
+          <t xml:space="preserve">BABADJANOVA ANGELA BATIRALIYEVNA </t>
+        </is>
+      </c>
+      <c r="M52" t="inlineStr">
+        <is>
+          <t>AD4481939</t>
+        </is>
+      </c>
+      <c r="N52" t="inlineStr">
+        <is>
+          <t>40511880470048</t>
+        </is>
+      </c>
+      <c r="O52" t="inlineStr">
+        <is>
+          <t>IIV 60120 04.09.2023</t>
+        </is>
+      </c>
+      <c r="P52" t="inlineStr">
+        <is>
+          <t>TOSHKENT VILOYATI CHIRCHIQ SHAHAR GULZOR MFY SUGDIYONA KUCHASI 8 UY</t>
+        </is>
+      </c>
+      <c r="Q52" t="inlineStr">
+        <is>
+          <t>+998936169555</t>
+        </is>
+      </c>
+      <c r="R52" t="inlineStr">
+        <is>
+          <t>AZIZ</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>55</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>2025-05-23</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>Блок-1</t>
+        </is>
+      </c>
+      <c r="D53" t="n">
+        <v>2</v>
+      </c>
+      <c r="E53" t="n">
+        <v>12</v>
+      </c>
+      <c r="F53" t="n">
+        <v>2</v>
+      </c>
+      <c r="G53" t="n">
+        <v>50.34</v>
+      </c>
+      <c r="H53" t="n">
+        <v>271836000</v>
+      </c>
+      <c r="I53" t="n">
+        <v>5400000</v>
+      </c>
+      <c r="J53" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="K53" t="n">
+        <v>81550800</v>
+      </c>
+      <c r="L53" t="inlineStr">
+        <is>
+          <t>SODIKOV SARDOR TOSHKUVATOVICH</t>
+        </is>
+      </c>
+      <c r="M53" t="inlineStr">
+        <is>
+          <t>AB0229238</t>
+        </is>
+      </c>
+      <c r="N53" t="inlineStr">
+        <is>
+          <t>32706862420013</t>
+        </is>
+      </c>
+      <c r="O53" t="inlineStr">
+        <is>
+          <t>NAVOIY VILOYATI KARMANA TUMANI IIB</t>
+        </is>
+      </c>
+      <c r="P53" t="inlineStr">
+        <is>
+          <t>TOSHKENT VILOYATI CHIRCHIQ SHAHAR XUMO MFY 8 KICHIK NOXYA 35 UY 31 XONADON</t>
+        </is>
+      </c>
+      <c r="Q53" t="inlineStr">
+        <is>
+          <t>+998936634497</t>
+        </is>
+      </c>
+      <c r="R53" t="inlineStr">
+        <is>
+          <t>AZIZ</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>56</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>2025-05-23</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>Блок 3</t>
+        </is>
+      </c>
+      <c r="D54" t="n">
+        <v>4</v>
+      </c>
+      <c r="E54" t="n">
+        <v>207</v>
+      </c>
+      <c r="F54" t="n">
+        <v>3</v>
+      </c>
+      <c r="G54" t="n">
+        <v>55.67</v>
+      </c>
+      <c r="H54" t="n">
+        <v>278350000</v>
+      </c>
+      <c r="I54" t="n">
+        <v>5000000</v>
+      </c>
+      <c r="J54" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="K54" t="n">
+        <v>83505000</v>
+      </c>
+      <c r="L54" t="inlineStr">
+        <is>
+          <t>ABDUXOLIQOV FARRUX FARHOD OGLI</t>
+        </is>
+      </c>
+      <c r="M54" t="inlineStr">
+        <is>
+          <t>AD6688630</t>
+        </is>
+      </c>
+      <c r="N54" t="inlineStr">
+        <is>
+          <t>32210900840063</t>
+        </is>
+      </c>
+      <c r="O54" t="inlineStr">
+        <is>
+          <t>IIV 27419 02.04.2024</t>
+        </is>
+      </c>
+      <c r="P54" t="inlineStr">
+        <is>
+          <t>TOSHKENT VILOYATI CHIRCHIQ SHAHAR ADOLAT MFY 9 KICHIK NOXYA 36 UY 17 XONADON</t>
+        </is>
+      </c>
+      <c r="Q54" t="inlineStr">
+        <is>
+          <t>+998917777229</t>
+        </is>
+      </c>
+      <c r="R54" t="inlineStr">
         <is>
           <t>AZIZ</t>
         </is>

--- a/static/Жилые_Комплексы/ЖК_Бахор/contract_registry.xlsx
+++ b/static/Жилые_Комплексы/ЖК_Бахор/contract_registry.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R54"/>
+  <dimension ref="A1:R64"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4648,6 +4648,786 @@
         </is>
       </c>
     </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>57</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>2025-05-24</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>Блок-1,1</t>
+        </is>
+      </c>
+      <c r="D55" t="n">
+        <v>3</v>
+      </c>
+      <c r="E55" t="n">
+        <v>61</v>
+      </c>
+      <c r="F55" t="n">
+        <v>1</v>
+      </c>
+      <c r="G55" t="n">
+        <v>34.66</v>
+      </c>
+      <c r="H55" t="n">
+        <v>173300000</v>
+      </c>
+      <c r="I55" t="n">
+        <v>5000000</v>
+      </c>
+      <c r="J55" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="K55" t="n">
+        <v>86650000</v>
+      </c>
+      <c r="L55" t="inlineStr">
+        <is>
+          <t>BOBODUSTOV SHOHZOD ZOKIR O`G`LI</t>
+        </is>
+      </c>
+      <c r="M55" t="inlineStr">
+        <is>
+          <t>AB3768763</t>
+        </is>
+      </c>
+      <c r="N55" t="inlineStr">
+        <is>
+          <t>30110985640034</t>
+        </is>
+      </c>
+      <c r="O55" t="inlineStr">
+        <is>
+          <t>QASHQADARYO VILOYATI CHIROQCHI TIIB</t>
+        </is>
+      </c>
+      <c r="P55" t="inlineStr">
+        <is>
+          <t>QASHQADARYO VILOYATI CHIROQCHI TUMANI BESHCHASHMA QMB PAST UYSHUN 666-XONADON</t>
+        </is>
+      </c>
+      <c r="Q55" t="inlineStr">
+        <is>
+          <t>+998 93 958-89-98</t>
+        </is>
+      </c>
+      <c r="R55" t="inlineStr">
+        <is>
+          <t>DILFUZA</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>58</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>2025-05-25</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>Блок 3,1</t>
+        </is>
+      </c>
+      <c r="D56" t="n">
+        <v>4</v>
+      </c>
+      <c r="E56" t="n">
+        <v>237</v>
+      </c>
+      <c r="F56" t="n">
+        <v>3</v>
+      </c>
+      <c r="G56" t="n">
+        <v>55.67</v>
+      </c>
+      <c r="H56" t="n">
+        <v>267216000</v>
+      </c>
+      <c r="I56" t="n">
+        <v>4800000</v>
+      </c>
+      <c r="J56" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="K56" t="n">
+        <v>133608000</v>
+      </c>
+      <c r="L56" t="inlineStr">
+        <is>
+          <t>NORMATOVA KAMOLA YULDASHEVNA</t>
+        </is>
+      </c>
+      <c r="M56" t="inlineStr">
+        <is>
+          <t>AD7797320</t>
+        </is>
+      </c>
+      <c r="N56" t="inlineStr">
+        <is>
+          <t>41008891520022</t>
+        </is>
+      </c>
+      <c r="O56" t="inlineStr">
+        <is>
+          <t>IIV 26296 09.072024</t>
+        </is>
+      </c>
+      <c r="P56" t="inlineStr">
+        <is>
+          <t>TOSHKENT SHAHAR MIRZO ULUGBEK TUMANI  FERUZA KUCHASI 51 UY 39 XONADON</t>
+        </is>
+      </c>
+      <c r="Q56" t="inlineStr">
+        <is>
+          <t>+998970021416</t>
+        </is>
+      </c>
+      <c r="R56" t="inlineStr">
+        <is>
+          <t>Руководство</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>59</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>2025-05-26</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>Блок 3</t>
+        </is>
+      </c>
+      <c r="D57" t="n">
+        <v>4</v>
+      </c>
+      <c r="E57" t="n">
+        <v>208</v>
+      </c>
+      <c r="F57" t="n">
+        <v>1</v>
+      </c>
+      <c r="G57" t="n">
+        <v>44.28</v>
+      </c>
+      <c r="H57" t="n">
+        <v>212544000</v>
+      </c>
+      <c r="I57" t="n">
+        <v>4800000</v>
+      </c>
+      <c r="J57" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="K57" t="n">
+        <v>106272000</v>
+      </c>
+      <c r="L57" t="inlineStr">
+        <is>
+          <t>FAYZULLAYEV HAYOT DILMURODOVICH</t>
+        </is>
+      </c>
+      <c r="M57" t="inlineStr">
+        <is>
+          <t>AD5839429</t>
+        </is>
+      </c>
+      <c r="N57" t="inlineStr">
+        <is>
+          <t>31612930470051</t>
+        </is>
+      </c>
+      <c r="O57" t="inlineStr">
+        <is>
+          <t>IIV 27419 20.01.2024</t>
+        </is>
+      </c>
+      <c r="P57" t="inlineStr">
+        <is>
+          <t>TOSHKENT  VILOYATI CHIRCHIQ SHAHAR GALABA KUCHASI 16 UY 31 XONADON</t>
+        </is>
+      </c>
+      <c r="Q57" t="inlineStr">
+        <is>
+          <t>917756969</t>
+        </is>
+      </c>
+      <c r="R57" t="inlineStr">
+        <is>
+          <t>РУКОВОДССТВО</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>60</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>2025-05-26</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>Блок-1</t>
+        </is>
+      </c>
+      <c r="D58" t="n">
+        <v>1</v>
+      </c>
+      <c r="E58" t="n">
+        <v>4</v>
+      </c>
+      <c r="F58" t="n">
+        <v>1</v>
+      </c>
+      <c r="G58" t="n">
+        <v>47.94</v>
+      </c>
+      <c r="H58" t="n">
+        <v>249288000</v>
+      </c>
+      <c r="I58" t="n">
+        <v>5200000</v>
+      </c>
+      <c r="J58" t="inlineStr">
+        <is>
+          <t>70</t>
+        </is>
+      </c>
+      <c r="K58" t="n">
+        <v>174501600</v>
+      </c>
+      <c r="L58" t="inlineStr">
+        <is>
+          <t>KARGAPOLOVNA ELENA PETROVNA</t>
+        </is>
+      </c>
+      <c r="M58" t="inlineStr">
+        <is>
+          <t>AD8083373</t>
+        </is>
+      </c>
+      <c r="N58" t="inlineStr">
+        <is>
+          <t>40907936860013</t>
+        </is>
+      </c>
+      <c r="O58" t="inlineStr">
+        <is>
+          <t>IIV 27419 01.08.2024</t>
+        </is>
+      </c>
+      <c r="P58" t="inlineStr">
+        <is>
+          <t>TOSHKENT VILOYATI CHIRCHIQ SHAHAR  OKRUJNAYA KUCHASI 33A XONADON</t>
+        </is>
+      </c>
+      <c r="Q58" t="inlineStr">
+        <is>
+          <t>+998998288286</t>
+        </is>
+      </c>
+      <c r="R58" t="inlineStr">
+        <is>
+          <t>РУКОВОДССТВО</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>61</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>2025-05-27</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>Блок 1,2</t>
+        </is>
+      </c>
+      <c r="D59" t="n">
+        <v>3</v>
+      </c>
+      <c r="E59" t="n">
+        <v>128</v>
+      </c>
+      <c r="F59" t="n">
+        <v>2</v>
+      </c>
+      <c r="G59" t="n">
+        <v>50.34</v>
+      </c>
+      <c r="H59" t="n">
+        <v>251700000</v>
+      </c>
+      <c r="I59" t="n">
+        <v>5000000</v>
+      </c>
+      <c r="J59" t="inlineStr">
+        <is>
+          <t>70</t>
+        </is>
+      </c>
+      <c r="K59" t="n">
+        <v>176190000</v>
+      </c>
+      <c r="L59" t="inlineStr">
+        <is>
+          <t>XAYTBAYEVA FARIDA TOSHTEMIROVNA</t>
+        </is>
+      </c>
+      <c r="M59" t="inlineStr">
+        <is>
+          <t>AD1665555</t>
+        </is>
+      </c>
+      <c r="N59" t="inlineStr">
+        <is>
+          <t>40110876860018</t>
+        </is>
+      </c>
+      <c r="O59" t="inlineStr">
+        <is>
+          <t>IIV 27419 17.08.2022</t>
+        </is>
+      </c>
+      <c r="P59" t="inlineStr">
+        <is>
+          <t>TOSHKENT VILOYATI CHIRCHIQ SHAHAR 8 KICHIK NOXYA 2 UY 75 XONADON</t>
+        </is>
+      </c>
+      <c r="Q59" t="inlineStr">
+        <is>
+          <t>+998917763438</t>
+        </is>
+      </c>
+      <c r="R59" t="inlineStr">
+        <is>
+          <t>MIKHAIL</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>62</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>2025-05-30</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>Блок-1,1</t>
+        </is>
+      </c>
+      <c r="D60" t="n">
+        <v>2</v>
+      </c>
+      <c r="E60" t="n">
+        <v>53</v>
+      </c>
+      <c r="F60" t="n">
+        <v>1</v>
+      </c>
+      <c r="G60" t="n">
+        <v>34.66</v>
+      </c>
+      <c r="H60" t="n">
+        <v>194096000</v>
+      </c>
+      <c r="I60" t="n">
+        <v>5600000</v>
+      </c>
+      <c r="J60" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="K60" t="n">
+        <v>58228800</v>
+      </c>
+      <c r="L60" t="inlineStr">
+        <is>
+          <t>RAXMANOV JAVOHIR AHMAD O'G'LI</t>
+        </is>
+      </c>
+      <c r="M60" t="inlineStr">
+        <is>
+          <t>AB4145338</t>
+        </is>
+      </c>
+      <c r="N60" t="inlineStr">
+        <is>
+          <t>33005975630050</t>
+        </is>
+      </c>
+      <c r="O60" t="inlineStr">
+        <is>
+          <t>10.06.2016 КАМАШИНСКИЙ РОВД, КАШКАДАРЬИНСКОЙ ОБЛАСТИ</t>
+        </is>
+      </c>
+      <c r="P60" t="inlineStr">
+        <is>
+          <t>Qashqadaryo viloyati Qamashi tumani Gʻishtli MFY 102- uy</t>
+        </is>
+      </c>
+      <c r="Q60" t="inlineStr">
+        <is>
+          <t>+998946699007</t>
+        </is>
+      </c>
+      <c r="R60" t="inlineStr">
+        <is>
+          <t>AZIZ</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>64</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>2025-05-31</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>Блок 3,1</t>
+        </is>
+      </c>
+      <c r="D61" t="n">
+        <v>4</v>
+      </c>
+      <c r="E61" t="n">
+        <v>238</v>
+      </c>
+      <c r="F61" t="n">
+        <v>2</v>
+      </c>
+      <c r="G61" t="n">
+        <v>44.28</v>
+      </c>
+      <c r="H61" t="n">
+        <v>221400000</v>
+      </c>
+      <c r="I61" t="n">
+        <v>5000000</v>
+      </c>
+      <c r="J61" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="K61" t="n">
+        <v>110700000</v>
+      </c>
+      <c r="L61" t="inlineStr">
+        <is>
+          <t>MAXMUDOVA GULNUR ABDUMUTAL QIZI</t>
+        </is>
+      </c>
+      <c r="M61" t="inlineStr">
+        <is>
+          <t>AD3854467</t>
+        </is>
+      </c>
+      <c r="N61" t="inlineStr">
+        <is>
+          <t>41810966780046</t>
+        </is>
+      </c>
+      <c r="O61" t="inlineStr">
+        <is>
+          <t>IIV 27248</t>
+        </is>
+      </c>
+      <c r="P61" t="inlineStr">
+        <is>
+          <t>TOSHKENT  VILOYATI  QIBRAY TUMANI ZAFARABOT XFY SHARQ MFY ZAFARABOT GULZOR UY; R/S</t>
+        </is>
+      </c>
+      <c r="Q61" t="inlineStr">
+        <is>
+          <t>+99833-001-18-10</t>
+        </is>
+      </c>
+      <c r="R61" t="inlineStr">
+        <is>
+          <t>NILUFAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>65</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>2025-06-01</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>Блок-1,1</t>
+        </is>
+      </c>
+      <c r="D62" t="n">
+        <v>3</v>
+      </c>
+      <c r="E62" t="n">
+        <v>57</v>
+      </c>
+      <c r="F62" t="n">
+        <v>1</v>
+      </c>
+      <c r="G62" t="n">
+        <v>34.66</v>
+      </c>
+      <c r="H62" t="n">
+        <v>180232000</v>
+      </c>
+      <c r="I62" t="n">
+        <v>5200000</v>
+      </c>
+      <c r="J62" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="K62" t="n">
+        <v>90116000</v>
+      </c>
+      <c r="L62" t="inlineStr">
+        <is>
+          <t>DAVLATBAYEV XASAN DILSHAD OGLI</t>
+        </is>
+      </c>
+      <c r="M62" t="inlineStr">
+        <is>
+          <t>AB6769142</t>
+        </is>
+      </c>
+      <c r="N62" t="inlineStr">
+        <is>
+          <t>52604016860035</t>
+        </is>
+      </c>
+      <c r="O62" t="inlineStr">
+        <is>
+          <t>TOSHKENT VILOYATI CHIRCHIQ SHAHAR IIB 19.05.2017</t>
+        </is>
+      </c>
+      <c r="P62" t="inlineStr">
+        <is>
+          <t>TOSHKENT VILOYATI CHIRCHIQ SHAHAR KIMYOGAR MFY YORKIN KELAJAK KUCHASI 2A UY</t>
+        </is>
+      </c>
+      <c r="Q62" t="inlineStr">
+        <is>
+          <t>+998998024662</t>
+        </is>
+      </c>
+      <c r="R62" t="inlineStr">
+        <is>
+          <t>AZIZ</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>66</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>2025-06-02</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>Блок 3,2</t>
+        </is>
+      </c>
+      <c r="D63" t="n">
+        <v>4</v>
+      </c>
+      <c r="E63" t="n">
+        <v>268</v>
+      </c>
+      <c r="F63" t="n">
+        <v>2</v>
+      </c>
+      <c r="G63" t="n">
+        <v>44.28</v>
+      </c>
+      <c r="H63" t="n">
+        <v>221400000</v>
+      </c>
+      <c r="I63" t="n">
+        <v>5000000</v>
+      </c>
+      <c r="J63" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="K63" t="n">
+        <v>110700000</v>
+      </c>
+      <c r="L63" t="inlineStr">
+        <is>
+          <t>MUSTAFAYEV ABDIMUROD OBULQOSIMOVICH</t>
+        </is>
+      </c>
+      <c r="M63" t="inlineStr">
+        <is>
+          <t>AD 0063132</t>
+        </is>
+      </c>
+      <c r="N63" t="inlineStr">
+        <is>
+          <t>32501848240012</t>
+        </is>
+      </c>
+      <c r="O63" t="inlineStr">
+        <is>
+          <t>IIV 10411</t>
+        </is>
+      </c>
+      <c r="P63" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TOSHKENT SHAXRI YASHNOBOD TUMANI olmas MFY Kunduzsay ul 4tupik 12 uy 231 xonadon </t>
+        </is>
+      </c>
+      <c r="Q63" t="inlineStr">
+        <is>
+          <t>+998946408017</t>
+        </is>
+      </c>
+      <c r="R63" t="inlineStr">
+        <is>
+          <t>NILUFAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>67</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>2025-06-05</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>Блок-1</t>
+        </is>
+      </c>
+      <c r="D64" t="n">
+        <v>5</v>
+      </c>
+      <c r="E64" t="n">
+        <v>36</v>
+      </c>
+      <c r="F64" t="n">
+        <v>2</v>
+      </c>
+      <c r="G64" t="n">
+        <v>50.34</v>
+      </c>
+      <c r="H64" t="n">
+        <v>251700000</v>
+      </c>
+      <c r="I64" t="n">
+        <v>5000000</v>
+      </c>
+      <c r="J64" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="K64" t="n">
+        <v>75510000</v>
+      </c>
+      <c r="L64" t="inlineStr">
+        <is>
+          <t>XUDAYBERGANOVA ONAPOSHSHA YULDASHOVNA</t>
+        </is>
+      </c>
+      <c r="M64" t="inlineStr">
+        <is>
+          <t>AB34993983</t>
+        </is>
+      </c>
+      <c r="N64" t="inlineStr">
+        <is>
+          <t>41103823070070</t>
+        </is>
+      </c>
+      <c r="O64" t="inlineStr">
+        <is>
+          <t>XORAZM VILOYATI BOG'OT TUMANI IIB</t>
+        </is>
+      </c>
+      <c r="P64" t="inlineStr">
+        <is>
+          <t>TOSHKENT VILOYATI BO'STONLIQ TUMANI G'AZALKENT SHAHRI YANGI CHORBOG' MAHALLA BESH TOSH KO'CHASI 23-UY</t>
+        </is>
+      </c>
+      <c r="Q64" t="inlineStr">
+        <is>
+          <t>+998 99 563 82 02</t>
+        </is>
+      </c>
+      <c r="R64" t="inlineStr">
+        <is>
+          <t>DILFUZA</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/static/Жилые_Комплексы/ЖК_Бахор/contract_registry.xlsx
+++ b/static/Жилые_Комплексы/ЖК_Бахор/contract_registry.xlsx
@@ -4105,73 +4105,73 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>52</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>2025-05-21</t>
+          <t>2025-05-22</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Блок 3,1</t>
+          <t>Блок-1,1</t>
         </is>
       </c>
       <c r="D48" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E48" t="n">
-        <v>240</v>
+        <v>60</v>
       </c>
       <c r="F48" t="n">
         <v>2</v>
       </c>
       <c r="G48" t="n">
-        <v>46.67</v>
+        <v>50.34</v>
       </c>
       <c r="H48" t="n">
-        <v>233350000</v>
+        <v>231564000</v>
       </c>
       <c r="I48" t="n">
-        <v>5000000</v>
+        <v>4600000</v>
       </c>
       <c r="J48" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>100</t>
         </is>
       </c>
       <c r="K48" t="n">
-        <v>70005000</v>
+        <v>231564000</v>
       </c>
       <c r="L48" t="inlineStr">
         <is>
-          <t>TURGUNOV SHOXOBIDDIN XALDAROVICH</t>
+          <t>YUSUPOVA NAFISA  AXMADJANOVNA</t>
         </is>
       </c>
       <c r="M48" t="inlineStr">
         <is>
-          <t>AD5175994</t>
+          <t>AB3354407</t>
         </is>
       </c>
       <c r="N48" t="inlineStr">
         <is>
-          <t>31506900231893</t>
+          <t>309242003836860031</t>
         </is>
       </c>
       <c r="O48" t="inlineStr">
         <is>
-          <t>IIV26284 20.11.2023</t>
+          <t>TOSHKENT  VILOYATI CHIRCHIQ SHAHAR IIB 10.03.2016</t>
         </is>
       </c>
       <c r="P48" t="inlineStr">
         <is>
-          <t>TOSHKENT SHAHAR SERGELI TUMANI XONOBOD MFY YAKUBOV KUCHASI 65 UY</t>
+          <t>TOSHKENT  VILOYATI CHIRCHIQ SHAHAR 8 KICHIK NOXYA 10 UY 38 XONADON</t>
         </is>
       </c>
       <c r="Q48" t="inlineStr">
         <is>
-          <t>+998998128448</t>
+          <t>+998880133833</t>
         </is>
       </c>
       <c r="R48" t="inlineStr">
@@ -4183,229 +4183,229 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>51</t>
+          <t>53</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>2025-05-21</t>
+          <t>2025-05-22</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Блок 3,1</t>
+          <t>Блок 1,2</t>
         </is>
       </c>
       <c r="D49" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E49" t="n">
-        <v>234</v>
+        <v>140</v>
       </c>
       <c r="F49" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G49" t="n">
-        <v>46.67</v>
+        <v>34.66</v>
       </c>
       <c r="H49" t="n">
-        <v>242684000</v>
+        <v>152504000</v>
       </c>
       <c r="I49" t="n">
-        <v>5200000</v>
+        <v>4400000</v>
       </c>
       <c r="J49" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>100</t>
         </is>
       </c>
       <c r="K49" t="n">
-        <v>72805200</v>
+        <v>152504000</v>
       </c>
       <c r="L49" t="inlineStr">
         <is>
-          <t>TURAEV JASURXON RAVSHANXONOVI</t>
+          <t>SOBIROV ABDULLA FATXILLA OGLI</t>
         </is>
       </c>
       <c r="M49" t="inlineStr">
         <is>
-          <t>AD2697466</t>
+          <t>AC0807821</t>
         </is>
       </c>
       <c r="N49" t="inlineStr">
         <is>
-          <t>31903840230025</t>
+          <t>33011940560028</t>
         </is>
       </c>
       <c r="O49" t="inlineStr">
         <is>
-          <t xml:space="preserve">IIV 60006 28.02.2023 </t>
+          <t>TOSHKENT VILOYATI CHIRCHIQ SHAHAR IIB 21.08.2018</t>
         </is>
       </c>
       <c r="P49" t="inlineStr">
         <is>
-          <t>TOSHKENT SHAHAR YANGI HAYOT TUMANI XUMO MFY SHOKIR ARIQ G 64 KUCHASI 113 UY</t>
+          <t>TOSHKENT VILOYATI CHIRCHIQ 8 KICHIK NOXIYA 36 UY 14 XONADON</t>
         </is>
       </c>
       <c r="Q49" t="inlineStr">
         <is>
-          <t>+998909080503</t>
+          <t>+998909099101</t>
         </is>
       </c>
       <c r="R49" t="inlineStr">
         <is>
-          <t>Aziz</t>
+          <t>AZIZ</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>52</t>
+          <t>54</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>2025-05-22</t>
+          <t>2025-05-23</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Блок-1,1</t>
+          <t>Блок 3</t>
         </is>
       </c>
       <c r="D50" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="E50" t="n">
-        <v>60</v>
+        <v>214</v>
       </c>
       <c r="F50" t="n">
         <v>2</v>
       </c>
       <c r="G50" t="n">
-        <v>50.34</v>
+        <v>44.28</v>
       </c>
       <c r="H50" t="n">
-        <v>231564000</v>
+        <v>194832000</v>
       </c>
       <c r="I50" t="n">
-        <v>4600000</v>
+        <v>4400000</v>
       </c>
       <c r="J50" t="inlineStr">
         <is>
-          <t>100</t>
+          <t>70</t>
         </is>
       </c>
       <c r="K50" t="n">
-        <v>231564000</v>
+        <v>136382400</v>
       </c>
       <c r="L50" t="inlineStr">
         <is>
-          <t>YUSUPOVA NAFISA  AXMADJANOVNA</t>
+          <t xml:space="preserve">BABADJANOVA ANGELA BATIRALIYEVNA </t>
         </is>
       </c>
       <c r="M50" t="inlineStr">
         <is>
-          <t>AB3354407</t>
+          <t>AD4481939</t>
         </is>
       </c>
       <c r="N50" t="inlineStr">
         <is>
-          <t>309242003836860031</t>
+          <t>40511880470048</t>
         </is>
       </c>
       <c r="O50" t="inlineStr">
         <is>
-          <t>TOSHKENT  VILOYATI CHIRCHIQ SHAHAR IIB 10.03.2016</t>
+          <t>IIV 60120 04.09.2023</t>
         </is>
       </c>
       <c r="P50" t="inlineStr">
         <is>
-          <t>TOSHKENT  VILOYATI CHIRCHIQ SHAHAR 8 KICHIK NOXYA 10 UY 38 XONADON</t>
+          <t>TOSHKENT VILOYATI CHIRCHIQ SHAHAR GULZOR MFY SUGDIYONA KUCHASI 8 UY</t>
         </is>
       </c>
       <c r="Q50" t="inlineStr">
         <is>
-          <t>+998880133833</t>
+          <t>+998936169555</t>
         </is>
       </c>
       <c r="R50" t="inlineStr">
         <is>
-          <t>Aziz</t>
+          <t>AZIZ</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>53</t>
+          <t>55</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>2025-05-22</t>
+          <t>2025-05-23</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Блок 1,2</t>
+          <t>Блок-1</t>
         </is>
       </c>
       <c r="D51" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E51" t="n">
-        <v>140</v>
+        <v>12</v>
       </c>
       <c r="F51" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G51" t="n">
-        <v>34.66</v>
+        <v>50.34</v>
       </c>
       <c r="H51" t="n">
-        <v>152504000</v>
+        <v>271836000</v>
       </c>
       <c r="I51" t="n">
-        <v>4400000</v>
+        <v>5400000</v>
       </c>
       <c r="J51" t="inlineStr">
         <is>
-          <t>100</t>
+          <t>30</t>
         </is>
       </c>
       <c r="K51" t="n">
-        <v>152504000</v>
+        <v>81550800</v>
       </c>
       <c r="L51" t="inlineStr">
         <is>
-          <t>SOBIROV ABDULLA FATXILLA OGLI</t>
+          <t>SODIKOV SARDOR TOSHKUVATOVICH</t>
         </is>
       </c>
       <c r="M51" t="inlineStr">
         <is>
-          <t>AC0807821</t>
+          <t>AB0229238</t>
         </is>
       </c>
       <c r="N51" t="inlineStr">
         <is>
-          <t>33011940560028</t>
+          <t>32706862420013</t>
         </is>
       </c>
       <c r="O51" t="inlineStr">
         <is>
-          <t>TOSHKENT VILOYATI CHIRCHIQ SHAHAR IIB 21.08.2018</t>
+          <t>NAVOIY VILOYATI KARMANA TUMANI IIB</t>
         </is>
       </c>
       <c r="P51" t="inlineStr">
         <is>
-          <t>TOSHKENT VILOYATI CHIRCHIQ 8 KICHIK NOXIYA 36 UY 14 XONADON</t>
+          <t>TOSHKENT VILOYATI CHIRCHIQ SHAHAR XUMO MFY 8 KICHIK NOXYA 35 UY 31 XONADON</t>
         </is>
       </c>
       <c r="Q51" t="inlineStr">
         <is>
-          <t>+998909099101</t>
+          <t>+998936634497</t>
         </is>
       </c>
       <c r="R51" t="inlineStr">
@@ -4417,7 +4417,7 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>54</t>
+          <t>56</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -4431,59 +4431,59 @@
         </is>
       </c>
       <c r="D52" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E52" t="n">
-        <v>214</v>
+        <v>207</v>
       </c>
       <c r="F52" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G52" t="n">
-        <v>44.28</v>
+        <v>55.67</v>
       </c>
       <c r="H52" t="n">
-        <v>194832000</v>
+        <v>278350000</v>
       </c>
       <c r="I52" t="n">
-        <v>4400000</v>
+        <v>5000000</v>
       </c>
       <c r="J52" t="inlineStr">
         <is>
-          <t>70</t>
+          <t>30</t>
         </is>
       </c>
       <c r="K52" t="n">
-        <v>136382400</v>
+        <v>83505000</v>
       </c>
       <c r="L52" t="inlineStr">
         <is>
-          <t xml:space="preserve">BABADJANOVA ANGELA BATIRALIYEVNA </t>
+          <t>ABDUXOLIQOV FARRUX FARHOD OGLI</t>
         </is>
       </c>
       <c r="M52" t="inlineStr">
         <is>
-          <t>AD4481939</t>
+          <t>AD6688630</t>
         </is>
       </c>
       <c r="N52" t="inlineStr">
         <is>
-          <t>40511880470048</t>
+          <t>32210900840063</t>
         </is>
       </c>
       <c r="O52" t="inlineStr">
         <is>
-          <t>IIV 60120 04.09.2023</t>
+          <t>IIV 27419 02.04.2024</t>
         </is>
       </c>
       <c r="P52" t="inlineStr">
         <is>
-          <t>TOSHKENT VILOYATI CHIRCHIQ SHAHAR GULZOR MFY SUGDIYONA KUCHASI 8 UY</t>
+          <t>TOSHKENT VILOYATI CHIRCHIQ SHAHAR ADOLAT MFY 9 KICHIK NOXYA 36 UY 17 XONADON</t>
         </is>
       </c>
       <c r="Q52" t="inlineStr">
         <is>
-          <t>+998936169555</t>
+          <t>+998917777229</t>
         </is>
       </c>
       <c r="R52" t="inlineStr">
@@ -4495,102 +4495,102 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>55</t>
+          <t>57</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>2025-05-23</t>
+          <t>2025-05-24</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Блок-1</t>
+          <t>Блок-1,1</t>
         </is>
       </c>
       <c r="D53" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E53" t="n">
-        <v>12</v>
+        <v>61</v>
       </c>
       <c r="F53" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G53" t="n">
-        <v>50.34</v>
+        <v>34.66</v>
       </c>
       <c r="H53" t="n">
-        <v>271836000</v>
+        <v>173300000</v>
       </c>
       <c r="I53" t="n">
-        <v>5400000</v>
+        <v>5000000</v>
       </c>
       <c r="J53" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>50</t>
         </is>
       </c>
       <c r="K53" t="n">
-        <v>81550800</v>
+        <v>86650000</v>
       </c>
       <c r="L53" t="inlineStr">
         <is>
-          <t>SODIKOV SARDOR TOSHKUVATOVICH</t>
+          <t>BOBODUSTOV SHOHZOD ZOKIR O`G`LI</t>
         </is>
       </c>
       <c r="M53" t="inlineStr">
         <is>
-          <t>AB0229238</t>
+          <t>AB3768763</t>
         </is>
       </c>
       <c r="N53" t="inlineStr">
         <is>
-          <t>32706862420013</t>
+          <t>30110985640034</t>
         </is>
       </c>
       <c r="O53" t="inlineStr">
         <is>
-          <t>NAVOIY VILOYATI KARMANA TUMANI IIB</t>
+          <t>QASHQADARYO VILOYATI CHIROQCHI TIIB</t>
         </is>
       </c>
       <c r="P53" t="inlineStr">
         <is>
-          <t>TOSHKENT VILOYATI CHIRCHIQ SHAHAR XUMO MFY 8 KICHIK NOXYA 35 UY 31 XONADON</t>
+          <t>QASHQADARYO VILOYATI CHIROQCHI TUMANI BESHCHASHMA QMB PAST UYSHUN 666-XONADON</t>
         </is>
       </c>
       <c r="Q53" t="inlineStr">
         <is>
-          <t>+998936634497</t>
+          <t>+998 93 958-89-98</t>
         </is>
       </c>
       <c r="R53" t="inlineStr">
         <is>
-          <t>AZIZ</t>
+          <t>DILFUZA</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>56</t>
+          <t>58</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>2025-05-23</t>
+          <t>2025-05-25</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Блок 3</t>
+          <t>Блок 3,1</t>
         </is>
       </c>
       <c r="D54" t="n">
         <v>4</v>
       </c>
       <c r="E54" t="n">
-        <v>207</v>
+        <v>237</v>
       </c>
       <c r="F54" t="n">
         <v>3</v>
@@ -4599,88 +4599,88 @@
         <v>55.67</v>
       </c>
       <c r="H54" t="n">
-        <v>278350000</v>
+        <v>267216000</v>
       </c>
       <c r="I54" t="n">
-        <v>5000000</v>
+        <v>4800000</v>
       </c>
       <c r="J54" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>50</t>
         </is>
       </c>
       <c r="K54" t="n">
-        <v>83505000</v>
+        <v>133608000</v>
       </c>
       <c r="L54" t="inlineStr">
         <is>
-          <t>ABDUXOLIQOV FARRUX FARHOD OGLI</t>
+          <t>NORMATOVA KAMOLA YULDASHEVNA</t>
         </is>
       </c>
       <c r="M54" t="inlineStr">
         <is>
-          <t>AD6688630</t>
+          <t>AD7797320</t>
         </is>
       </c>
       <c r="N54" t="inlineStr">
         <is>
-          <t>32210900840063</t>
+          <t>41008891520022</t>
         </is>
       </c>
       <c r="O54" t="inlineStr">
         <is>
-          <t>IIV 27419 02.04.2024</t>
+          <t>IIV 26296 09.072024</t>
         </is>
       </c>
       <c r="P54" t="inlineStr">
         <is>
-          <t>TOSHKENT VILOYATI CHIRCHIQ SHAHAR ADOLAT MFY 9 KICHIK NOXYA 36 UY 17 XONADON</t>
+          <t>TOSHKENT SHAHAR MIRZO ULUGBEK TUMANI  FERUZA KUCHASI 51 UY 39 XONADON</t>
         </is>
       </c>
       <c r="Q54" t="inlineStr">
         <is>
-          <t>+998917777229</t>
+          <t>+998970021416</t>
         </is>
       </c>
       <c r="R54" t="inlineStr">
         <is>
-          <t>AZIZ</t>
+          <t>Руководство</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>57</t>
+          <t>59</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>2025-05-24</t>
+          <t>2025-05-26</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Блок-1,1</t>
+          <t>Блок 3</t>
         </is>
       </c>
       <c r="D55" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E55" t="n">
-        <v>61</v>
+        <v>208</v>
       </c>
       <c r="F55" t="n">
         <v>1</v>
       </c>
       <c r="G55" t="n">
-        <v>34.66</v>
+        <v>44.28</v>
       </c>
       <c r="H55" t="n">
-        <v>173300000</v>
+        <v>212544000</v>
       </c>
       <c r="I55" t="n">
-        <v>5000000</v>
+        <v>4800000</v>
       </c>
       <c r="J55" t="inlineStr">
         <is>
@@ -4688,365 +4688,365 @@
         </is>
       </c>
       <c r="K55" t="n">
-        <v>86650000</v>
+        <v>106272000</v>
       </c>
       <c r="L55" t="inlineStr">
         <is>
-          <t>BOBODUSTOV SHOHZOD ZOKIR O`G`LI</t>
+          <t>FAYZULLAYEV HAYOT DILMURODOVICH</t>
         </is>
       </c>
       <c r="M55" t="inlineStr">
         <is>
-          <t>AB3768763</t>
+          <t>AD5839429</t>
         </is>
       </c>
       <c r="N55" t="inlineStr">
         <is>
-          <t>30110985640034</t>
+          <t>31612930470051</t>
         </is>
       </c>
       <c r="O55" t="inlineStr">
         <is>
-          <t>QASHQADARYO VILOYATI CHIROQCHI TIIB</t>
+          <t>IIV 27419 20.01.2024</t>
         </is>
       </c>
       <c r="P55" t="inlineStr">
         <is>
-          <t>QASHQADARYO VILOYATI CHIROQCHI TUMANI BESHCHASHMA QMB PAST UYSHUN 666-XONADON</t>
+          <t>TOSHKENT  VILOYATI CHIRCHIQ SHAHAR GALABA KUCHASI 16 UY 31 XONADON</t>
         </is>
       </c>
       <c r="Q55" t="inlineStr">
         <is>
-          <t>+998 93 958-89-98</t>
+          <t>917756969</t>
         </is>
       </c>
       <c r="R55" t="inlineStr">
         <is>
-          <t>DILFUZA</t>
+          <t>РУКОВОДССТВО</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>58</t>
+          <t>60</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>2025-05-25</t>
+          <t>2025-05-26</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Блок 3,1</t>
+          <t>Блок-1</t>
         </is>
       </c>
       <c r="D56" t="n">
+        <v>1</v>
+      </c>
+      <c r="E56" t="n">
         <v>4</v>
       </c>
-      <c r="E56" t="n">
-        <v>237</v>
-      </c>
       <c r="F56" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G56" t="n">
-        <v>55.67</v>
+        <v>47.94</v>
       </c>
       <c r="H56" t="n">
-        <v>267216000</v>
+        <v>249288000</v>
       </c>
       <c r="I56" t="n">
-        <v>4800000</v>
+        <v>5200000</v>
       </c>
       <c r="J56" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>70</t>
         </is>
       </c>
       <c r="K56" t="n">
-        <v>133608000</v>
+        <v>174501600</v>
       </c>
       <c r="L56" t="inlineStr">
         <is>
-          <t>NORMATOVA KAMOLA YULDASHEVNA</t>
+          <t>KARGAPOLOVNA ELENA PETROVNA</t>
         </is>
       </c>
       <c r="M56" t="inlineStr">
         <is>
-          <t>AD7797320</t>
+          <t>AD8083373</t>
         </is>
       </c>
       <c r="N56" t="inlineStr">
         <is>
-          <t>41008891520022</t>
+          <t>40907936860013</t>
         </is>
       </c>
       <c r="O56" t="inlineStr">
         <is>
-          <t>IIV 26296 09.072024</t>
+          <t>IIV 27419 01.08.2024</t>
         </is>
       </c>
       <c r="P56" t="inlineStr">
         <is>
-          <t>TOSHKENT SHAHAR MIRZO ULUGBEK TUMANI  FERUZA KUCHASI 51 UY 39 XONADON</t>
+          <t>TOSHKENT VILOYATI CHIRCHIQ SHAHAR  OKRUJNAYA KUCHASI 33A XONADON</t>
         </is>
       </c>
       <c r="Q56" t="inlineStr">
         <is>
-          <t>+998970021416</t>
+          <t>+998998288286</t>
         </is>
       </c>
       <c r="R56" t="inlineStr">
         <is>
-          <t>Руководство</t>
+          <t>РУКОВОДССТВО</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>59</t>
+          <t>61</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>2025-05-26</t>
+          <t>2025-05-27</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Блок 3</t>
+          <t>Блок 1,2</t>
         </is>
       </c>
       <c r="D57" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E57" t="n">
-        <v>208</v>
+        <v>128</v>
       </c>
       <c r="F57" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G57" t="n">
-        <v>44.28</v>
+        <v>50.34</v>
       </c>
       <c r="H57" t="n">
-        <v>212544000</v>
+        <v>251700000</v>
       </c>
       <c r="I57" t="n">
-        <v>4800000</v>
+        <v>5000000</v>
       </c>
       <c r="J57" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>70</t>
         </is>
       </c>
       <c r="K57" t="n">
-        <v>106272000</v>
+        <v>176190000</v>
       </c>
       <c r="L57" t="inlineStr">
         <is>
-          <t>FAYZULLAYEV HAYOT DILMURODOVICH</t>
+          <t>XAYTBAYEVA FARIDA TOSHTEMIROVNA</t>
         </is>
       </c>
       <c r="M57" t="inlineStr">
         <is>
-          <t>AD5839429</t>
+          <t>AD1665555</t>
         </is>
       </c>
       <c r="N57" t="inlineStr">
         <is>
-          <t>31612930470051</t>
+          <t>40110876860018</t>
         </is>
       </c>
       <c r="O57" t="inlineStr">
         <is>
-          <t>IIV 27419 20.01.2024</t>
+          <t>IIV 27419 17.08.2022</t>
         </is>
       </c>
       <c r="P57" t="inlineStr">
         <is>
-          <t>TOSHKENT  VILOYATI CHIRCHIQ SHAHAR GALABA KUCHASI 16 UY 31 XONADON</t>
+          <t>TOSHKENT VILOYATI CHIRCHIQ SHAHAR 8 KICHIK NOXYA 2 UY 75 XONADON</t>
         </is>
       </c>
       <c r="Q57" t="inlineStr">
         <is>
-          <t>917756969</t>
+          <t>+998917763438</t>
         </is>
       </c>
       <c r="R57" t="inlineStr">
         <is>
-          <t>РУКОВОДССТВО</t>
+          <t>MIKHAIL</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>60</t>
+          <t>62</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>2025-05-26</t>
+          <t>2025-05-30</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Блок-1</t>
+          <t>Блок-1,1</t>
         </is>
       </c>
       <c r="D58" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E58" t="n">
-        <v>4</v>
+        <v>53</v>
       </c>
       <c r="F58" t="n">
         <v>1</v>
       </c>
       <c r="G58" t="n">
-        <v>47.94</v>
+        <v>34.66</v>
       </c>
       <c r="H58" t="n">
-        <v>249288000</v>
+        <v>194096000</v>
       </c>
       <c r="I58" t="n">
-        <v>5200000</v>
+        <v>5600000</v>
       </c>
       <c r="J58" t="inlineStr">
         <is>
-          <t>70</t>
+          <t>30</t>
         </is>
       </c>
       <c r="K58" t="n">
-        <v>174501600</v>
+        <v>58228800</v>
       </c>
       <c r="L58" t="inlineStr">
         <is>
-          <t>KARGAPOLOVNA ELENA PETROVNA</t>
+          <t>RAXMANOV JAVOHIR AHMAD O'G'LI</t>
         </is>
       </c>
       <c r="M58" t="inlineStr">
         <is>
-          <t>AD8083373</t>
+          <t>AB4145338</t>
         </is>
       </c>
       <c r="N58" t="inlineStr">
         <is>
-          <t>40907936860013</t>
+          <t>33005975630050</t>
         </is>
       </c>
       <c r="O58" t="inlineStr">
         <is>
-          <t>IIV 27419 01.08.2024</t>
+          <t>10.06.2016 КАМАШИНСКИЙ РОВД, КАШКАДАРЬИНСКОЙ ОБЛАСТИ</t>
         </is>
       </c>
       <c r="P58" t="inlineStr">
         <is>
-          <t>TOSHKENT VILOYATI CHIRCHIQ SHAHAR  OKRUJNAYA KUCHASI 33A XONADON</t>
+          <t>Qashqadaryo viloyati Qamashi tumani Gʻishtli MFY 102- uy</t>
         </is>
       </c>
       <c r="Q58" t="inlineStr">
         <is>
-          <t>+998998288286</t>
+          <t>+998946699007</t>
         </is>
       </c>
       <c r="R58" t="inlineStr">
         <is>
-          <t>РУКОВОДССТВО</t>
+          <t>AZIZ</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>61</t>
+          <t>64</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>2025-05-27</t>
+          <t>2025-05-31</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Блок 1,2</t>
+          <t>Блок 3,1</t>
         </is>
       </c>
       <c r="D59" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E59" t="n">
-        <v>128</v>
+        <v>238</v>
       </c>
       <c r="F59" t="n">
         <v>2</v>
       </c>
       <c r="G59" t="n">
-        <v>50.34</v>
+        <v>44.28</v>
       </c>
       <c r="H59" t="n">
-        <v>251700000</v>
+        <v>221400000</v>
       </c>
       <c r="I59" t="n">
         <v>5000000</v>
       </c>
       <c r="J59" t="inlineStr">
         <is>
-          <t>70</t>
+          <t>50</t>
         </is>
       </c>
       <c r="K59" t="n">
-        <v>176190000</v>
+        <v>110700000</v>
       </c>
       <c r="L59" t="inlineStr">
         <is>
-          <t>XAYTBAYEVA FARIDA TOSHTEMIROVNA</t>
+          <t>MAXMUDOVA GULNUR ABDUMUTAL QIZI</t>
         </is>
       </c>
       <c r="M59" t="inlineStr">
         <is>
-          <t>AD1665555</t>
+          <t>AD3854467</t>
         </is>
       </c>
       <c r="N59" t="inlineStr">
         <is>
-          <t>40110876860018</t>
+          <t>41810966780046</t>
         </is>
       </c>
       <c r="O59" t="inlineStr">
         <is>
-          <t>IIV 27419 17.08.2022</t>
+          <t>IIV 27248</t>
         </is>
       </c>
       <c r="P59" t="inlineStr">
         <is>
-          <t>TOSHKENT VILOYATI CHIRCHIQ SHAHAR 8 KICHIK NOXYA 2 UY 75 XONADON</t>
+          <t>TOSHKENT  VILOYATI  QIBRAY TUMANI ZAFARABOT XFY SHARQ MFY ZAFARABOT GULZOR UY; R/S</t>
         </is>
       </c>
       <c r="Q59" t="inlineStr">
         <is>
-          <t>+998917763438</t>
+          <t>+99833-001-18-10</t>
         </is>
       </c>
       <c r="R59" t="inlineStr">
         <is>
-          <t>MIKHAIL</t>
+          <t>NILUFAR</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>62</t>
+          <t>65</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>2025-05-30</t>
+          <t>2025-06-01</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
@@ -5055,10 +5055,10 @@
         </is>
       </c>
       <c r="D60" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E60" t="n">
-        <v>53</v>
+        <v>57</v>
       </c>
       <c r="F60" t="n">
         <v>1</v>
@@ -5067,47 +5067,47 @@
         <v>34.66</v>
       </c>
       <c r="H60" t="n">
-        <v>194096000</v>
+        <v>180232000</v>
       </c>
       <c r="I60" t="n">
-        <v>5600000</v>
+        <v>5200000</v>
       </c>
       <c r="J60" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>50</t>
         </is>
       </c>
       <c r="K60" t="n">
-        <v>58228800</v>
+        <v>90116000</v>
       </c>
       <c r="L60" t="inlineStr">
         <is>
-          <t>RAXMANOV JAVOHIR AHMAD O'G'LI</t>
+          <t>DAVLATBAYEV XASAN DILSHAD OGLI</t>
         </is>
       </c>
       <c r="M60" t="inlineStr">
         <is>
-          <t>AB4145338</t>
+          <t>AB6769142</t>
         </is>
       </c>
       <c r="N60" t="inlineStr">
         <is>
-          <t>33005975630050</t>
+          <t>52604016860035</t>
         </is>
       </c>
       <c r="O60" t="inlineStr">
         <is>
-          <t>10.06.2016 КАМАШИНСКИЙ РОВД, КАШКАДАРЬИНСКОЙ ОБЛАСТИ</t>
+          <t>TOSHKENT VILOYATI CHIRCHIQ SHAHAR IIB 19.05.2017</t>
         </is>
       </c>
       <c r="P60" t="inlineStr">
         <is>
-          <t>Qashqadaryo viloyati Qamashi tumani Gʻishtli MFY 102- uy</t>
+          <t>TOSHKENT VILOYATI CHIRCHIQ SHAHAR KIMYOGAR MFY YORKIN KELAJAK KUCHASI 2A UY</t>
         </is>
       </c>
       <c r="Q60" t="inlineStr">
         <is>
-          <t>+998946699007</t>
+          <t>+998998024662</t>
         </is>
       </c>
       <c r="R60" t="inlineStr">
@@ -5119,24 +5119,24 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>64</t>
+          <t>66</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>2025-05-31</t>
+          <t>2025-06-02</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Блок 3,1</t>
+          <t>Блок 3,2</t>
         </is>
       </c>
       <c r="D61" t="n">
         <v>4</v>
       </c>
       <c r="E61" t="n">
-        <v>238</v>
+        <v>268</v>
       </c>
       <c r="F61" t="n">
         <v>2</v>
@@ -5160,32 +5160,32 @@
       </c>
       <c r="L61" t="inlineStr">
         <is>
-          <t>MAXMUDOVA GULNUR ABDUMUTAL QIZI</t>
+          <t>MUSTAFAYEV ABDIMUROD OBULQOSIMOVICH</t>
         </is>
       </c>
       <c r="M61" t="inlineStr">
         <is>
-          <t>AD3854467</t>
+          <t>AD 0063132</t>
         </is>
       </c>
       <c r="N61" t="inlineStr">
         <is>
-          <t>41810966780046</t>
+          <t>32501848240012</t>
         </is>
       </c>
       <c r="O61" t="inlineStr">
         <is>
-          <t>IIV 27248</t>
+          <t>IIV 10411</t>
         </is>
       </c>
       <c r="P61" t="inlineStr">
         <is>
-          <t>TOSHKENT  VILOYATI  QIBRAY TUMANI ZAFARABOT XFY SHARQ MFY ZAFARABOT GULZOR UY; R/S</t>
+          <t xml:space="preserve">TOSHKENT SHAXRI YASHNOBOD TUMANI olmas MFY Kunduzsay ul 4tupik 12 uy 231 xonadon </t>
         </is>
       </c>
       <c r="Q61" t="inlineStr">
         <is>
-          <t>+99833-001-18-10</t>
+          <t>+998946408017</t>
         </is>
       </c>
       <c r="R61" t="inlineStr">
@@ -5197,33 +5197,33 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>65</t>
+          <t>69</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>2025-06-01</t>
+          <t>2025-06-07</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Блок-1,1</t>
+          <t>Блок 3,1</t>
         </is>
       </c>
       <c r="D62" t="n">
         <v>3</v>
       </c>
       <c r="E62" t="n">
-        <v>57</v>
+        <v>232</v>
       </c>
       <c r="F62" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G62" t="n">
-        <v>34.66</v>
+        <v>44.28</v>
       </c>
       <c r="H62" t="n">
-        <v>180232000</v>
+        <v>230256000</v>
       </c>
       <c r="I62" t="n">
         <v>5200000</v>
@@ -5234,131 +5234,131 @@
         </is>
       </c>
       <c r="K62" t="n">
-        <v>90116000</v>
+        <v>115128000</v>
       </c>
       <c r="L62" t="inlineStr">
         <is>
-          <t>DAVLATBAYEV XASAN DILSHAD OGLI</t>
+          <t xml:space="preserve">RASSKAZOVA DJAMILYA KARIMOVNA </t>
         </is>
       </c>
       <c r="M62" t="inlineStr">
         <is>
-          <t>AB6769142</t>
+          <t>AD1014793</t>
         </is>
       </c>
       <c r="N62" t="inlineStr">
         <is>
-          <t>52604016860035</t>
+          <t>42508900241339</t>
         </is>
       </c>
       <c r="O62" t="inlineStr">
         <is>
-          <t>TOSHKENT VILOYATI CHIRCHIQ SHAHAR IIB 19.05.2017</t>
+          <t xml:space="preserve">IIV26287   </t>
         </is>
       </c>
       <c r="P62" t="inlineStr">
         <is>
-          <t>TOSHKENT VILOYATI CHIRCHIQ SHAHAR KIMYOGAR MFY YORKIN KELAJAK KUCHASI 2A UY</t>
+          <t>г. Ташкент Яккасарайский р-н ул. Шота Руставелли дом 59-53</t>
         </is>
       </c>
       <c r="Q62" t="inlineStr">
         <is>
-          <t>+998998024662</t>
+          <t>+998909495490</t>
         </is>
       </c>
       <c r="R62" t="inlineStr">
         <is>
-          <t>AZIZ</t>
+          <t xml:space="preserve">михаил </t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>66</t>
+          <t>70</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>2025-06-02</t>
+          <t>2025-06-07</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Блок 3,2</t>
+          <t>Блок-1</t>
         </is>
       </c>
       <c r="D63" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E63" t="n">
-        <v>268</v>
+        <v>21</v>
       </c>
       <c r="F63" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G63" t="n">
-        <v>44.28</v>
+        <v>34.66</v>
       </c>
       <c r="H63" t="n">
-        <v>221400000</v>
+        <v>187164000</v>
       </c>
       <c r="I63" t="n">
-        <v>5000000</v>
+        <v>5400000</v>
       </c>
       <c r="J63" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>30</t>
         </is>
       </c>
       <c r="K63" t="n">
-        <v>110700000</v>
+        <v>56149200</v>
       </c>
       <c r="L63" t="inlineStr">
         <is>
-          <t>MUSTAFAYEV ABDIMUROD OBULQOSIMOVICH</t>
+          <t xml:space="preserve">IRGASHEV ALMAZ BAXADIROVICH </t>
         </is>
       </c>
       <c r="M63" t="inlineStr">
         <is>
-          <t>AD 0063132</t>
+          <t>AC1381774</t>
         </is>
       </c>
       <c r="N63" t="inlineStr">
         <is>
-          <t>32501848240012</t>
+          <t>52709026590029</t>
         </is>
       </c>
       <c r="O63" t="inlineStr">
         <is>
-          <t>IIV 10411</t>
+          <t>TOSHKENT SHAHAR CHILONZOR TUMANI IIB</t>
         </is>
       </c>
       <c r="P63" t="inlineStr">
         <is>
-          <t xml:space="preserve">TOSHKENT SHAXRI YASHNOBOD TUMANI olmas MFY Kunduzsay ul 4tupik 12 uy 231 xonadon </t>
+          <t>ЧИЛАНЗАР КВАРТАЛ-8 ДОМ 25 КВАТИРА 46</t>
         </is>
       </c>
       <c r="Q63" t="inlineStr">
         <is>
-          <t>+998946408017</t>
+          <t>+998903461245</t>
         </is>
       </c>
       <c r="R63" t="inlineStr">
         <is>
-          <t>NILUFAR</t>
+          <t>МИХАИЛ</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>67</t>
+          <t>71</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>2025-06-05</t>
+          <t>2025-06-08</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
@@ -5379,18 +5379,18 @@
         <v>50.34</v>
       </c>
       <c r="H64" t="n">
-        <v>251700000</v>
+        <v>241632000</v>
       </c>
       <c r="I64" t="n">
-        <v>5000000</v>
+        <v>4800000</v>
       </c>
       <c r="J64" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>50</t>
         </is>
       </c>
       <c r="K64" t="n">
-        <v>75510000</v>
+        <v>120816000</v>
       </c>
       <c r="L64" t="inlineStr">
         <is>
@@ -5424,7 +5424,7 @@
       </c>
       <c r="R64" t="inlineStr">
         <is>
-          <t>DILFUZA</t>
+          <t>NILUFAR</t>
         </is>
       </c>
     </row>

--- a/static/Жилые_Комплексы/ЖК_Бахор/contract_registry.xlsx
+++ b/static/Жилые_Комплексы/ЖК_Бахор/contract_registry.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R64"/>
+  <dimension ref="A1:R79"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2857,24 +2857,24 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>32</t>
+          <t>34</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>2025-04-30</t>
+          <t>2025-05-03</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Блок-1,1</t>
+          <t>Блок 1,2</t>
         </is>
       </c>
       <c r="D32" t="n">
         <v>5</v>
       </c>
       <c r="E32" t="n">
-        <v>77</v>
+        <v>145</v>
       </c>
       <c r="F32" t="n">
         <v>1</v>
@@ -2883,232 +2883,232 @@
         <v>34.66</v>
       </c>
       <c r="H32" t="n">
-        <v>138640000</v>
+        <v>166368000</v>
       </c>
       <c r="I32" t="n">
-        <v>4000000</v>
+        <v>4800000</v>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>100</t>
+          <t>30</t>
         </is>
       </c>
       <c r="K32" t="n">
-        <v>138640000</v>
+        <v>49910400</v>
       </c>
       <c r="L32" t="inlineStr">
         <is>
-          <t>NISHANOV AZIZ YASHINOVICH</t>
+          <t>MIRALIMOV ERKIN ERGASHVOIVICH</t>
         </is>
       </c>
       <c r="M32" t="inlineStr">
         <is>
-          <t>AD1571420</t>
+          <t>AD2988250</t>
         </is>
       </c>
       <c r="N32" t="inlineStr">
         <is>
-          <t>30103976890015</t>
+          <t>31710810470037</t>
         </is>
       </c>
       <c r="O32" t="inlineStr">
         <is>
-          <t xml:space="preserve">  IIV 30401 20.07.2022</t>
+          <t>TOSHKENT VILOYATI CHIRCHIQ SHAHAR IIV 27419</t>
         </is>
       </c>
       <c r="P32" t="inlineStr">
         <is>
-          <t>FARGONA VILOYATI FARGONA SHAHAR SAKKOKIY KUCHASI 10 UY</t>
+          <t>TOSHKENT VILOYATI CHIRCHIQ SHAHAR G`OFUR G`ULOM KO`CHASI 17-UY</t>
         </is>
       </c>
       <c r="Q32" t="inlineStr">
         <is>
-          <t>+998982768888</t>
+          <t xml:space="preserve">+998 77 072 63 69 </t>
         </is>
       </c>
       <c r="R32" t="inlineStr">
         <is>
-          <t>РУКОВОДССТВО</t>
+          <t>DILFUZA</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>33</t>
+          <t>35</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>2025-04-30</t>
+          <t>2025-05-05</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Блок-1,1</t>
+          <t>Блок 3,1</t>
         </is>
       </c>
       <c r="D33" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="E33" t="n">
-        <v>80</v>
+        <v>220</v>
       </c>
       <c r="F33" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G33" t="n">
-        <v>34.66</v>
+        <v>41.88</v>
       </c>
       <c r="H33" t="n">
-        <v>138640000</v>
+        <v>234528000</v>
       </c>
       <c r="I33" t="n">
-        <v>4000000</v>
+        <v>5600000</v>
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>100</t>
+          <t>30</t>
         </is>
       </c>
       <c r="K33" t="n">
-        <v>138640000</v>
+        <v>70358400</v>
       </c>
       <c r="L33" t="inlineStr">
         <is>
-          <t>TOXTANAZAROV KOMIL FAXRITDINOVICH</t>
+          <t>TOSHMATOVA GULGINA MIDXATOVNA</t>
         </is>
       </c>
       <c r="M33" t="inlineStr">
         <is>
-          <t>AD2698825</t>
+          <t>AD3519875</t>
         </is>
       </c>
       <c r="N33" t="inlineStr">
         <is>
-          <t>31009876890045</t>
+          <t>41408686860016</t>
         </is>
       </c>
       <c r="O33" t="inlineStr">
         <is>
-          <t>IIV 30401 01.03.2033</t>
+          <t>IIV 27419</t>
         </is>
       </c>
       <c r="P33" t="inlineStr">
         <is>
-          <t>FARGONA VILOYATI FARGONA SHAHAR TALABALAR KUCHASI 8 UY</t>
+          <t>TOSHKENT VILOYATI CHIRCHIQ SHAHAR XAYOTGULI KO'CHASI 39-UY</t>
         </is>
       </c>
       <c r="Q33" t="inlineStr">
         <is>
-          <t>+998985758111</t>
+          <t>+998 88 178 98 48</t>
         </is>
       </c>
       <c r="R33" t="inlineStr">
         <is>
-          <t>РУКОВОДССТВО</t>
+          <t>DILFUZA</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>34</t>
+          <t>36</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>2025-05-03</t>
+          <t>2025-05-05</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Блок 1,2</t>
+          <t>Блок-1</t>
         </is>
       </c>
       <c r="D34" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="E34" t="n">
-        <v>145</v>
+        <v>20</v>
       </c>
       <c r="F34" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G34" t="n">
-        <v>34.66</v>
+        <v>50.34</v>
       </c>
       <c r="H34" t="n">
-        <v>166368000</v>
+        <v>251700000</v>
       </c>
       <c r="I34" t="n">
-        <v>4800000</v>
+        <v>5000000</v>
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>50</t>
         </is>
       </c>
       <c r="K34" t="n">
-        <v>49910400</v>
+        <v>125850000</v>
       </c>
       <c r="L34" t="inlineStr">
         <is>
-          <t>MIRALIMOV ERKIN ERGASHVOIVICH</t>
+          <t>OXUNOV MUXTOR TULQINOVICH</t>
         </is>
       </c>
       <c r="M34" t="inlineStr">
         <is>
-          <t>AD2988250</t>
+          <t>AD3843344</t>
         </is>
       </c>
       <c r="N34" t="inlineStr">
         <is>
-          <t>31710810470037</t>
+          <t>33005686860012</t>
         </is>
       </c>
       <c r="O34" t="inlineStr">
         <is>
-          <t>TOSHKENT VILOYATI CHIRCHIQ SHAHAR IIV 27419</t>
+          <t>IIV 27419 06.07.2023</t>
         </is>
       </c>
       <c r="P34" t="inlineStr">
         <is>
-          <t>TOSHKENT VILOYATI CHIRCHIQ SHAHAR G`OFUR G`ULOM KO`CHASI 17-UY</t>
+          <t>TOSHKENT VILOYATI CHIRCHIK SHAHAR 10 KICHIK NOXIYA 31 UY 53 XONADON</t>
         </is>
       </c>
       <c r="Q34" t="inlineStr">
         <is>
-          <t xml:space="preserve">+998 77 072 63 69 </t>
+          <t>+998942125661</t>
         </is>
       </c>
       <c r="R34" t="inlineStr">
         <is>
-          <t>DILFUZA</t>
+          <t>AZIZ</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>35</t>
+          <t>37</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>2025-05-05</t>
+          <t>2025-05-08</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Блок 3,1</t>
+          <t>Блок 3</t>
         </is>
       </c>
       <c r="D35" t="n">
         <v>1</v>
       </c>
       <c r="E35" t="n">
-        <v>220</v>
+        <v>190</v>
       </c>
       <c r="F35" t="n">
         <v>2</v>
@@ -3132,32 +3132,32 @@
       </c>
       <c r="L35" t="inlineStr">
         <is>
-          <t>TOSHMATOVA GULGINA MIDXATOVNA</t>
+          <t>NAZIROVA MAFTUNA BAXTIYOROVNA</t>
         </is>
       </c>
       <c r="M35" t="inlineStr">
         <is>
-          <t>AD3519875</t>
+          <t>AB4820841</t>
         </is>
       </c>
       <c r="N35" t="inlineStr">
         <is>
-          <t>41408686860016</t>
+          <t>41508930500043</t>
         </is>
       </c>
       <c r="O35" t="inlineStr">
         <is>
-          <t>IIV 27419</t>
+          <t>TOSHKENT VILOYATI BO`STONLIQ TUMANI IIB</t>
         </is>
       </c>
       <c r="P35" t="inlineStr">
         <is>
-          <t>TOSHKENT VILOYATI CHIRCHIQ SHAHAR XAYOTGULI KO'CHASI 39-UY</t>
+          <t>TOSHKENT VILOYATI CHIRCHIQ SHAHAR MUQUMIY KO`CHASI 38-UY 28-XONADON</t>
         </is>
       </c>
       <c r="Q35" t="inlineStr">
         <is>
-          <t>+998 88 178 98 48</t>
+          <t>+998 99 993-69-47</t>
         </is>
       </c>
       <c r="R35" t="inlineStr">
@@ -3169,348 +3169,348 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>36</t>
+          <t>38</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>2025-05-05</t>
+          <t>2025-05-12</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Блок-1</t>
+          <t>Блок 3,2</t>
         </is>
       </c>
       <c r="D36" t="n">
         <v>3</v>
       </c>
       <c r="E36" t="n">
-        <v>20</v>
+        <v>266</v>
       </c>
       <c r="F36" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G36" t="n">
-        <v>50.34</v>
+        <v>25.04</v>
       </c>
       <c r="H36" t="n">
-        <v>251700000</v>
+        <v>115184000</v>
       </c>
       <c r="I36" t="n">
-        <v>5000000</v>
+        <v>4600000</v>
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>100</t>
         </is>
       </c>
       <c r="K36" t="n">
-        <v>125850000</v>
+        <v>115184000</v>
       </c>
       <c r="L36" t="inlineStr">
         <is>
-          <t>OXUNOV MUXTOR TULQINOVICH</t>
+          <t>XAMIDULLAYEV ASADBEK SHERXON O'G'LI</t>
         </is>
       </c>
       <c r="M36" t="inlineStr">
         <is>
-          <t>AD3843344</t>
+          <t>AC2489461</t>
         </is>
       </c>
       <c r="N36" t="inlineStr">
         <is>
-          <t>33005686860012</t>
+          <t>51711036060037</t>
         </is>
       </c>
       <c r="O36" t="inlineStr">
         <is>
-          <t>IIV 27419 06.07.2023</t>
+          <t>SAMARQAND VILOYATI KATTAQO'RG'ON TUMANI IIB</t>
         </is>
       </c>
       <c r="P36" t="inlineStr">
         <is>
-          <t>TOSHKENT VILOYATI CHIRCHIK SHAHAR 10 KICHIK NOXIYA 31 UY 53 XONADON</t>
+          <t>SAMARQAND VILOYATI KATTAQO'RG'ON TUMANI KATTA KO'RPA KO'CHASI 2-UY</t>
         </is>
       </c>
       <c r="Q36" t="inlineStr">
         <is>
-          <t>+998942125661</t>
+          <t>+998 97 727 36 42</t>
         </is>
       </c>
       <c r="R36" t="inlineStr">
         <is>
-          <t>AZIZ</t>
+          <t>NILUFAR</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>37</t>
+          <t>39</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>2025-05-08</t>
+          <t>2025-05-12</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Блок 3</t>
+          <t>Блок 3,2</t>
         </is>
       </c>
       <c r="D37" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E37" t="n">
-        <v>190</v>
+        <v>265</v>
       </c>
       <c r="F37" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G37" t="n">
-        <v>41.88</v>
+        <v>57.77</v>
       </c>
       <c r="H37" t="n">
-        <v>234528000</v>
+        <v>288850000</v>
       </c>
       <c r="I37" t="n">
-        <v>5600000</v>
+        <v>5000000</v>
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>50</t>
         </is>
       </c>
       <c r="K37" t="n">
-        <v>70358400</v>
+        <v>144425000</v>
       </c>
       <c r="L37" t="inlineStr">
         <is>
-          <t>NAZIROVA MAFTUNA BAXTIYOROVNA</t>
+          <t>XAMIDULLAYEV ASADBEK SHERXON O'G'LI</t>
         </is>
       </c>
       <c r="M37" t="inlineStr">
         <is>
-          <t>AB4820841</t>
+          <t>AC2489461</t>
         </is>
       </c>
       <c r="N37" t="inlineStr">
         <is>
-          <t>41508930500043</t>
+          <t>51711036060037</t>
         </is>
       </c>
       <c r="O37" t="inlineStr">
         <is>
-          <t>TOSHKENT VILOYATI BO`STONLIQ TUMANI IIB</t>
+          <t>SAMARQAND VILOYATI KATTAQO'RG'ON TUMANI IIB</t>
         </is>
       </c>
       <c r="P37" t="inlineStr">
         <is>
-          <t>TOSHKENT VILOYATI CHIRCHIQ SHAHAR MUQUMIY KO`CHASI 38-UY 28-XONADON</t>
+          <t>SAMARQAND VILOYATI KATTAQO'RG'ON TUMANI KATTA KO'RPA KO'CHASI 2-UY</t>
         </is>
       </c>
       <c r="Q37" t="inlineStr">
         <is>
-          <t>+998 99 993-69-47</t>
+          <t>+998 97 727 36 42</t>
         </is>
       </c>
       <c r="R37" t="inlineStr">
         <is>
-          <t>DILFUZA</t>
+          <t>NILUFAR</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>38</t>
+          <t>41</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>2025-05-12</t>
+          <t>2025-05-14</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Блок 3,2</t>
+          <t>Блок 1,2</t>
         </is>
       </c>
       <c r="D38" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E38" t="n">
-        <v>266</v>
+        <v>137</v>
       </c>
       <c r="F38" t="n">
         <v>1</v>
       </c>
       <c r="G38" t="n">
-        <v>25.04</v>
+        <v>34.66</v>
       </c>
       <c r="H38" t="n">
-        <v>115184000</v>
+        <v>173300000</v>
       </c>
       <c r="I38" t="n">
-        <v>4600000</v>
+        <v>5000000</v>
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t>100</t>
+          <t>30</t>
         </is>
       </c>
       <c r="K38" t="n">
-        <v>115184000</v>
+        <v>51990000</v>
       </c>
       <c r="L38" t="inlineStr">
         <is>
-          <t>XAMIDULLAYEV ASADBEK SHERXON O'G'LI</t>
+          <t>XODJAYEVA FERUZA SAYDULLAYEVNA</t>
         </is>
       </c>
       <c r="M38" t="inlineStr">
         <is>
-          <t>AC2489461</t>
+          <t>AD7157367</t>
         </is>
       </c>
       <c r="N38" t="inlineStr">
         <is>
-          <t>51711036060037</t>
+          <t>41211703930016</t>
         </is>
       </c>
       <c r="O38" t="inlineStr">
         <is>
-          <t>SAMARQAND VILOYATI KATTAQO'RG'ON TUMANI IIB</t>
+          <t>IIV 27419</t>
         </is>
       </c>
       <c r="P38" t="inlineStr">
         <is>
-          <t>SAMARQAND VILOYATI KATTAQO'RG'ON TUMANI KATTA KO'RPA KO'CHASI 2-UY</t>
+          <t>TOSHKENT VILOYATI CHIRCHIQ SHAHAR 9-KICHIK NOHIYA 25A-UY 16-XONADON</t>
         </is>
       </c>
       <c r="Q38" t="inlineStr">
         <is>
-          <t>+998 97 727 36 42</t>
+          <t>+998 90 011 18 54</t>
         </is>
       </c>
       <c r="R38" t="inlineStr">
         <is>
-          <t>NILUFAR</t>
+          <t>DILFUZA</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>39</t>
+          <t>42</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>2025-05-12</t>
+          <t>2025-05-14</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Блок 3,2</t>
+          <t>Блок 3,1</t>
         </is>
       </c>
       <c r="D39" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="E39" t="n">
-        <v>265</v>
+        <v>244</v>
       </c>
       <c r="F39" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G39" t="n">
-        <v>57.77</v>
+        <v>44.28</v>
       </c>
       <c r="H39" t="n">
-        <v>288850000</v>
+        <v>212544000</v>
       </c>
       <c r="I39" t="n">
-        <v>5000000</v>
+        <v>4800000</v>
       </c>
       <c r="J39" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>30</t>
         </is>
       </c>
       <c r="K39" t="n">
-        <v>144425000</v>
+        <v>63763200</v>
       </c>
       <c r="L39" t="inlineStr">
         <is>
-          <t>XAMIDULLAYEV ASADBEK SHERXON O'G'LI</t>
+          <t>MANAPOV MURODJON DILSHOD O`G`LI</t>
         </is>
       </c>
       <c r="M39" t="inlineStr">
         <is>
-          <t>AC2489461</t>
+          <t>AB0744993</t>
         </is>
       </c>
       <c r="N39" t="inlineStr">
         <is>
-          <t>51711036060037</t>
+          <t>32005930470081</t>
         </is>
       </c>
       <c r="O39" t="inlineStr">
         <is>
-          <t>SAMARQAND VILOYATI KATTAQO'RG'ON TUMANI IIB</t>
+          <t>TOSHKENT VILOYATI CHIRCHIQ SHAHAR IIB</t>
         </is>
       </c>
       <c r="P39" t="inlineStr">
         <is>
-          <t>SAMARQAND VILOYATI KATTAQO'RG'ON TUMANI KATTA KO'RPA KO'CHASI 2-UY</t>
+          <t>CHIRCHIQ SHAHAR G`ALABA M.F.Y G`ALABA KO`CHASI 17-UY 33-XONADON</t>
         </is>
       </c>
       <c r="Q39" t="inlineStr">
         <is>
-          <t>+998 97 727 36 42</t>
+          <t xml:space="preserve">+998 95 647-70-07 </t>
         </is>
       </c>
       <c r="R39" t="inlineStr">
         <is>
-          <t>NILUFAR</t>
+          <t>DILFUZA</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>41</t>
+          <t>43</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>2025-05-14</t>
+          <t>2025-05-15</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Блок 1,2</t>
+          <t>Блок-1</t>
         </is>
       </c>
       <c r="D40" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E40" t="n">
-        <v>137</v>
+        <v>39</v>
       </c>
       <c r="F40" t="n">
         <v>1</v>
       </c>
       <c r="G40" t="n">
-        <v>34.66</v>
+        <v>47.91</v>
       </c>
       <c r="H40" t="n">
-        <v>173300000</v>
+        <v>229968000</v>
       </c>
       <c r="I40" t="n">
-        <v>5000000</v>
+        <v>4800000</v>
       </c>
       <c r="J40" t="inlineStr">
         <is>
@@ -3518,21 +3518,21 @@
         </is>
       </c>
       <c r="K40" t="n">
-        <v>51990000</v>
+        <v>68990400</v>
       </c>
       <c r="L40" t="inlineStr">
         <is>
-          <t>XODJAYEVA FERUZA SAYDULLAYEVNA</t>
+          <t>RUSTAMKULOV DILSHOD MANAPOVICH</t>
         </is>
       </c>
       <c r="M40" t="inlineStr">
         <is>
-          <t>AD7157367</t>
+          <t>AD6024587</t>
         </is>
       </c>
       <c r="N40" t="inlineStr">
         <is>
-          <t>41211703930016</t>
+          <t>33001696860048</t>
         </is>
       </c>
       <c r="O40" t="inlineStr">
@@ -3542,50 +3542,50 @@
       </c>
       <c r="P40" t="inlineStr">
         <is>
-          <t>TOSHKENT VILOYATI CHIRCHIQ SHAHAR 9-KICHIK NOHIYA 25A-UY 16-XONADON</t>
+          <t>TOSHKENT VILOYATI CHIRCHIQ SHAHAR G'ALABA MFY G'ALABA KO'CHASI 14-UY 33-XONADON</t>
         </is>
       </c>
       <c r="Q40" t="inlineStr">
         <is>
-          <t>+998 90 011 18 54</t>
+          <t>+998 99 000 25 60</t>
         </is>
       </c>
       <c r="R40" t="inlineStr">
         <is>
-          <t>DILFUZA</t>
+          <t>NILUFAR</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>42</t>
+          <t>44</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>2025-05-14</t>
+          <t>2025-05-15</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Блок 3,1</t>
+          <t>Блок-1</t>
         </is>
       </c>
       <c r="D41" t="n">
         <v>5</v>
       </c>
       <c r="E41" t="n">
-        <v>244</v>
+        <v>38</v>
       </c>
       <c r="F41" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G41" t="n">
-        <v>44.28</v>
+        <v>47.91</v>
       </c>
       <c r="H41" t="n">
-        <v>212544000</v>
+        <v>229968000</v>
       </c>
       <c r="I41" t="n">
         <v>4800000</v>
@@ -3596,74 +3596,74 @@
         </is>
       </c>
       <c r="K41" t="n">
-        <v>63763200</v>
+        <v>68990400</v>
       </c>
       <c r="L41" t="inlineStr">
         <is>
-          <t>MANAPOV MURODJON DILSHOD O`G`LI</t>
+          <t>RUSTAMKULOV DILSHOD MANAPOVICH</t>
         </is>
       </c>
       <c r="M41" t="inlineStr">
         <is>
-          <t>AB0744993</t>
+          <t>AD6024587</t>
         </is>
       </c>
       <c r="N41" t="inlineStr">
         <is>
-          <t>32005930470081</t>
+          <t>33001696860048</t>
         </is>
       </c>
       <c r="O41" t="inlineStr">
         <is>
-          <t>TOSHKENT VILOYATI CHIRCHIQ SHAHAR IIB</t>
+          <t>IIV 27419</t>
         </is>
       </c>
       <c r="P41" t="inlineStr">
         <is>
-          <t>CHIRCHIQ SHAHAR G`ALABA M.F.Y G`ALABA KO`CHASI 17-UY 33-XONADON</t>
+          <t>TOSHKENT VILOYATI CHIRCHIQ SHAHAR G'ALABA MFY G'ALABA KO'CHASI 14-UY 33-XONADON</t>
         </is>
       </c>
       <c r="Q41" t="inlineStr">
         <is>
-          <t xml:space="preserve">+998 95 647-70-07 </t>
+          <t>+998 99 000 25 60</t>
         </is>
       </c>
       <c r="R41" t="inlineStr">
         <is>
-          <t>DILFUZA</t>
+          <t>NILUFAR</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>43</t>
+          <t>45</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>2025-05-15</t>
+          <t>2025-05-16</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Блок-1</t>
+          <t>Блок 3,2</t>
         </is>
       </c>
       <c r="D42" t="n">
         <v>5</v>
       </c>
       <c r="E42" t="n">
-        <v>39</v>
+        <v>274</v>
       </c>
       <c r="F42" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G42" t="n">
-        <v>47.91</v>
+        <v>44.28</v>
       </c>
       <c r="H42" t="n">
-        <v>229968000</v>
+        <v>212544000</v>
       </c>
       <c r="I42" t="n">
         <v>4800000</v>
@@ -3674,155 +3674,155 @@
         </is>
       </c>
       <c r="K42" t="n">
-        <v>68990400</v>
+        <v>63763200</v>
       </c>
       <c r="L42" t="inlineStr">
         <is>
-          <t>RUSTAMKULOV DILSHOD MANAPOVICH</t>
+          <t>ATEMKULOV MURAT ORINBASAROVICH</t>
         </is>
       </c>
       <c r="M42" t="inlineStr">
         <is>
-          <t>AD6024587</t>
+          <t>AC2593883</t>
         </is>
       </c>
       <c r="N42" t="inlineStr">
         <is>
-          <t>33001696860048</t>
+          <t>32903920500010</t>
         </is>
       </c>
       <c r="O42" t="inlineStr">
         <is>
-          <t>IIV 27419</t>
+          <t>TOSHKENT VILOYATI BO`STONLIQ TUMANI</t>
         </is>
       </c>
       <c r="P42" t="inlineStr">
         <is>
-          <t>TOSHKENT VILOYATI CHIRCHIQ SHAHAR G'ALABA MFY G'ALABA KO'CHASI 14-UY 33-XONADON</t>
+          <t>TOSHKENT VILOYATI BO`STONLIQ TUMANI OZODBOSH BERUNIY KO`CHASI 56</t>
         </is>
       </c>
       <c r="Q42" t="inlineStr">
         <is>
-          <t>+998 99 000 25 60</t>
+          <t>+998 99 400 20 01</t>
         </is>
       </c>
       <c r="R42" t="inlineStr">
         <is>
-          <t>NILUFAR</t>
+          <t>DILFUZA</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>44</t>
+          <t>46</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>2025-05-15</t>
+          <t>2025-05-18</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Блок-1</t>
+          <t>Блок-1,1</t>
         </is>
       </c>
       <c r="D43" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E43" t="n">
-        <v>38</v>
+        <v>68</v>
       </c>
       <c r="F43" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G43" t="n">
-        <v>47.91</v>
+        <v>50.34</v>
       </c>
       <c r="H43" t="n">
-        <v>229968000</v>
+        <v>221496000</v>
       </c>
       <c r="I43" t="n">
-        <v>4800000</v>
+        <v>4400000</v>
       </c>
       <c r="J43" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>100</t>
         </is>
       </c>
       <c r="K43" t="n">
-        <v>68990400</v>
+        <v>221496000</v>
       </c>
       <c r="L43" t="inlineStr">
         <is>
-          <t>RUSTAMKULOV DILSHOD MANAPOVICH</t>
+          <t xml:space="preserve">ABDUVALIYEV SANJAR SODIQOVICH </t>
         </is>
       </c>
       <c r="M43" t="inlineStr">
         <is>
-          <t>AD6024587</t>
+          <t>AD9447749</t>
         </is>
       </c>
       <c r="N43" t="inlineStr">
         <is>
-          <t>33001696860048</t>
+          <t>32110840510041</t>
         </is>
       </c>
       <c r="O43" t="inlineStr">
         <is>
-          <t>IIV 27419</t>
+          <t>IIV 27419 18.11.2024</t>
         </is>
       </c>
       <c r="P43" t="inlineStr">
         <is>
-          <t>TOSHKENT VILOYATI CHIRCHIQ SHAHAR G'ALABA MFY G'ALABA KO'CHASI 14-UY 33-XONADON</t>
+          <t>TOSHKENT VILOYATI CHIRCHIQ SHAHAR SEMURG MFY 8 KICHIK NOXYA 8 UY 73 XONADON</t>
         </is>
       </c>
       <c r="Q43" t="inlineStr">
         <is>
-          <t>+998 99 000 25 60</t>
+          <t>+998900044109</t>
         </is>
       </c>
       <c r="R43" t="inlineStr">
         <is>
-          <t>NILUFAR</t>
+          <t>Фатима</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>45</t>
+          <t>47</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>2025-05-16</t>
+          <t>2025-05-18</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Блок 3,2</t>
+          <t>Блок 1,2</t>
         </is>
       </c>
       <c r="D44" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E44" t="n">
-        <v>274</v>
+        <v>133</v>
       </c>
       <c r="F44" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G44" t="n">
-        <v>44.28</v>
+        <v>34.66</v>
       </c>
       <c r="H44" t="n">
-        <v>212544000</v>
+        <v>173300000</v>
       </c>
       <c r="I44" t="n">
-        <v>4800000</v>
+        <v>5000000</v>
       </c>
       <c r="J44" t="inlineStr">
         <is>
@@ -3830,53 +3830,53 @@
         </is>
       </c>
       <c r="K44" t="n">
-        <v>63763200</v>
+        <v>51990000</v>
       </c>
       <c r="L44" t="inlineStr">
         <is>
-          <t>ATEMKULOV MURAT ORINBASAROVICH</t>
+          <t>NAVROZOV SARVAR ALISHEROVICH</t>
         </is>
       </c>
       <c r="M44" t="inlineStr">
         <is>
-          <t>AC2593883</t>
+          <t>AD3743500</t>
         </is>
       </c>
       <c r="N44" t="inlineStr">
         <is>
-          <t>32903920500010</t>
+          <t>31607890191388</t>
         </is>
       </c>
       <c r="O44" t="inlineStr">
         <is>
-          <t>TOSHKENT VILOYATI BO`STONLIQ TUMANI</t>
+          <t>23.06.2023</t>
         </is>
       </c>
       <c r="P44" t="inlineStr">
         <is>
-          <t>TOSHKENT VILOYATI BO`STONLIQ TUMANI OZODBOSH BERUNIY KO`CHASI 56</t>
+          <t>TOSHKENT SHAHAR YUNUSOBOD TUMANI CHINOBOD KOCHASI 8 UY 51 XONADON</t>
         </is>
       </c>
       <c r="Q44" t="inlineStr">
         <is>
-          <t>+998 99 400 20 01</t>
+          <t>+998909003004 +998339005009</t>
         </is>
       </c>
       <c r="R44" t="inlineStr">
         <is>
-          <t>DILFUZA</t>
+          <t>AZIZ</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>46</t>
+          <t>49</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>2025-05-18</t>
+          <t>2025-05-20</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -3885,166 +3885,166 @@
         </is>
       </c>
       <c r="D45" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E45" t="n">
-        <v>68</v>
+        <v>56</v>
       </c>
       <c r="F45" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G45" t="n">
-        <v>50.34</v>
+        <v>34.66</v>
       </c>
       <c r="H45" t="n">
-        <v>221496000</v>
+        <v>187164000</v>
       </c>
       <c r="I45" t="n">
-        <v>4400000</v>
+        <v>5400000</v>
       </c>
       <c r="J45" t="inlineStr">
         <is>
-          <t>100</t>
+          <t>30</t>
         </is>
       </c>
       <c r="K45" t="n">
-        <v>221496000</v>
+        <v>56149200</v>
       </c>
       <c r="L45" t="inlineStr">
         <is>
-          <t xml:space="preserve">ABDUVALIYEV SANJAR SODIQOVICH </t>
+          <t>XURRAMOV NURBEK SHOMURODOVICH</t>
         </is>
       </c>
       <c r="M45" t="inlineStr">
         <is>
-          <t>AD9447749</t>
+          <t>AD1546754</t>
         </is>
       </c>
       <c r="N45" t="inlineStr">
         <is>
-          <t>32110840510041</t>
+          <t>30404842600050</t>
         </is>
       </c>
       <c r="O45" t="inlineStr">
         <is>
-          <t>IIV 27419 18.11.2024</t>
+          <t>IIV  14.07.2022</t>
         </is>
       </c>
       <c r="P45" t="inlineStr">
         <is>
-          <t>TOSHKENT VILOYATI CHIRCHIQ SHAHAR SEMURG MFY 8 KICHIK NOXYA 8 UY 73 XONADON</t>
+          <t>TOSHKENT SHAHAR MIRZO ULUGBEK TUMANI ZAKOVAT MFY FAROVON HAYOT2 KUCHASI 1A UY</t>
         </is>
       </c>
       <c r="Q45" t="inlineStr">
         <is>
-          <t>+998900044109</t>
+          <t>+998882021984</t>
         </is>
       </c>
       <c r="R45" t="inlineStr">
         <is>
-          <t>Фатима</t>
+          <t>AZIZ</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>47</t>
+          <t>52</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>2025-05-18</t>
+          <t>2025-05-22</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Блок 1,2</t>
+          <t>Блок-1,1</t>
         </is>
       </c>
       <c r="D46" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E46" t="n">
-        <v>133</v>
+        <v>60</v>
       </c>
       <c r="F46" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G46" t="n">
-        <v>34.66</v>
+        <v>50.34</v>
       </c>
       <c r="H46" t="n">
-        <v>173300000</v>
+        <v>231564000</v>
       </c>
       <c r="I46" t="n">
-        <v>5000000</v>
+        <v>4600000</v>
       </c>
       <c r="J46" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>100</t>
         </is>
       </c>
       <c r="K46" t="n">
-        <v>51990000</v>
+        <v>231564000</v>
       </c>
       <c r="L46" t="inlineStr">
         <is>
-          <t>NAVROZOV SARVAR ALISHEROVICH</t>
+          <t>YUSUPOVA NAFISA  AXMADJANOVNA</t>
         </is>
       </c>
       <c r="M46" t="inlineStr">
         <is>
-          <t>AD3743500</t>
+          <t>AB3354407</t>
         </is>
       </c>
       <c r="N46" t="inlineStr">
         <is>
-          <t>31607890191388</t>
+          <t>309242003836860031</t>
         </is>
       </c>
       <c r="O46" t="inlineStr">
         <is>
-          <t>23.06.2023</t>
+          <t>TOSHKENT  VILOYATI CHIRCHIQ SHAHAR IIB 10.03.2016</t>
         </is>
       </c>
       <c r="P46" t="inlineStr">
         <is>
-          <t>TOSHKENT SHAHAR YUNUSOBOD TUMANI CHINOBOD KOCHASI 8 UY 51 XONADON</t>
+          <t>TOSHKENT  VILOYATI CHIRCHIQ SHAHAR 8 KICHIK NOXYA 10 UY 38 XONADON</t>
         </is>
       </c>
       <c r="Q46" t="inlineStr">
         <is>
-          <t>+998909003004 +998339005009</t>
+          <t>+998880133833</t>
         </is>
       </c>
       <c r="R46" t="inlineStr">
         <is>
-          <t>AZIZ</t>
+          <t>Aziz</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>49</t>
+          <t>53</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>2025-05-20</t>
+          <t>2025-05-22</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Блок-1,1</t>
+          <t>Блок 1,2</t>
         </is>
       </c>
       <c r="D47" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E47" t="n">
-        <v>56</v>
+        <v>140</v>
       </c>
       <c r="F47" t="n">
         <v>1</v>
@@ -4053,47 +4053,47 @@
         <v>34.66</v>
       </c>
       <c r="H47" t="n">
-        <v>187164000</v>
+        <v>152504000</v>
       </c>
       <c r="I47" t="n">
-        <v>5400000</v>
+        <v>4400000</v>
       </c>
       <c r="J47" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>100</t>
         </is>
       </c>
       <c r="K47" t="n">
-        <v>56149200</v>
+        <v>152504000</v>
       </c>
       <c r="L47" t="inlineStr">
         <is>
-          <t>XURRAMOV NURBEK SHOMURODOVICH</t>
+          <t>SOBIROV ABDULLA FATXILLA OGLI</t>
         </is>
       </c>
       <c r="M47" t="inlineStr">
         <is>
-          <t>AD1546754</t>
+          <t>AC0807821</t>
         </is>
       </c>
       <c r="N47" t="inlineStr">
         <is>
-          <t>30404842600050</t>
+          <t>33011940560028</t>
         </is>
       </c>
       <c r="O47" t="inlineStr">
         <is>
-          <t>IIV  14.07.2022</t>
+          <t>TOSHKENT VILOYATI CHIRCHIQ SHAHAR IIB 21.08.2018</t>
         </is>
       </c>
       <c r="P47" t="inlineStr">
         <is>
-          <t>TOSHKENT SHAHAR MIRZO ULUGBEK TUMANI ZAKOVAT MFY FAROVON HAYOT2 KUCHASI 1A UY</t>
+          <t>TOSHKENT VILOYATI CHIRCHIQ 8 KICHIK NOXIYA 36 UY 14 XONADON</t>
         </is>
       </c>
       <c r="Q47" t="inlineStr">
         <is>
-          <t>+998882021984</t>
+          <t>+998909099101</t>
         </is>
       </c>
       <c r="R47" t="inlineStr">
@@ -4105,151 +4105,151 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>52</t>
+          <t>54</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>2025-05-22</t>
+          <t>2025-05-23</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Блок-1,1</t>
+          <t>Блок 3</t>
         </is>
       </c>
       <c r="D48" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="E48" t="n">
-        <v>60</v>
+        <v>214</v>
       </c>
       <c r="F48" t="n">
         <v>2</v>
       </c>
       <c r="G48" t="n">
-        <v>50.34</v>
+        <v>44.28</v>
       </c>
       <c r="H48" t="n">
-        <v>231564000</v>
+        <v>194832000</v>
       </c>
       <c r="I48" t="n">
-        <v>4600000</v>
+        <v>4400000</v>
       </c>
       <c r="J48" t="inlineStr">
         <is>
-          <t>100</t>
+          <t>70</t>
         </is>
       </c>
       <c r="K48" t="n">
-        <v>231564000</v>
+        <v>136382400</v>
       </c>
       <c r="L48" t="inlineStr">
         <is>
-          <t>YUSUPOVA NAFISA  AXMADJANOVNA</t>
+          <t xml:space="preserve">BABADJANOVA ANGELA BATIRALIYEVNA </t>
         </is>
       </c>
       <c r="M48" t="inlineStr">
         <is>
-          <t>AB3354407</t>
+          <t>AD4481939</t>
         </is>
       </c>
       <c r="N48" t="inlineStr">
         <is>
-          <t>309242003836860031</t>
+          <t>40511880470048</t>
         </is>
       </c>
       <c r="O48" t="inlineStr">
         <is>
-          <t>TOSHKENT  VILOYATI CHIRCHIQ SHAHAR IIB 10.03.2016</t>
+          <t>IIV 60120 04.09.2023</t>
         </is>
       </c>
       <c r="P48" t="inlineStr">
         <is>
-          <t>TOSHKENT  VILOYATI CHIRCHIQ SHAHAR 8 KICHIK NOXYA 10 UY 38 XONADON</t>
+          <t>TOSHKENT VILOYATI CHIRCHIQ SHAHAR GULZOR MFY SUGDIYONA KUCHASI 8 UY</t>
         </is>
       </c>
       <c r="Q48" t="inlineStr">
         <is>
-          <t>+998880133833</t>
+          <t>+998936169555</t>
         </is>
       </c>
       <c r="R48" t="inlineStr">
         <is>
-          <t>Aziz</t>
+          <t>AZIZ</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>53</t>
+          <t>55</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>2025-05-22</t>
+          <t>2025-05-23</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Блок 1,2</t>
+          <t>Блок-1</t>
         </is>
       </c>
       <c r="D49" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E49" t="n">
-        <v>140</v>
+        <v>12</v>
       </c>
       <c r="F49" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G49" t="n">
-        <v>34.66</v>
+        <v>50.34</v>
       </c>
       <c r="H49" t="n">
-        <v>152504000</v>
+        <v>271836000</v>
       </c>
       <c r="I49" t="n">
-        <v>4400000</v>
+        <v>5400000</v>
       </c>
       <c r="J49" t="inlineStr">
         <is>
-          <t>100</t>
+          <t>30</t>
         </is>
       </c>
       <c r="K49" t="n">
-        <v>152504000</v>
+        <v>81550800</v>
       </c>
       <c r="L49" t="inlineStr">
         <is>
-          <t>SOBIROV ABDULLA FATXILLA OGLI</t>
+          <t>SODIKOV SARDOR TOSHKUVATOVICH</t>
         </is>
       </c>
       <c r="M49" t="inlineStr">
         <is>
-          <t>AC0807821</t>
+          <t>AB0229238</t>
         </is>
       </c>
       <c r="N49" t="inlineStr">
         <is>
-          <t>33011940560028</t>
+          <t>32706862420013</t>
         </is>
       </c>
       <c r="O49" t="inlineStr">
         <is>
-          <t>TOSHKENT VILOYATI CHIRCHIQ SHAHAR IIB 21.08.2018</t>
+          <t>NAVOIY VILOYATI KARMANA TUMANI IIB</t>
         </is>
       </c>
       <c r="P49" t="inlineStr">
         <is>
-          <t>TOSHKENT VILOYATI CHIRCHIQ 8 KICHIK NOXIYA 36 UY 14 XONADON</t>
+          <t>TOSHKENT VILOYATI CHIRCHIQ SHAHAR XUMO MFY 8 KICHIK NOXYA 35 UY 31 XONADON</t>
         </is>
       </c>
       <c r="Q49" t="inlineStr">
         <is>
-          <t>+998909099101</t>
+          <t>+998936634497</t>
         </is>
       </c>
       <c r="R49" t="inlineStr">
@@ -4261,7 +4261,7 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>54</t>
+          <t>56</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -4275,59 +4275,59 @@
         </is>
       </c>
       <c r="D50" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E50" t="n">
-        <v>214</v>
+        <v>207</v>
       </c>
       <c r="F50" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G50" t="n">
-        <v>44.28</v>
+        <v>55.67</v>
       </c>
       <c r="H50" t="n">
-        <v>194832000</v>
+        <v>278350000</v>
       </c>
       <c r="I50" t="n">
-        <v>4400000</v>
+        <v>5000000</v>
       </c>
       <c r="J50" t="inlineStr">
         <is>
-          <t>70</t>
+          <t>30</t>
         </is>
       </c>
       <c r="K50" t="n">
-        <v>136382400</v>
+        <v>83505000</v>
       </c>
       <c r="L50" t="inlineStr">
         <is>
-          <t xml:space="preserve">BABADJANOVA ANGELA BATIRALIYEVNA </t>
+          <t>ABDUXOLIQOV FARRUX FARHOD OGLI</t>
         </is>
       </c>
       <c r="M50" t="inlineStr">
         <is>
-          <t>AD4481939</t>
+          <t>AD6688630</t>
         </is>
       </c>
       <c r="N50" t="inlineStr">
         <is>
-          <t>40511880470048</t>
+          <t>32210900840063</t>
         </is>
       </c>
       <c r="O50" t="inlineStr">
         <is>
-          <t>IIV 60120 04.09.2023</t>
+          <t>IIV 27419 02.04.2024</t>
         </is>
       </c>
       <c r="P50" t="inlineStr">
         <is>
-          <t>TOSHKENT VILOYATI CHIRCHIQ SHAHAR GULZOR MFY SUGDIYONA KUCHASI 8 UY</t>
+          <t>TOSHKENT VILOYATI CHIRCHIQ SHAHAR ADOLAT MFY 9 KICHIK NOXYA 36 UY 17 XONADON</t>
         </is>
       </c>
       <c r="Q50" t="inlineStr">
         <is>
-          <t>+998936169555</t>
+          <t>+998917777229</t>
         </is>
       </c>
       <c r="R50" t="inlineStr">
@@ -4339,102 +4339,102 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>55</t>
+          <t>57</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>2025-05-23</t>
+          <t>2025-05-24</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Блок-1</t>
+          <t>Блок-1,1</t>
         </is>
       </c>
       <c r="D51" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E51" t="n">
-        <v>12</v>
+        <v>61</v>
       </c>
       <c r="F51" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G51" t="n">
-        <v>50.34</v>
+        <v>34.66</v>
       </c>
       <c r="H51" t="n">
-        <v>271836000</v>
+        <v>173300000</v>
       </c>
       <c r="I51" t="n">
-        <v>5400000</v>
+        <v>5000000</v>
       </c>
       <c r="J51" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>50</t>
         </is>
       </c>
       <c r="K51" t="n">
-        <v>81550800</v>
+        <v>86650000</v>
       </c>
       <c r="L51" t="inlineStr">
         <is>
-          <t>SODIKOV SARDOR TOSHKUVATOVICH</t>
+          <t>BOBODUSTOV SHOHZOD ZOKIR O`G`LI</t>
         </is>
       </c>
       <c r="M51" t="inlineStr">
         <is>
-          <t>AB0229238</t>
+          <t>AB3768763</t>
         </is>
       </c>
       <c r="N51" t="inlineStr">
         <is>
-          <t>32706862420013</t>
+          <t>30110985640034</t>
         </is>
       </c>
       <c r="O51" t="inlineStr">
         <is>
-          <t>NAVOIY VILOYATI KARMANA TUMANI IIB</t>
+          <t>QASHQADARYO VILOYATI CHIROQCHI TIIB</t>
         </is>
       </c>
       <c r="P51" t="inlineStr">
         <is>
-          <t>TOSHKENT VILOYATI CHIRCHIQ SHAHAR XUMO MFY 8 KICHIK NOXYA 35 UY 31 XONADON</t>
+          <t>QASHQADARYO VILOYATI CHIROQCHI TUMANI BESHCHASHMA QMB PAST UYSHUN 666-XONADON</t>
         </is>
       </c>
       <c r="Q51" t="inlineStr">
         <is>
-          <t>+998936634497</t>
+          <t>+998 93 958-89-98</t>
         </is>
       </c>
       <c r="R51" t="inlineStr">
         <is>
-          <t>AZIZ</t>
+          <t>DILFUZA</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>56</t>
+          <t>58</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>2025-05-23</t>
+          <t>2025-05-25</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Блок 3</t>
+          <t>Блок 3,1</t>
         </is>
       </c>
       <c r="D52" t="n">
         <v>4</v>
       </c>
       <c r="E52" t="n">
-        <v>207</v>
+        <v>237</v>
       </c>
       <c r="F52" t="n">
         <v>3</v>
@@ -4443,88 +4443,88 @@
         <v>55.67</v>
       </c>
       <c r="H52" t="n">
-        <v>278350000</v>
+        <v>267216000</v>
       </c>
       <c r="I52" t="n">
-        <v>5000000</v>
+        <v>4800000</v>
       </c>
       <c r="J52" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>50</t>
         </is>
       </c>
       <c r="K52" t="n">
-        <v>83505000</v>
+        <v>133608000</v>
       </c>
       <c r="L52" t="inlineStr">
         <is>
-          <t>ABDUXOLIQOV FARRUX FARHOD OGLI</t>
+          <t>NORMATOVA KAMOLA YULDASHEVNA</t>
         </is>
       </c>
       <c r="M52" t="inlineStr">
         <is>
-          <t>AD6688630</t>
+          <t>AD7797320</t>
         </is>
       </c>
       <c r="N52" t="inlineStr">
         <is>
-          <t>32210900840063</t>
+          <t>41008891520022</t>
         </is>
       </c>
       <c r="O52" t="inlineStr">
         <is>
-          <t>IIV 27419 02.04.2024</t>
+          <t>IIV 26296 09.072024</t>
         </is>
       </c>
       <c r="P52" t="inlineStr">
         <is>
-          <t>TOSHKENT VILOYATI CHIRCHIQ SHAHAR ADOLAT MFY 9 KICHIK NOXYA 36 UY 17 XONADON</t>
+          <t>TOSHKENT SHAHAR MIRZO ULUGBEK TUMANI  FERUZA KUCHASI 51 UY 39 XONADON</t>
         </is>
       </c>
       <c r="Q52" t="inlineStr">
         <is>
-          <t>+998917777229</t>
+          <t>+998970021416</t>
         </is>
       </c>
       <c r="R52" t="inlineStr">
         <is>
-          <t>AZIZ</t>
+          <t>Руководство</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>57</t>
+          <t>59</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>2025-05-24</t>
+          <t>2025-05-26</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Блок-1,1</t>
+          <t>Блок 3</t>
         </is>
       </c>
       <c r="D53" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E53" t="n">
-        <v>61</v>
+        <v>208</v>
       </c>
       <c r="F53" t="n">
         <v>1</v>
       </c>
       <c r="G53" t="n">
-        <v>34.66</v>
+        <v>44.28</v>
       </c>
       <c r="H53" t="n">
-        <v>173300000</v>
+        <v>212544000</v>
       </c>
       <c r="I53" t="n">
-        <v>5000000</v>
+        <v>4800000</v>
       </c>
       <c r="J53" t="inlineStr">
         <is>
@@ -4532,365 +4532,365 @@
         </is>
       </c>
       <c r="K53" t="n">
-        <v>86650000</v>
+        <v>106272000</v>
       </c>
       <c r="L53" t="inlineStr">
         <is>
-          <t>BOBODUSTOV SHOHZOD ZOKIR O`G`LI</t>
+          <t>FAYZULLAYEV HAYOT DILMURODOVICH</t>
         </is>
       </c>
       <c r="M53" t="inlineStr">
         <is>
-          <t>AB3768763</t>
+          <t>AD5839429</t>
         </is>
       </c>
       <c r="N53" t="inlineStr">
         <is>
-          <t>30110985640034</t>
+          <t>31612930470051</t>
         </is>
       </c>
       <c r="O53" t="inlineStr">
         <is>
-          <t>QASHQADARYO VILOYATI CHIROQCHI TIIB</t>
+          <t>IIV 27419 20.01.2024</t>
         </is>
       </c>
       <c r="P53" t="inlineStr">
         <is>
-          <t>QASHQADARYO VILOYATI CHIROQCHI TUMANI BESHCHASHMA QMB PAST UYSHUN 666-XONADON</t>
+          <t>TOSHKENT  VILOYATI CHIRCHIQ SHAHAR GALABA KUCHASI 16 UY 31 XONADON</t>
         </is>
       </c>
       <c r="Q53" t="inlineStr">
         <is>
-          <t>+998 93 958-89-98</t>
+          <t>917756969</t>
         </is>
       </c>
       <c r="R53" t="inlineStr">
         <is>
-          <t>DILFUZA</t>
+          <t>РУКОВОДССТВО</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>58</t>
+          <t>60</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>2025-05-25</t>
+          <t>2025-05-26</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Блок 3,1</t>
+          <t>Блок-1</t>
         </is>
       </c>
       <c r="D54" t="n">
+        <v>1</v>
+      </c>
+      <c r="E54" t="n">
         <v>4</v>
       </c>
-      <c r="E54" t="n">
-        <v>237</v>
-      </c>
       <c r="F54" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G54" t="n">
-        <v>55.67</v>
+        <v>47.94</v>
       </c>
       <c r="H54" t="n">
-        <v>267216000</v>
+        <v>249288000</v>
       </c>
       <c r="I54" t="n">
-        <v>4800000</v>
+        <v>5200000</v>
       </c>
       <c r="J54" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>70</t>
         </is>
       </c>
       <c r="K54" t="n">
-        <v>133608000</v>
+        <v>174501600</v>
       </c>
       <c r="L54" t="inlineStr">
         <is>
-          <t>NORMATOVA KAMOLA YULDASHEVNA</t>
+          <t>KARGAPOLOVNA ELENA PETROVNA</t>
         </is>
       </c>
       <c r="M54" t="inlineStr">
         <is>
-          <t>AD7797320</t>
+          <t>AD8083373</t>
         </is>
       </c>
       <c r="N54" t="inlineStr">
         <is>
-          <t>41008891520022</t>
+          <t>40907936860013</t>
         </is>
       </c>
       <c r="O54" t="inlineStr">
         <is>
-          <t>IIV 26296 09.072024</t>
+          <t>IIV 27419 01.08.2024</t>
         </is>
       </c>
       <c r="P54" t="inlineStr">
         <is>
-          <t>TOSHKENT SHAHAR MIRZO ULUGBEK TUMANI  FERUZA KUCHASI 51 UY 39 XONADON</t>
+          <t>TOSHKENT VILOYATI CHIRCHIQ SHAHAR  OKRUJNAYA KUCHASI 33A XONADON</t>
         </is>
       </c>
       <c r="Q54" t="inlineStr">
         <is>
-          <t>+998970021416</t>
+          <t>+998998288286</t>
         </is>
       </c>
       <c r="R54" t="inlineStr">
         <is>
-          <t>Руководство</t>
+          <t>РУКОВОДССТВО</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>59</t>
+          <t>61</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>2025-05-26</t>
+          <t>2025-05-27</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Блок 3</t>
+          <t>Блок 1,2</t>
         </is>
       </c>
       <c r="D55" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E55" t="n">
-        <v>208</v>
+        <v>128</v>
       </c>
       <c r="F55" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G55" t="n">
-        <v>44.28</v>
+        <v>50.34</v>
       </c>
       <c r="H55" t="n">
-        <v>212544000</v>
+        <v>251700000</v>
       </c>
       <c r="I55" t="n">
-        <v>4800000</v>
+        <v>5000000</v>
       </c>
       <c r="J55" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>70</t>
         </is>
       </c>
       <c r="K55" t="n">
-        <v>106272000</v>
+        <v>176190000</v>
       </c>
       <c r="L55" t="inlineStr">
         <is>
-          <t>FAYZULLAYEV HAYOT DILMURODOVICH</t>
+          <t>XAYTBAYEVA FARIDA TOSHTEMIROVNA</t>
         </is>
       </c>
       <c r="M55" t="inlineStr">
         <is>
-          <t>AD5839429</t>
+          <t>AD1665555</t>
         </is>
       </c>
       <c r="N55" t="inlineStr">
         <is>
-          <t>31612930470051</t>
+          <t>40110876860018</t>
         </is>
       </c>
       <c r="O55" t="inlineStr">
         <is>
-          <t>IIV 27419 20.01.2024</t>
+          <t>IIV 27419 17.08.2022</t>
         </is>
       </c>
       <c r="P55" t="inlineStr">
         <is>
-          <t>TOSHKENT  VILOYATI CHIRCHIQ SHAHAR GALABA KUCHASI 16 UY 31 XONADON</t>
+          <t>TOSHKENT VILOYATI CHIRCHIQ SHAHAR 8 KICHIK NOXYA 2 UY 75 XONADON</t>
         </is>
       </c>
       <c r="Q55" t="inlineStr">
         <is>
-          <t>917756969</t>
+          <t>+998917763438</t>
         </is>
       </c>
       <c r="R55" t="inlineStr">
         <is>
-          <t>РУКОВОДССТВО</t>
+          <t>MIKHAIL</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>60</t>
+          <t>62</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>2025-05-26</t>
+          <t>2025-05-30</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Блок-1</t>
+          <t>Блок-1,1</t>
         </is>
       </c>
       <c r="D56" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E56" t="n">
-        <v>4</v>
+        <v>53</v>
       </c>
       <c r="F56" t="n">
         <v>1</v>
       </c>
       <c r="G56" t="n">
-        <v>47.94</v>
+        <v>34.66</v>
       </c>
       <c r="H56" t="n">
-        <v>249288000</v>
+        <v>194096000</v>
       </c>
       <c r="I56" t="n">
-        <v>5200000</v>
+        <v>5600000</v>
       </c>
       <c r="J56" t="inlineStr">
         <is>
-          <t>70</t>
+          <t>30</t>
         </is>
       </c>
       <c r="K56" t="n">
-        <v>174501600</v>
+        <v>58228800</v>
       </c>
       <c r="L56" t="inlineStr">
         <is>
-          <t>KARGAPOLOVNA ELENA PETROVNA</t>
+          <t>RAXMANOV JAVOHIR AHMAD O'G'LI</t>
         </is>
       </c>
       <c r="M56" t="inlineStr">
         <is>
-          <t>AD8083373</t>
+          <t>AB4145338</t>
         </is>
       </c>
       <c r="N56" t="inlineStr">
         <is>
-          <t>40907936860013</t>
+          <t>33005975630050</t>
         </is>
       </c>
       <c r="O56" t="inlineStr">
         <is>
-          <t>IIV 27419 01.08.2024</t>
+          <t>10.06.2016 КАМАШИНСКИЙ РОВД, КАШКАДАРЬИНСКОЙ ОБЛАСТИ</t>
         </is>
       </c>
       <c r="P56" t="inlineStr">
         <is>
-          <t>TOSHKENT VILOYATI CHIRCHIQ SHAHAR  OKRUJNAYA KUCHASI 33A XONADON</t>
+          <t>Qashqadaryo viloyati Qamashi tumani Gʻishtli MFY 102- uy</t>
         </is>
       </c>
       <c r="Q56" t="inlineStr">
         <is>
-          <t>+998998288286</t>
+          <t>+998946699007</t>
         </is>
       </c>
       <c r="R56" t="inlineStr">
         <is>
-          <t>РУКОВОДССТВО</t>
+          <t>AZIZ</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>61</t>
+          <t>64</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>2025-05-27</t>
+          <t>2025-05-31</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Блок 1,2</t>
+          <t>Блок 3,1</t>
         </is>
       </c>
       <c r="D57" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E57" t="n">
-        <v>128</v>
+        <v>238</v>
       </c>
       <c r="F57" t="n">
         <v>2</v>
       </c>
       <c r="G57" t="n">
-        <v>50.34</v>
+        <v>44.28</v>
       </c>
       <c r="H57" t="n">
-        <v>251700000</v>
+        <v>221400000</v>
       </c>
       <c r="I57" t="n">
         <v>5000000</v>
       </c>
       <c r="J57" t="inlineStr">
         <is>
-          <t>70</t>
+          <t>50</t>
         </is>
       </c>
       <c r="K57" t="n">
-        <v>176190000</v>
+        <v>110700000</v>
       </c>
       <c r="L57" t="inlineStr">
         <is>
-          <t>XAYTBAYEVA FARIDA TOSHTEMIROVNA</t>
+          <t>MAXMUDOVA GULNUR ABDUMUTAL QIZI</t>
         </is>
       </c>
       <c r="M57" t="inlineStr">
         <is>
-          <t>AD1665555</t>
+          <t>AD3854467</t>
         </is>
       </c>
       <c r="N57" t="inlineStr">
         <is>
-          <t>40110876860018</t>
+          <t>41810966780046</t>
         </is>
       </c>
       <c r="O57" t="inlineStr">
         <is>
-          <t>IIV 27419 17.08.2022</t>
+          <t>IIV 27248</t>
         </is>
       </c>
       <c r="P57" t="inlineStr">
         <is>
-          <t>TOSHKENT VILOYATI CHIRCHIQ SHAHAR 8 KICHIK NOXYA 2 UY 75 XONADON</t>
+          <t>TOSHKENT  VILOYATI  QIBRAY TUMANI ZAFARABOT XFY SHARQ MFY ZAFARABOT GULZOR UY; R/S</t>
         </is>
       </c>
       <c r="Q57" t="inlineStr">
         <is>
-          <t>+998917763438</t>
+          <t>+99833-001-18-10</t>
         </is>
       </c>
       <c r="R57" t="inlineStr">
         <is>
-          <t>MIKHAIL</t>
+          <t>NILUFAR</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>62</t>
+          <t>65</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>2025-05-30</t>
+          <t>2025-06-01</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
@@ -4899,10 +4899,10 @@
         </is>
       </c>
       <c r="D58" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E58" t="n">
-        <v>53</v>
+        <v>57</v>
       </c>
       <c r="F58" t="n">
         <v>1</v>
@@ -4911,47 +4911,47 @@
         <v>34.66</v>
       </c>
       <c r="H58" t="n">
-        <v>194096000</v>
+        <v>180232000</v>
       </c>
       <c r="I58" t="n">
-        <v>5600000</v>
+        <v>5200000</v>
       </c>
       <c r="J58" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>50</t>
         </is>
       </c>
       <c r="K58" t="n">
-        <v>58228800</v>
+        <v>90116000</v>
       </c>
       <c r="L58" t="inlineStr">
         <is>
-          <t>RAXMANOV JAVOHIR AHMAD O'G'LI</t>
+          <t>DAVLATBAYEV XASAN DILSHAD OGLI</t>
         </is>
       </c>
       <c r="M58" t="inlineStr">
         <is>
-          <t>AB4145338</t>
+          <t>AB6769142</t>
         </is>
       </c>
       <c r="N58" t="inlineStr">
         <is>
-          <t>33005975630050</t>
+          <t>52604016860035</t>
         </is>
       </c>
       <c r="O58" t="inlineStr">
         <is>
-          <t>10.06.2016 КАМАШИНСКИЙ РОВД, КАШКАДАРЬИНСКОЙ ОБЛАСТИ</t>
+          <t>TOSHKENT VILOYATI CHIRCHIQ SHAHAR IIB 19.05.2017</t>
         </is>
       </c>
       <c r="P58" t="inlineStr">
         <is>
-          <t>Qashqadaryo viloyati Qamashi tumani Gʻishtli MFY 102- uy</t>
+          <t>TOSHKENT VILOYATI CHIRCHIQ SHAHAR KIMYOGAR MFY YORKIN KELAJAK KUCHASI 2A UY</t>
         </is>
       </c>
       <c r="Q58" t="inlineStr">
         <is>
-          <t>+998946699007</t>
+          <t>+998998024662</t>
         </is>
       </c>
       <c r="R58" t="inlineStr">
@@ -4963,24 +4963,24 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>64</t>
+          <t>66</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>2025-05-31</t>
+          <t>2025-06-02</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Блок 3,1</t>
+          <t>Блок 3,2</t>
         </is>
       </c>
       <c r="D59" t="n">
         <v>4</v>
       </c>
       <c r="E59" t="n">
-        <v>238</v>
+        <v>268</v>
       </c>
       <c r="F59" t="n">
         <v>2</v>
@@ -5004,32 +5004,32 @@
       </c>
       <c r="L59" t="inlineStr">
         <is>
-          <t>MAXMUDOVA GULNUR ABDUMUTAL QIZI</t>
+          <t>MUSTAFAYEV ABDIMUROD OBULQOSIMOVICH</t>
         </is>
       </c>
       <c r="M59" t="inlineStr">
         <is>
-          <t>AD3854467</t>
+          <t>AD 0063132</t>
         </is>
       </c>
       <c r="N59" t="inlineStr">
         <is>
-          <t>41810966780046</t>
+          <t>32501848240012</t>
         </is>
       </c>
       <c r="O59" t="inlineStr">
         <is>
-          <t>IIV 27248</t>
+          <t>IIV 10411</t>
         </is>
       </c>
       <c r="P59" t="inlineStr">
         <is>
-          <t>TOSHKENT  VILOYATI  QIBRAY TUMANI ZAFARABOT XFY SHARQ MFY ZAFARABOT GULZOR UY; R/S</t>
+          <t xml:space="preserve">TOSHKENT SHAXRI YASHNOBOD TUMANI olmas MFY Kunduzsay ul 4tupik 12 uy 231 xonadon </t>
         </is>
       </c>
       <c r="Q59" t="inlineStr">
         <is>
-          <t>+99833-001-18-10</t>
+          <t>+998946408017</t>
         </is>
       </c>
       <c r="R59" t="inlineStr">
@@ -5041,33 +5041,33 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>65</t>
+          <t>69</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>2025-06-01</t>
+          <t>2025-06-07</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Блок-1,1</t>
+          <t>Блок 3,1</t>
         </is>
       </c>
       <c r="D60" t="n">
         <v>3</v>
       </c>
       <c r="E60" t="n">
-        <v>57</v>
+        <v>232</v>
       </c>
       <c r="F60" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G60" t="n">
-        <v>34.66</v>
+        <v>44.28</v>
       </c>
       <c r="H60" t="n">
-        <v>180232000</v>
+        <v>230256000</v>
       </c>
       <c r="I60" t="n">
         <v>5200000</v>
@@ -5078,155 +5078,155 @@
         </is>
       </c>
       <c r="K60" t="n">
-        <v>90116000</v>
+        <v>115128000</v>
       </c>
       <c r="L60" t="inlineStr">
         <is>
-          <t>DAVLATBAYEV XASAN DILSHAD OGLI</t>
+          <t xml:space="preserve">RASSKAZOVA DJAMILYA KARIMOVNA </t>
         </is>
       </c>
       <c r="M60" t="inlineStr">
         <is>
-          <t>AB6769142</t>
+          <t>AD1014793</t>
         </is>
       </c>
       <c r="N60" t="inlineStr">
         <is>
-          <t>52604016860035</t>
+          <t>42508900241339</t>
         </is>
       </c>
       <c r="O60" t="inlineStr">
         <is>
-          <t>TOSHKENT VILOYATI CHIRCHIQ SHAHAR IIB 19.05.2017</t>
+          <t xml:space="preserve">IIV26287   </t>
         </is>
       </c>
       <c r="P60" t="inlineStr">
         <is>
-          <t>TOSHKENT VILOYATI CHIRCHIQ SHAHAR KIMYOGAR MFY YORKIN KELAJAK KUCHASI 2A UY</t>
+          <t>г. Ташкент Яккасарайский р-н ул. Шота Руставелли дом 59-53</t>
         </is>
       </c>
       <c r="Q60" t="inlineStr">
         <is>
-          <t>+998998024662</t>
+          <t>+998909495490</t>
         </is>
       </c>
       <c r="R60" t="inlineStr">
         <is>
-          <t>AZIZ</t>
+          <t xml:space="preserve">михаил </t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>66</t>
+          <t>70</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>2025-06-02</t>
+          <t>2025-06-07</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Блок 3,2</t>
+          <t>Блок-1</t>
         </is>
       </c>
       <c r="D61" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E61" t="n">
-        <v>268</v>
+        <v>21</v>
       </c>
       <c r="F61" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G61" t="n">
-        <v>44.28</v>
+        <v>34.66</v>
       </c>
       <c r="H61" t="n">
-        <v>221400000</v>
+        <v>187164000</v>
       </c>
       <c r="I61" t="n">
-        <v>5000000</v>
+        <v>5400000</v>
       </c>
       <c r="J61" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>30</t>
         </is>
       </c>
       <c r="K61" t="n">
-        <v>110700000</v>
+        <v>56149200</v>
       </c>
       <c r="L61" t="inlineStr">
         <is>
-          <t>MUSTAFAYEV ABDIMUROD OBULQOSIMOVICH</t>
+          <t xml:space="preserve">IRGASHEV ALMAZ BAXADIROVICH </t>
         </is>
       </c>
       <c r="M61" t="inlineStr">
         <is>
-          <t>AD 0063132</t>
+          <t>AC1381774</t>
         </is>
       </c>
       <c r="N61" t="inlineStr">
         <is>
-          <t>32501848240012</t>
+          <t>52709026590029</t>
         </is>
       </c>
       <c r="O61" t="inlineStr">
         <is>
-          <t>IIV 10411</t>
+          <t>TOSHKENT SHAHAR CHILONZOR TUMANI IIB</t>
         </is>
       </c>
       <c r="P61" t="inlineStr">
         <is>
-          <t xml:space="preserve">TOSHKENT SHAXRI YASHNOBOD TUMANI olmas MFY Kunduzsay ul 4tupik 12 uy 231 xonadon </t>
+          <t>ЧИЛАНЗАР КВАРТАЛ-8 ДОМ 25 КВАТИРА 46</t>
         </is>
       </c>
       <c r="Q61" t="inlineStr">
         <is>
-          <t>+998946408017</t>
+          <t>+998903461245</t>
         </is>
       </c>
       <c r="R61" t="inlineStr">
         <is>
-          <t>NILUFAR</t>
+          <t>МИХАИЛ</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>69</t>
+          <t>71</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>2025-06-07</t>
+          <t>2025-06-08</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Блок 3,1</t>
+          <t>Блок-1</t>
         </is>
       </c>
       <c r="D62" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="E62" t="n">
-        <v>232</v>
+        <v>36</v>
       </c>
       <c r="F62" t="n">
         <v>2</v>
       </c>
       <c r="G62" t="n">
-        <v>44.28</v>
+        <v>50.34</v>
       </c>
       <c r="H62" t="n">
-        <v>230256000</v>
+        <v>241632000</v>
       </c>
       <c r="I62" t="n">
-        <v>5200000</v>
+        <v>4800000</v>
       </c>
       <c r="J62" t="inlineStr">
         <is>
@@ -5234,77 +5234,77 @@
         </is>
       </c>
       <c r="K62" t="n">
-        <v>115128000</v>
+        <v>120816000</v>
       </c>
       <c r="L62" t="inlineStr">
         <is>
-          <t xml:space="preserve">RASSKAZOVA DJAMILYA KARIMOVNA </t>
+          <t>XUDAYBERGANOVA ONAPOSHSHA YULDASHOVNA</t>
         </is>
       </c>
       <c r="M62" t="inlineStr">
         <is>
-          <t>AD1014793</t>
+          <t>AB34993983</t>
         </is>
       </c>
       <c r="N62" t="inlineStr">
         <is>
-          <t>42508900241339</t>
+          <t>41103823070070</t>
         </is>
       </c>
       <c r="O62" t="inlineStr">
         <is>
-          <t xml:space="preserve">IIV26287   </t>
+          <t>XORAZM VILOYATI BOG'OT TUMANI IIB</t>
         </is>
       </c>
       <c r="P62" t="inlineStr">
         <is>
-          <t>г. Ташкент Яккасарайский р-н ул. Шота Руставелли дом 59-53</t>
+          <t>TOSHKENT VILOYATI BO'STONLIQ TUMANI G'AZALKENT SHAHRI YANGI CHORBOG' MAHALLA BESH TOSH KO'CHASI 23-UY</t>
         </is>
       </c>
       <c r="Q62" t="inlineStr">
         <is>
-          <t>+998909495490</t>
+          <t>+998 99 563 82 02</t>
         </is>
       </c>
       <c r="R62" t="inlineStr">
         <is>
-          <t xml:space="preserve">михаил </t>
+          <t>NILUFAR</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>70</t>
+          <t>72</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>2025-06-07</t>
+          <t>2025-06-12</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Блок-1</t>
+          <t>Блок 3</t>
         </is>
       </c>
       <c r="D63" t="n">
+        <v>5</v>
+      </c>
+      <c r="E63" t="n">
+        <v>213</v>
+      </c>
+      <c r="F63" t="n">
         <v>3</v>
       </c>
-      <c r="E63" t="n">
-        <v>21</v>
-      </c>
-      <c r="F63" t="n">
-        <v>1</v>
-      </c>
       <c r="G63" t="n">
-        <v>34.66</v>
+        <v>55.67</v>
       </c>
       <c r="H63" t="n">
-        <v>187164000</v>
+        <v>278350000</v>
       </c>
       <c r="I63" t="n">
-        <v>5400000</v>
+        <v>5000000</v>
       </c>
       <c r="J63" t="inlineStr">
         <is>
@@ -5312,119 +5312,1289 @@
         </is>
       </c>
       <c r="K63" t="n">
-        <v>56149200</v>
+        <v>83505000</v>
       </c>
       <c r="L63" t="inlineStr">
         <is>
-          <t xml:space="preserve">IRGASHEV ALMAZ BAXADIROVICH </t>
+          <t xml:space="preserve">YUSUBJONOVA DONO XAYRIDINOVNA </t>
         </is>
       </c>
       <c r="M63" t="inlineStr">
         <is>
-          <t>AC1381774</t>
+          <t>AD7098958</t>
         </is>
       </c>
       <c r="N63" t="inlineStr">
         <is>
-          <t>52709026590029</t>
+          <t>40307860500069</t>
         </is>
       </c>
       <c r="O63" t="inlineStr">
         <is>
-          <t>TOSHKENT SHAHAR CHILONZOR TUMANI IIB</t>
+          <t>IIV27419  08.05.2024</t>
         </is>
       </c>
       <c r="P63" t="inlineStr">
         <is>
-          <t>ЧИЛАНЗАР КВАРТАЛ-8 ДОМ 25 КВАТИРА 46</t>
+          <t>CHIRCHIQ SHAHAR 64/4</t>
         </is>
       </c>
       <c r="Q63" t="inlineStr">
         <is>
-          <t>+998903461245</t>
+          <t>+998886773742</t>
         </is>
       </c>
       <c r="R63" t="inlineStr">
         <is>
-          <t>МИХАИЛ</t>
+          <t xml:space="preserve">ФАТИМА </t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>71</t>
+          <t>73</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>2025-06-08</t>
+          <t>2025-06-12</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Блок-1</t>
+          <t>Блок 3</t>
         </is>
       </c>
       <c r="D64" t="n">
+        <v>2</v>
+      </c>
+      <c r="E64" t="n">
+        <v>195</v>
+      </c>
+      <c r="F64" t="n">
+        <v>3</v>
+      </c>
+      <c r="G64" t="n">
+        <v>55.67</v>
+      </c>
+      <c r="H64" t="n">
+        <v>311752000</v>
+      </c>
+      <c r="I64" t="n">
+        <v>5600000</v>
+      </c>
+      <c r="J64" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="K64" t="n">
+        <v>93525600</v>
+      </c>
+      <c r="L64" t="inlineStr">
+        <is>
+          <t xml:space="preserve">YUSUBJONOVA DONO XAYRIDINOVNA </t>
+        </is>
+      </c>
+      <c r="M64" t="inlineStr">
+        <is>
+          <t>AD7098958</t>
+        </is>
+      </c>
+      <c r="N64" t="inlineStr">
+        <is>
+          <t>40307860500069</t>
+        </is>
+      </c>
+      <c r="O64" t="inlineStr">
+        <is>
+          <t>IIV27419  08.05.2024</t>
+        </is>
+      </c>
+      <c r="P64" t="inlineStr">
+        <is>
+          <t>CHIRCHIQ SHAHAR 64/4</t>
+        </is>
+      </c>
+      <c r="Q64" t="inlineStr">
+        <is>
+          <t>+998888773742</t>
+        </is>
+      </c>
+      <c r="R64" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ФАТИМА </t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>74</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>2025-06-13</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>Блок 2</t>
+        </is>
+      </c>
+      <c r="D65" t="n">
         <v>5</v>
       </c>
-      <c r="E64" t="n">
-        <v>36</v>
-      </c>
-      <c r="F64" t="n">
+      <c r="E65" t="n">
+        <v>105</v>
+      </c>
+      <c r="F65" t="n">
         <v>2</v>
       </c>
-      <c r="G64" t="n">
+      <c r="G65" t="n">
+        <v>48.13</v>
+      </c>
+      <c r="H65" t="n">
+        <v>240650000</v>
+      </c>
+      <c r="I65" t="n">
+        <v>5000000</v>
+      </c>
+      <c r="J65" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="K65" t="n">
+        <v>72195000</v>
+      </c>
+      <c r="L65" t="inlineStr">
+        <is>
+          <t>BOLTAYEV ALISHER AZAMATOVICH</t>
+        </is>
+      </c>
+      <c r="M65" t="inlineStr">
+        <is>
+          <t>AE2523040</t>
+        </is>
+      </c>
+      <c r="N65" t="inlineStr">
+        <is>
+          <t>32510941170030</t>
+        </is>
+      </c>
+      <c r="O65" t="inlineStr">
+        <is>
+          <t>IIV 27419 01.05.2025</t>
+        </is>
+      </c>
+      <c r="P65" t="inlineStr">
+        <is>
+          <t>TOSHKENT VILOYATI CHIRCHIQ SHAHAR YANHGI OZBEKISTON 5 UY 47 XONADON</t>
+        </is>
+      </c>
+      <c r="Q65" t="inlineStr">
+        <is>
+          <t>+998901260201</t>
+        </is>
+      </c>
+      <c r="R65" t="inlineStr">
+        <is>
+          <t>AZIZ</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>75</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>2025-06-14</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>Блок-1,1</t>
+        </is>
+      </c>
+      <c r="D66" t="n">
+        <v>5</v>
+      </c>
+      <c r="E66" t="n">
+        <v>80</v>
+      </c>
+      <c r="F66" t="n">
+        <v>1</v>
+      </c>
+      <c r="G66" t="n">
+        <v>34.66</v>
+      </c>
+      <c r="H66" t="n">
+        <v>152504000</v>
+      </c>
+      <c r="I66" t="n">
+        <v>4400000</v>
+      </c>
+      <c r="J66" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="K66" t="n">
+        <v>152504000</v>
+      </c>
+      <c r="L66" t="inlineStr">
+        <is>
+          <t>OSIPOVA NATALYA VLADIMIROVNA</t>
+        </is>
+      </c>
+      <c r="M66" t="inlineStr">
+        <is>
+          <t>AD9119200</t>
+        </is>
+      </c>
+      <c r="N66" t="inlineStr">
+        <is>
+          <t>41306820270029</t>
+        </is>
+      </c>
+      <c r="O66" t="inlineStr">
+        <is>
+          <t>IIV 26296 23.10.2024</t>
+        </is>
+      </c>
+      <c r="P66" t="inlineStr">
+        <is>
+          <t>TOSHKENT SHAHAR MIRZO ULUGBEK TUMANI KORASUV 4 2 UY 223 XONADON</t>
+        </is>
+      </c>
+      <c r="Q66" t="inlineStr">
+        <is>
+          <t>+998903509084 +998974509084</t>
+        </is>
+      </c>
+      <c r="R66" t="inlineStr">
+        <is>
+          <t xml:space="preserve">АЗИЗ </t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>77</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>2025-06-15</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>Блок-1,1</t>
+        </is>
+      </c>
+      <c r="D67" t="n">
+        <v>2</v>
+      </c>
+      <c r="E67" t="n">
+        <v>52</v>
+      </c>
+      <c r="F67" t="n">
+        <v>2</v>
+      </c>
+      <c r="G67" t="n">
         <v>50.34</v>
       </c>
-      <c r="H64" t="n">
+      <c r="H67" t="n">
+        <v>271836000</v>
+      </c>
+      <c r="I67" t="n">
+        <v>5400000</v>
+      </c>
+      <c r="J67" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="K67" t="n">
+        <v>135918000</v>
+      </c>
+      <c r="L67" t="inlineStr">
+        <is>
+          <t xml:space="preserve">KARSHIYEV DILSHOD ABDURAXMANOVICH </t>
+        </is>
+      </c>
+      <c r="M67" t="inlineStr">
+        <is>
+          <t>AD3846805</t>
+        </is>
+      </c>
+      <c r="N67" t="inlineStr">
+        <is>
+          <t>32404640060016</t>
+        </is>
+      </c>
+      <c r="O67" t="inlineStr">
+        <is>
+          <t>IIV26291</t>
+        </is>
+      </c>
+      <c r="P67" t="inlineStr">
+        <is>
+          <t>Ташкент  Яшнабадский  р-н ул. Истикбол дом-1 кв-25</t>
+        </is>
+      </c>
+      <c r="Q67" t="inlineStr">
+        <is>
+          <t>+998901745602      +998909006759</t>
+        </is>
+      </c>
+      <c r="R67" t="inlineStr">
+        <is>
+          <t xml:space="preserve">михаил </t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>78</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>2025-06-16</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>Блок 1,2</t>
+        </is>
+      </c>
+      <c r="D68" t="n">
+        <v>3</v>
+      </c>
+      <c r="E68" t="n">
+        <v>132</v>
+      </c>
+      <c r="F68" t="n">
+        <v>1</v>
+      </c>
+      <c r="G68" t="n">
+        <v>34.66</v>
+      </c>
+      <c r="H68" t="n">
+        <v>166368000</v>
+      </c>
+      <c r="I68" t="n">
+        <v>4800000</v>
+      </c>
+      <c r="J68" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="K68" t="n">
+        <v>166368000</v>
+      </c>
+      <c r="L68" t="inlineStr">
+        <is>
+          <t xml:space="preserve">XABIBULLAYEV JAMOLIDDIN XAYRULLA OGLI </t>
+        </is>
+      </c>
+      <c r="M68" t="inlineStr">
+        <is>
+          <t>AB6930577</t>
+        </is>
+      </c>
+      <c r="N68" t="inlineStr">
+        <is>
+          <t>524110067200114</t>
+        </is>
+      </c>
+      <c r="O68" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TOSHKENT VILOYATI BOSTONLIQ TUMANI IIB </t>
+        </is>
+      </c>
+      <c r="P68" t="inlineStr">
+        <is>
+          <t>Тошкент Вилояти Бостонлик тумани Товоксой Нурчилар-76</t>
+        </is>
+      </c>
+      <c r="Q68" t="inlineStr">
+        <is>
+          <t>+998901327755</t>
+        </is>
+      </c>
+      <c r="R68" t="inlineStr">
+        <is>
+          <t>Руководство</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>79</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>2025-06-16</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>Блок 3,1</t>
+        </is>
+      </c>
+      <c r="D69" t="n">
+        <v>3</v>
+      </c>
+      <c r="E69" t="n">
+        <v>236</v>
+      </c>
+      <c r="F69" t="n">
+        <v>1</v>
+      </c>
+      <c r="G69" t="n">
+        <v>25.04</v>
+      </c>
+      <c r="H69" t="n">
+        <v>120192000</v>
+      </c>
+      <c r="I69" t="n">
+        <v>4800000</v>
+      </c>
+      <c r="J69" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="K69" t="n">
+        <v>120192000</v>
+      </c>
+      <c r="L69" t="inlineStr">
+        <is>
+          <t xml:space="preserve">KHABIBULAYEV JAMOLODDIN XAYRULLA OGLI </t>
+        </is>
+      </c>
+      <c r="M69" t="inlineStr">
+        <is>
+          <t>AB6930577</t>
+        </is>
+      </c>
+      <c r="N69" t="inlineStr">
+        <is>
+          <t>524110067200114</t>
+        </is>
+      </c>
+      <c r="O69" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TOSHKENT VILOYATI BOSTONLIQ TUMANI IIB </t>
+        </is>
+      </c>
+      <c r="P69" t="inlineStr">
+        <is>
+          <t>Тошкент Вилояти Бостонлик тумани Товоксой Нурчилар-76</t>
+        </is>
+      </c>
+      <c r="Q69" t="inlineStr">
+        <is>
+          <t>+998901327755</t>
+        </is>
+      </c>
+      <c r="R69" t="inlineStr">
+        <is>
+          <t>Руководство</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>86</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>2025-06-19</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>Блок 3,1</t>
+        </is>
+      </c>
+      <c r="D70" t="n">
+        <v>2</v>
+      </c>
+      <c r="E70" t="n">
+        <v>229</v>
+      </c>
+      <c r="F70" t="n">
+        <v>3</v>
+      </c>
+      <c r="G70" t="n">
+        <v>57.77</v>
+      </c>
+      <c r="H70" t="n">
+        <v>323512000</v>
+      </c>
+      <c r="I70" t="n">
+        <v>5600000</v>
+      </c>
+      <c r="J70" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="K70" t="n">
+        <v>97053600</v>
+      </c>
+      <c r="L70" t="inlineStr">
+        <is>
+          <t xml:space="preserve">AXMEDOVA MEXRIBON SAPAEVNA </t>
+        </is>
+      </c>
+      <c r="M70" t="inlineStr">
+        <is>
+          <t>AE2721527</t>
+        </is>
+      </c>
+      <c r="N70" t="inlineStr">
+        <is>
+          <t>411106631160030</t>
+        </is>
+      </c>
+      <c r="O70" t="inlineStr">
+        <is>
+          <t>IIV33401</t>
+        </is>
+      </c>
+      <c r="P70" t="inlineStr">
+        <is>
+          <t>XORAZIM VILOYATI  URGENCH SHAHAR NAVRUZTOR KOCHASI 22-UY</t>
+        </is>
+      </c>
+      <c r="Q70" t="inlineStr">
+        <is>
+          <t>+998978536611</t>
+        </is>
+      </c>
+      <c r="R70" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ФАТИМА </t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>87</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>2025-06-22</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>Блок 1,2</t>
+        </is>
+      </c>
+      <c r="D71" t="n">
+        <v>2</v>
+      </c>
+      <c r="E71" t="n">
+        <v>120</v>
+      </c>
+      <c r="F71" t="n">
+        <v>2</v>
+      </c>
+      <c r="G71" t="n">
+        <v>50.34</v>
+      </c>
+      <c r="H71" t="n">
+        <v>261768000</v>
+      </c>
+      <c r="I71" t="n">
+        <v>5200000</v>
+      </c>
+      <c r="J71" t="inlineStr">
+        <is>
+          <t>70</t>
+        </is>
+      </c>
+      <c r="K71" t="n">
+        <v>183237600</v>
+      </c>
+      <c r="L71" t="inlineStr">
+        <is>
+          <t>MADREIMOV ANVAR IBADULLAYEVICH</t>
+        </is>
+      </c>
+      <c r="M71" t="inlineStr">
+        <is>
+          <t>AD1854109</t>
+        </is>
+      </c>
+      <c r="N71" t="inlineStr">
+        <is>
+          <t>32809873480015</t>
+        </is>
+      </c>
+      <c r="O71" t="inlineStr">
+        <is>
+          <t>IIV26296</t>
+        </is>
+      </c>
+      <c r="P71" t="inlineStr">
+        <is>
+          <t xml:space="preserve">М. Улугбек р-н улица М.Улугбек 111 дом 48-квартира </t>
+        </is>
+      </c>
+      <c r="Q71" t="inlineStr">
+        <is>
+          <t>+998901255254      +998887085254</t>
+        </is>
+      </c>
+      <c r="R71" t="inlineStr">
+        <is>
+          <t xml:space="preserve">михаил </t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>88</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>2025-06-24</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>Блок 1,2</t>
+        </is>
+      </c>
+      <c r="D72" t="n">
+        <v>5</v>
+      </c>
+      <c r="E72" t="n">
+        <v>144</v>
+      </c>
+      <c r="F72" t="n">
+        <v>2</v>
+      </c>
+      <c r="G72" t="n">
+        <v>50.34</v>
+      </c>
+      <c r="H72" t="n">
         <v>241632000</v>
       </c>
-      <c r="I64" t="n">
+      <c r="I72" t="n">
         <v>4800000</v>
       </c>
-      <c r="J64" t="inlineStr">
+      <c r="J72" t="inlineStr">
         <is>
           <t>50</t>
         </is>
       </c>
-      <c r="K64" t="n">
+      <c r="K72" t="n">
         <v>120816000</v>
       </c>
-      <c r="L64" t="inlineStr">
-        <is>
-          <t>XUDAYBERGANOVA ONAPOSHSHA YULDASHOVNA</t>
-        </is>
-      </c>
-      <c r="M64" t="inlineStr">
-        <is>
-          <t>AB34993983</t>
-        </is>
-      </c>
-      <c r="N64" t="inlineStr">
-        <is>
-          <t>41103823070070</t>
-        </is>
-      </c>
-      <c r="O64" t="inlineStr">
-        <is>
-          <t>XORAZM VILOYATI BOG'OT TUMANI IIB</t>
-        </is>
-      </c>
-      <c r="P64" t="inlineStr">
-        <is>
-          <t>TOSHKENT VILOYATI BO'STONLIQ TUMANI G'AZALKENT SHAHRI YANGI CHORBOG' MAHALLA BESH TOSH KO'CHASI 23-UY</t>
-        </is>
-      </c>
-      <c r="Q64" t="inlineStr">
-        <is>
-          <t>+998 99 563 82 02</t>
-        </is>
-      </c>
-      <c r="R64" t="inlineStr">
-        <is>
-          <t>NILUFAR</t>
+      <c r="L72" t="inlineStr">
+        <is>
+          <t>PAYAZOVA GULCHEXRA DIKAMBAYEVNA</t>
+        </is>
+      </c>
+      <c r="M72" t="inlineStr">
+        <is>
+          <t>AD4348777</t>
+        </is>
+      </c>
+      <c r="N72" t="inlineStr">
+        <is>
+          <t>42411796860013</t>
+        </is>
+      </c>
+      <c r="O72" t="inlineStr">
+        <is>
+          <t>IIV 27419</t>
+        </is>
+      </c>
+      <c r="P72" t="inlineStr">
+        <is>
+          <t>TOSHKENT VILOYATI CHIRCHIQ SHAHAR VOHID XAYDAROV KO'CHASI 29-UY 48-XONADON</t>
+        </is>
+      </c>
+      <c r="Q72" t="inlineStr">
+        <is>
+          <t>+998 88 345 11 50</t>
+        </is>
+      </c>
+      <c r="R72" t="inlineStr">
+        <is>
+          <t>DILFUZA</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>89</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>2025-06-28</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>Блок 3</t>
+        </is>
+      </c>
+      <c r="D73" t="n">
+        <v>2</v>
+      </c>
+      <c r="E73" t="n">
+        <v>198</v>
+      </c>
+      <c r="F73" t="n">
+        <v>2</v>
+      </c>
+      <c r="G73" t="n">
+        <v>46.67</v>
+      </c>
+      <c r="H73" t="n">
+        <v>261352000</v>
+      </c>
+      <c r="I73" t="n">
+        <v>5600000</v>
+      </c>
+      <c r="J73" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="K73" t="n">
+        <v>78405600</v>
+      </c>
+      <c r="L73" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TUYCHIBEKOVA ZULFIYA ILESBAYEVNA </t>
+        </is>
+      </c>
+      <c r="M73" t="inlineStr">
+        <is>
+          <t>AD2122621</t>
+        </is>
+      </c>
+      <c r="N73" t="inlineStr">
+        <is>
+          <t>41303680840018</t>
+        </is>
+      </c>
+      <c r="O73" t="inlineStr">
+        <is>
+          <t>IIV27419</t>
+        </is>
+      </c>
+      <c r="P73" t="inlineStr">
+        <is>
+          <t>10-мкр дом-93 квартира-11</t>
+        </is>
+      </c>
+      <c r="Q73" t="inlineStr">
+        <is>
+          <t>+998917796107  978711087</t>
+        </is>
+      </c>
+      <c r="R73" t="inlineStr">
+        <is>
+          <t xml:space="preserve">михаил </t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>91</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>2025-06-28</t>
+        </is>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>Блок 3,2</t>
+        </is>
+      </c>
+      <c r="D74" t="n">
+        <v>4</v>
+      </c>
+      <c r="E74" t="n">
+        <v>271</v>
+      </c>
+      <c r="F74" t="n">
+        <v>3</v>
+      </c>
+      <c r="G74" t="n">
+        <v>57.77</v>
+      </c>
+      <c r="H74" t="n">
+        <v>277296000</v>
+      </c>
+      <c r="I74" t="n">
+        <v>4800000</v>
+      </c>
+      <c r="J74" t="inlineStr">
+        <is>
+          <t>70</t>
+        </is>
+      </c>
+      <c r="K74" t="n">
+        <v>194107200</v>
+      </c>
+      <c r="L74" t="inlineStr">
+        <is>
+          <t xml:space="preserve">KURBANOVA RANO URUMBAYEVNA </t>
+        </is>
+      </c>
+      <c r="M74" t="inlineStr">
+        <is>
+          <t>AD4133774</t>
+        </is>
+      </c>
+      <c r="N74" t="inlineStr">
+        <is>
+          <t>43010750470023</t>
+        </is>
+      </c>
+      <c r="O74" t="inlineStr">
+        <is>
+          <t>IIV27419</t>
+        </is>
+      </c>
+      <c r="P74" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> Г. ЧИРЧИК  ТУПИК АЙНИ-17А</t>
+        </is>
+      </c>
+      <c r="Q74" t="inlineStr">
+        <is>
+          <t>+998935401828    +998994004231</t>
+        </is>
+      </c>
+      <c r="R74" t="inlineStr">
+        <is>
+          <t>Aziz</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>92</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>2025-06-30</t>
+        </is>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>Блок 2</t>
+        </is>
+      </c>
+      <c r="D75" t="n">
+        <v>3</v>
+      </c>
+      <c r="E75" t="n">
+        <v>93</v>
+      </c>
+      <c r="F75" t="n">
+        <v>2</v>
+      </c>
+      <c r="G75" t="n">
+        <v>48.13</v>
+      </c>
+      <c r="H75" t="n">
+        <v>259902000</v>
+      </c>
+      <c r="I75" t="n">
+        <v>5400000</v>
+      </c>
+      <c r="J75" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="K75" t="n">
+        <v>77970600</v>
+      </c>
+      <c r="L75" t="inlineStr">
+        <is>
+          <t xml:space="preserve">SUYUNOVA GULNARA IZETOVNA </t>
+        </is>
+      </c>
+      <c r="M75" t="inlineStr">
+        <is>
+          <t>AD9337235</t>
+        </is>
+      </c>
+      <c r="N75" t="inlineStr">
+        <is>
+          <t>40710600500010</t>
+        </is>
+      </c>
+      <c r="O75" t="inlineStr">
+        <is>
+          <t>IIV27419   09.11.2024</t>
+        </is>
+      </c>
+      <c r="P75" t="inlineStr">
+        <is>
+          <t>TOSHKENT VILOYATI BOSTONLIQ TUMANI AZADBASH MFY PAXTA KUCHASI 3 UY 15 XONADON</t>
+        </is>
+      </c>
+      <c r="Q75" t="inlineStr">
+        <is>
+          <t>+998509970157</t>
+        </is>
+      </c>
+      <c r="R75" t="inlineStr">
+        <is>
+          <t>AZIZ</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>93</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>2025-06-30</t>
+        </is>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>Блок 3,1</t>
+        </is>
+      </c>
+      <c r="D76" t="n">
+        <v>2</v>
+      </c>
+      <c r="E76" t="n">
+        <v>226</v>
+      </c>
+      <c r="F76" t="n">
+        <v>2</v>
+      </c>
+      <c r="G76" t="n">
+        <v>44.28</v>
+      </c>
+      <c r="H76" t="n">
+        <v>247968000</v>
+      </c>
+      <c r="I76" t="n">
+        <v>5600000</v>
+      </c>
+      <c r="J76" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="K76" t="n">
+        <v>74390400</v>
+      </c>
+      <c r="L76" t="inlineStr">
+        <is>
+          <t>UMAROVA JANILGAN MALDAYEVNA</t>
+        </is>
+      </c>
+      <c r="M76" t="inlineStr">
+        <is>
+          <t>AD9959841</t>
+        </is>
+      </c>
+      <c r="N76" t="inlineStr">
+        <is>
+          <t>40611580470022</t>
+        </is>
+      </c>
+      <c r="O76" t="inlineStr">
+        <is>
+          <t>IIV 27419</t>
+        </is>
+      </c>
+      <c r="P76" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CHIRCHIQ SHAHAR 2-MIKRORAYON 3-DOM 65-XONADON </t>
+        </is>
+      </c>
+      <c r="Q76" t="inlineStr">
+        <is>
+          <t>+998943611989</t>
+        </is>
+      </c>
+      <c r="R76" t="inlineStr">
+        <is>
+          <t>AZIZ</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>94</t>
+        </is>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>2025-06-30</t>
+        </is>
+      </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>Блок-1,1</t>
+        </is>
+      </c>
+      <c r="D77" t="n">
+        <v>5</v>
+      </c>
+      <c r="E77" t="n">
+        <v>77</v>
+      </c>
+      <c r="F77" t="n">
+        <v>1</v>
+      </c>
+      <c r="G77" t="n">
+        <v>34.66</v>
+      </c>
+      <c r="H77" t="n">
+        <v>173300000</v>
+      </c>
+      <c r="I77" t="n">
+        <v>5000000</v>
+      </c>
+      <c r="J77" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="K77" t="n">
+        <v>51990000</v>
+      </c>
+      <c r="L77" t="inlineStr">
+        <is>
+          <t>ERGASHEV ISLOM ABDIGANIYEVICH</t>
+        </is>
+      </c>
+      <c r="M77" t="inlineStr">
+        <is>
+          <t>AD8839971</t>
+        </is>
+      </c>
+      <c r="N77" t="inlineStr">
+        <is>
+          <t>312059860035</t>
+        </is>
+      </c>
+      <c r="O77" t="inlineStr">
+        <is>
+          <t>IIV 27419 02.10.2024</t>
+        </is>
+      </c>
+      <c r="P77" t="inlineStr">
+        <is>
+          <t>TOSHKENT VILOYATI CHIRCHIK SHAHAR 10 KICHIK NOXIYA 10 UY 45 XONADON</t>
+        </is>
+      </c>
+      <c r="Q77" t="inlineStr">
+        <is>
+          <t>+998887388818</t>
+        </is>
+      </c>
+      <c r="R77" t="inlineStr">
+        <is>
+          <t>Руководство</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>95</t>
+        </is>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>2025-07-01</t>
+        </is>
+      </c>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>Блок 3,2</t>
+        </is>
+      </c>
+      <c r="D78" t="n">
+        <v>4</v>
+      </c>
+      <c r="E78" t="n">
+        <v>268</v>
+      </c>
+      <c r="F78" t="n">
+        <v>2</v>
+      </c>
+      <c r="G78" t="n">
+        <v>44.28</v>
+      </c>
+      <c r="H78" t="n">
+        <v>212544000</v>
+      </c>
+      <c r="I78" t="n">
+        <v>4800000</v>
+      </c>
+      <c r="J78" t="inlineStr">
+        <is>
+          <t>70</t>
+        </is>
+      </c>
+      <c r="K78" t="n">
+        <v>148780800</v>
+      </c>
+      <c r="L78" t="inlineStr">
+        <is>
+          <t xml:space="preserve">BOYKO LYUDMILA VASILEVNA </t>
+        </is>
+      </c>
+      <c r="M78" t="inlineStr">
+        <is>
+          <t>AD3085165</t>
+        </is>
+      </c>
+      <c r="N78" t="inlineStr">
+        <is>
+          <t>41212622630016</t>
+        </is>
+      </c>
+      <c r="O78" t="inlineStr">
+        <is>
+          <t>IIV27419  18/04/2023</t>
+        </is>
+      </c>
+      <c r="P78" t="inlineStr">
+        <is>
+          <t xml:space="preserve">КАШКАДАРЬИНСКИЙ ВИЛОЯТ КАСАНСКИЙ ТУМАН ПАХТАЗОР МФЙ маркази кучаси 3/6- уй 7- хонадон </t>
+        </is>
+      </c>
+      <c r="Q78" t="inlineStr">
+        <is>
+          <t>998907163506   998912622670</t>
+        </is>
+      </c>
+      <c r="R78" t="inlineStr">
+        <is>
+          <t xml:space="preserve">михаил </t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>96</t>
+        </is>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>2025-07-01</t>
+        </is>
+      </c>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>Блок 2</t>
+        </is>
+      </c>
+      <c r="D79" t="n">
+        <v>2</v>
+      </c>
+      <c r="E79" t="n">
+        <v>87</v>
+      </c>
+      <c r="F79" t="n">
+        <v>2</v>
+      </c>
+      <c r="G79" t="n">
+        <v>48.13</v>
+      </c>
+      <c r="H79" t="n">
+        <v>240650000</v>
+      </c>
+      <c r="I79" t="n">
+        <v>5000000</v>
+      </c>
+      <c r="J79" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="K79" t="n">
+        <v>240650000</v>
+      </c>
+      <c r="L79" t="inlineStr">
+        <is>
+          <t>SALIYEV RUZI XIZAMEDENOVICH</t>
+        </is>
+      </c>
+      <c r="M79" t="inlineStr">
+        <is>
+          <t>AD6776174</t>
+        </is>
+      </c>
+      <c r="N79" t="inlineStr">
+        <is>
+          <t>30109760470049</t>
+        </is>
+      </c>
+      <c r="O79" t="inlineStr">
+        <is>
+          <t>IIV 27419 09.04.2024</t>
+        </is>
+      </c>
+      <c r="P79" t="inlineStr">
+        <is>
+          <t>TOSHKENT VILOYATI CHIRCHIQ 8 KICHIK NOXIYA 24 UY 46 XONADON</t>
+        </is>
+      </c>
+      <c r="Q79" t="inlineStr">
+        <is>
+          <t>+998917757912</t>
+        </is>
+      </c>
+      <c r="R79" t="inlineStr">
+        <is>
+          <t xml:space="preserve">михаил </t>
         </is>
       </c>
     </row>
